--- a/site/data/banka-mdc-kirilimi.xlsx
+++ b/site/data/banka-mdc-kirilimi.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U312"/>
+  <dimension ref="A1:U313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11775,72 +11775,72 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="6" t="inlineStr">
-        <is>
-          <t>TSKB</t>
-        </is>
-      </c>
-      <c r="B174" s="7" t="inlineStr">
-        <is>
-          <t>2021 Ç1</t>
-        </is>
-      </c>
-      <c r="C174" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D174" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E174" s="8" t="n">
-        <v>2254</v>
-      </c>
-      <c r="F174" s="8" t="n">
-        <v>6096</v>
-      </c>
-      <c r="G174" s="8" t="n">
-        <v>3322</v>
-      </c>
-      <c r="H174" s="8" t="n">
-        <v>634</v>
-      </c>
-      <c r="I174" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J174" s="8" t="n">
-        <v>263</v>
-      </c>
-      <c r="K174" s="8" t="n">
-        <v>374</v>
-      </c>
-      <c r="L174" s="8" t="n">
-        <v>197</v>
-      </c>
-      <c r="M174" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N174" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O174" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P174" s="8" t="n">
-        <v>263</v>
-      </c>
-      <c r="Q174" s="8" t="n">
-        <v>2628</v>
-      </c>
-      <c r="R174" s="8" t="n">
-        <v>6293</v>
-      </c>
-      <c r="S174" s="8" t="n">
-        <v>3322</v>
-      </c>
-      <c r="T174" s="8" t="n">
-        <v>634</v>
-      </c>
-      <c r="U174" s="9" t="n">
-        <v>13140</v>
+      <c r="A174" s="10" t="inlineStr">
+        <is>
+          <t>TEB</t>
+        </is>
+      </c>
+      <c r="B174" s="11" t="inlineStr">
+        <is>
+          <t>2026 Ç3</t>
+        </is>
+      </c>
+      <c r="C174" s="12" t="n">
+        <v>2808</v>
+      </c>
+      <c r="D174" s="12" t="n">
+        <v>707</v>
+      </c>
+      <c r="E174" s="12" t="n">
+        <v>27437</v>
+      </c>
+      <c r="F174" s="12" t="n">
+        <v>1786</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>61004</v>
+      </c>
+      <c r="H174" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" s="12" t="n">
+        <v>338</v>
+      </c>
+      <c r="J174" s="12" t="n">
+        <v>774</v>
+      </c>
+      <c r="K174" s="12" t="n">
+        <v>270</v>
+      </c>
+      <c r="L174" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" s="12" t="n">
+        <v>3146</v>
+      </c>
+      <c r="P174" s="12" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Q174" s="12" t="n">
+        <v>27707</v>
+      </c>
+      <c r="R174" s="12" t="n">
+        <v>1786</v>
+      </c>
+      <c r="S174" s="12" t="n">
+        <v>61004</v>
+      </c>
+      <c r="T174" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U174" s="13" t="n">
+        <v>95124</v>
       </c>
     </row>
     <row r="175">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="B175" s="7" t="inlineStr">
         <is>
-          <t>2021 Ç2</t>
+          <t>2021 Ç1</t>
         </is>
       </c>
       <c r="C175" s="8" t="n">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="B176" s="7" t="inlineStr">
         <is>
-          <t>2021 Ç3</t>
+          <t>2021 Ç2</t>
         </is>
       </c>
       <c r="C176" s="8" t="n">
@@ -11989,7 +11989,7 @@
       </c>
       <c r="B177" s="7" t="inlineStr">
         <is>
-          <t>2021 Ç4</t>
+          <t>2021 Ç3</t>
         </is>
       </c>
       <c r="C177" s="8" t="n">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="B178" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç1</t>
+          <t>2021 Ç4</t>
         </is>
       </c>
       <c r="C178" s="8" t="n">
@@ -12068,28 +12068,28 @@
         <v>0</v>
       </c>
       <c r="E178" s="8" t="n">
-        <v>2187</v>
+        <v>2254</v>
       </c>
       <c r="F178" s="8" t="n">
-        <v>7806</v>
+        <v>6096</v>
       </c>
       <c r="G178" s="8" t="n">
-        <v>3848</v>
+        <v>3322</v>
       </c>
       <c r="H178" s="8" t="n">
-        <v>687</v>
+        <v>634</v>
       </c>
       <c r="I178" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J178" s="8" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="K178" s="8" t="n">
-        <v>310</v>
+        <v>374</v>
       </c>
       <c r="L178" s="8" t="n">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="M178" s="8" t="n">
         <v>0</v>
@@ -12101,22 +12101,22 @@
         <v>0</v>
       </c>
       <c r="P178" s="8" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="Q178" s="8" t="n">
-        <v>2497</v>
+        <v>2628</v>
       </c>
       <c r="R178" s="8" t="n">
-        <v>8035</v>
+        <v>6293</v>
       </c>
       <c r="S178" s="8" t="n">
-        <v>3848</v>
+        <v>3322</v>
       </c>
       <c r="T178" s="8" t="n">
-        <v>687</v>
+        <v>634</v>
       </c>
       <c r="U178" s="9" t="n">
-        <v>15068</v>
+        <v>13140</v>
       </c>
     </row>
     <row r="179">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="B179" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç2</t>
+          <t>2022 Ç1</t>
         </is>
       </c>
       <c r="C179" s="8" t="n">
@@ -12137,16 +12137,16 @@
         <v>0</v>
       </c>
       <c r="E179" s="8" t="n">
-        <v>2456</v>
+        <v>2187</v>
       </c>
       <c r="F179" s="8" t="n">
-        <v>8566</v>
+        <v>7806</v>
       </c>
       <c r="G179" s="8" t="n">
-        <v>4413</v>
+        <v>3848</v>
       </c>
       <c r="H179" s="8" t="n">
-        <v>4145</v>
+        <v>687</v>
       </c>
       <c r="I179" s="8" t="n">
         <v>0</v>
@@ -12155,10 +12155,10 @@
         <v>0</v>
       </c>
       <c r="K179" s="8" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
       <c r="L179" s="8" t="n">
-        <v>307</v>
+        <v>229</v>
       </c>
       <c r="M179" s="8" t="n">
         <v>0</v>
@@ -12173,19 +12173,19 @@
         <v>0</v>
       </c>
       <c r="Q179" s="8" t="n">
-        <v>2798</v>
+        <v>2497</v>
       </c>
       <c r="R179" s="8" t="n">
-        <v>8873</v>
+        <v>8035</v>
       </c>
       <c r="S179" s="8" t="n">
-        <v>4413</v>
+        <v>3848</v>
       </c>
       <c r="T179" s="8" t="n">
-        <v>4145</v>
+        <v>687</v>
       </c>
       <c r="U179" s="9" t="n">
-        <v>20230</v>
+        <v>15068</v>
       </c>
     </row>
     <row r="180">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="B180" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç3</t>
+          <t>2022 Ç2</t>
         </is>
       </c>
       <c r="C180" s="8" t="n">
@@ -12206,16 +12206,16 @@
         <v>0</v>
       </c>
       <c r="E180" s="8" t="n">
-        <v>2747</v>
+        <v>2456</v>
       </c>
       <c r="F180" s="8" t="n">
-        <v>8245</v>
+        <v>8566</v>
       </c>
       <c r="G180" s="8" t="n">
-        <v>5557</v>
+        <v>4413</v>
       </c>
       <c r="H180" s="8" t="n">
-        <v>4520</v>
+        <v>4145</v>
       </c>
       <c r="I180" s="8" t="n">
         <v>0</v>
@@ -12224,10 +12224,10 @@
         <v>0</v>
       </c>
       <c r="K180" s="8" t="n">
-        <v>426</v>
+        <v>342</v>
       </c>
       <c r="L180" s="8" t="n">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="M180" s="8" t="n">
         <v>0</v>
@@ -12242,19 +12242,19 @@
         <v>0</v>
       </c>
       <c r="Q180" s="8" t="n">
-        <v>3173</v>
+        <v>2798</v>
       </c>
       <c r="R180" s="8" t="n">
-        <v>8576</v>
+        <v>8873</v>
       </c>
       <c r="S180" s="8" t="n">
-        <v>5557</v>
+        <v>4413</v>
       </c>
       <c r="T180" s="8" t="n">
-        <v>4520</v>
+        <v>4145</v>
       </c>
       <c r="U180" s="9" t="n">
-        <v>21826</v>
+        <v>20230</v>
       </c>
     </row>
     <row r="181">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="B181" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç4</t>
+          <t>2022 Ç3</t>
         </is>
       </c>
       <c r="C181" s="8" t="n">
@@ -12275,16 +12275,16 @@
         <v>0</v>
       </c>
       <c r="E181" s="8" t="n">
-        <v>2846</v>
+        <v>2747</v>
       </c>
       <c r="F181" s="8" t="n">
-        <v>6903</v>
+        <v>8245</v>
       </c>
       <c r="G181" s="8" t="n">
-        <v>6196</v>
+        <v>5557</v>
       </c>
       <c r="H181" s="8" t="n">
-        <v>6630</v>
+        <v>4520</v>
       </c>
       <c r="I181" s="8" t="n">
         <v>0</v>
@@ -12293,10 +12293,10 @@
         <v>0</v>
       </c>
       <c r="K181" s="8" t="n">
-        <v>897</v>
+        <v>426</v>
       </c>
       <c r="L181" s="8" t="n">
-        <v>407</v>
+        <v>330</v>
       </c>
       <c r="M181" s="8" t="n">
         <v>0</v>
@@ -12311,19 +12311,19 @@
         <v>0</v>
       </c>
       <c r="Q181" s="8" t="n">
-        <v>3744</v>
+        <v>3173</v>
       </c>
       <c r="R181" s="8" t="n">
-        <v>7310</v>
+        <v>8576</v>
       </c>
       <c r="S181" s="8" t="n">
-        <v>6196</v>
+        <v>5557</v>
       </c>
       <c r="T181" s="8" t="n">
-        <v>6630</v>
+        <v>4520</v>
       </c>
       <c r="U181" s="9" t="n">
-        <v>23880</v>
+        <v>21826</v>
       </c>
     </row>
     <row r="182">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="B182" s="7" t="inlineStr">
         <is>
-          <t>2023 Ç1</t>
+          <t>2022 Ç4</t>
         </is>
       </c>
       <c r="C182" s="8" t="n">
@@ -12344,16 +12344,16 @@
         <v>0</v>
       </c>
       <c r="E182" s="8" t="n">
-        <v>2586</v>
+        <v>2846</v>
       </c>
       <c r="F182" s="8" t="n">
-        <v>4232</v>
+        <v>6903</v>
       </c>
       <c r="G182" s="8" t="n">
-        <v>6992</v>
+        <v>6196</v>
       </c>
       <c r="H182" s="8" t="n">
-        <v>6754</v>
+        <v>6630</v>
       </c>
       <c r="I182" s="8" t="n">
         <v>0</v>
@@ -12362,10 +12362,10 @@
         <v>0</v>
       </c>
       <c r="K182" s="8" t="n">
-        <v>796</v>
+        <v>897</v>
       </c>
       <c r="L182" s="8" t="n">
-        <v>460</v>
+        <v>407</v>
       </c>
       <c r="M182" s="8" t="n">
         <v>0</v>
@@ -12380,19 +12380,19 @@
         <v>0</v>
       </c>
       <c r="Q182" s="8" t="n">
-        <v>3382</v>
+        <v>3744</v>
       </c>
       <c r="R182" s="8" t="n">
-        <v>4693</v>
+        <v>7310</v>
       </c>
       <c r="S182" s="8" t="n">
-        <v>6992</v>
+        <v>6196</v>
       </c>
       <c r="T182" s="8" t="n">
-        <v>6754</v>
+        <v>6630</v>
       </c>
       <c r="U182" s="9" t="n">
-        <v>21820</v>
+        <v>23880</v>
       </c>
     </row>
     <row r="183">
@@ -12403,7 +12403,7 @@
       </c>
       <c r="B183" s="7" t="inlineStr">
         <is>
-          <t>2023 Ç2</t>
+          <t>2023 Ç1</t>
         </is>
       </c>
       <c r="C183" s="8" t="n">
@@ -12413,16 +12413,16 @@
         <v>0</v>
       </c>
       <c r="E183" s="8" t="n">
-        <v>2464</v>
+        <v>2586</v>
       </c>
       <c r="F183" s="8" t="n">
-        <v>5627</v>
+        <v>4232</v>
       </c>
       <c r="G183" s="8" t="n">
-        <v>7304</v>
+        <v>6992</v>
       </c>
       <c r="H183" s="8" t="n">
-        <v>9241</v>
+        <v>6754</v>
       </c>
       <c r="I183" s="8" t="n">
         <v>0</v>
@@ -12431,10 +12431,10 @@
         <v>0</v>
       </c>
       <c r="K183" s="8" t="n">
-        <v>947</v>
+        <v>796</v>
       </c>
       <c r="L183" s="8" t="n">
-        <v>633</v>
+        <v>460</v>
       </c>
       <c r="M183" s="8" t="n">
         <v>0</v>
@@ -12449,19 +12449,19 @@
         <v>0</v>
       </c>
       <c r="Q183" s="8" t="n">
-        <v>3411</v>
+        <v>3382</v>
       </c>
       <c r="R183" s="8" t="n">
-        <v>6260</v>
+        <v>4693</v>
       </c>
       <c r="S183" s="8" t="n">
-        <v>7304</v>
+        <v>6992</v>
       </c>
       <c r="T183" s="8" t="n">
-        <v>9241</v>
+        <v>6754</v>
       </c>
       <c r="U183" s="9" t="n">
-        <v>26216</v>
+        <v>21820</v>
       </c>
     </row>
     <row r="184">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="B184" s="7" t="inlineStr">
         <is>
-          <t>2023 Ç3</t>
+          <t>2023 Ç2</t>
         </is>
       </c>
       <c r="C184" s="8" t="n">
@@ -12482,16 +12482,16 @@
         <v>0</v>
       </c>
       <c r="E184" s="8" t="n">
-        <v>2142</v>
+        <v>2464</v>
       </c>
       <c r="F184" s="8" t="n">
-        <v>6026</v>
+        <v>5627</v>
       </c>
       <c r="G184" s="8" t="n">
-        <v>7700</v>
+        <v>7304</v>
       </c>
       <c r="H184" s="8" t="n">
-        <v>9637</v>
+        <v>9241</v>
       </c>
       <c r="I184" s="8" t="n">
         <v>0</v>
@@ -12500,10 +12500,10 @@
         <v>0</v>
       </c>
       <c r="K184" s="8" t="n">
-        <v>372</v>
+        <v>947</v>
       </c>
       <c r="L184" s="8" t="n">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="M184" s="8" t="n">
         <v>0</v>
@@ -12518,19 +12518,19 @@
         <v>0</v>
       </c>
       <c r="Q184" s="8" t="n">
-        <v>2514</v>
+        <v>3411</v>
       </c>
       <c r="R184" s="8" t="n">
-        <v>6662</v>
+        <v>6260</v>
       </c>
       <c r="S184" s="8" t="n">
-        <v>7700</v>
+        <v>7304</v>
       </c>
       <c r="T184" s="8" t="n">
-        <v>9637</v>
+        <v>9241</v>
       </c>
       <c r="U184" s="9" t="n">
-        <v>26513</v>
+        <v>26216</v>
       </c>
     </row>
     <row r="185">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="B185" s="7" t="inlineStr">
         <is>
-          <t>2024 Ç1</t>
+          <t>2023 Ç3</t>
         </is>
       </c>
       <c r="C185" s="8" t="n">
@@ -12551,28 +12551,28 @@
         <v>0</v>
       </c>
       <c r="E185" s="8" t="n">
-        <v>11611</v>
+        <v>2142</v>
       </c>
       <c r="F185" s="8" t="n">
-        <v>5006</v>
+        <v>6026</v>
       </c>
       <c r="G185" s="8" t="n">
-        <v>9950</v>
+        <v>7700</v>
       </c>
       <c r="H185" s="8" t="n">
-        <v>14270</v>
+        <v>9637</v>
       </c>
       <c r="I185" s="8" t="n">
-        <v>1384</v>
+        <v>0</v>
       </c>
       <c r="J185" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K185" s="8" t="n">
-        <v>844</v>
+        <v>372</v>
       </c>
       <c r="L185" s="8" t="n">
-        <v>892</v>
+        <v>635</v>
       </c>
       <c r="M185" s="8" t="n">
         <v>0</v>
@@ -12581,25 +12581,25 @@
         <v>0</v>
       </c>
       <c r="O185" s="8" t="n">
-        <v>1384</v>
+        <v>0</v>
       </c>
       <c r="P185" s="8" t="n">
         <v>0</v>
       </c>
       <c r="Q185" s="8" t="n">
-        <v>12456</v>
+        <v>2514</v>
       </c>
       <c r="R185" s="8" t="n">
-        <v>5897</v>
+        <v>6662</v>
       </c>
       <c r="S185" s="8" t="n">
-        <v>9950</v>
+        <v>7700</v>
       </c>
       <c r="T185" s="8" t="n">
-        <v>14270</v>
+        <v>9637</v>
       </c>
       <c r="U185" s="9" t="n">
-        <v>43956</v>
+        <v>26513</v>
       </c>
     </row>
     <row r="186">
@@ -12610,38 +12610,38 @@
       </c>
       <c r="B186" s="7" t="inlineStr">
         <is>
-          <t>2024 Ç2</t>
+          <t>2024 Ç1</t>
         </is>
       </c>
       <c r="C186" s="8" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D186" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E186" s="8" t="n">
-        <v>6972</v>
+        <v>11611</v>
       </c>
       <c r="F186" s="8" t="n">
-        <v>5705</v>
+        <v>5006</v>
       </c>
       <c r="G186" s="8" t="n">
-        <v>10867</v>
+        <v>9950</v>
       </c>
       <c r="H186" s="8" t="n">
-        <v>13351</v>
+        <v>14270</v>
       </c>
       <c r="I186" s="8" t="n">
-        <v>384</v>
+        <v>1384</v>
       </c>
       <c r="J186" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K186" s="8" t="n">
-        <v>590</v>
+        <v>844</v>
       </c>
       <c r="L186" s="8" t="n">
-        <v>832</v>
+        <v>892</v>
       </c>
       <c r="M186" s="8" t="n">
         <v>0</v>
@@ -12650,25 +12650,25 @@
         <v>0</v>
       </c>
       <c r="O186" s="8" t="n">
-        <v>411</v>
+        <v>1384</v>
       </c>
       <c r="P186" s="8" t="n">
         <v>0</v>
       </c>
       <c r="Q186" s="8" t="n">
-        <v>7562</v>
+        <v>12456</v>
       </c>
       <c r="R186" s="8" t="n">
-        <v>6536</v>
+        <v>5897</v>
       </c>
       <c r="S186" s="8" t="n">
-        <v>10867</v>
+        <v>9950</v>
       </c>
       <c r="T186" s="8" t="n">
-        <v>13351</v>
+        <v>14270</v>
       </c>
       <c r="U186" s="9" t="n">
-        <v>38728</v>
+        <v>43956</v>
       </c>
     </row>
     <row r="187">
@@ -12679,38 +12679,38 @@
       </c>
       <c r="B187" s="7" t="inlineStr">
         <is>
-          <t>2024 Ç3</t>
+          <t>2024 Ç2</t>
         </is>
       </c>
       <c r="C187" s="8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D187" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E187" s="8" t="n">
-        <v>11611</v>
+        <v>6972</v>
       </c>
       <c r="F187" s="8" t="n">
-        <v>5006</v>
+        <v>5705</v>
       </c>
       <c r="G187" s="8" t="n">
-        <v>9950</v>
+        <v>10867</v>
       </c>
       <c r="H187" s="8" t="n">
-        <v>14270</v>
+        <v>13351</v>
       </c>
       <c r="I187" s="8" t="n">
-        <v>1384</v>
+        <v>384</v>
       </c>
       <c r="J187" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K187" s="8" t="n">
-        <v>844</v>
+        <v>590</v>
       </c>
       <c r="L187" s="8" t="n">
-        <v>892</v>
+        <v>832</v>
       </c>
       <c r="M187" s="8" t="n">
         <v>0</v>
@@ -12719,25 +12719,25 @@
         <v>0</v>
       </c>
       <c r="O187" s="8" t="n">
-        <v>1384</v>
+        <v>411</v>
       </c>
       <c r="P187" s="8" t="n">
         <v>0</v>
       </c>
       <c r="Q187" s="8" t="n">
-        <v>12456</v>
+        <v>7562</v>
       </c>
       <c r="R187" s="8" t="n">
-        <v>5897</v>
+        <v>6536</v>
       </c>
       <c r="S187" s="8" t="n">
-        <v>9950</v>
+        <v>10867</v>
       </c>
       <c r="T187" s="8" t="n">
-        <v>14270</v>
+        <v>13351</v>
       </c>
       <c r="U187" s="9" t="n">
-        <v>43956</v>
+        <v>38728</v>
       </c>
     </row>
     <row r="188">
@@ -12748,7 +12748,7 @@
       </c>
       <c r="B188" s="7" t="inlineStr">
         <is>
-          <t>2024 Ç4</t>
+          <t>2024 Ç3</t>
         </is>
       </c>
       <c r="C188" s="8" t="n">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="B189" s="7" t="inlineStr">
         <is>
-          <t>2025 Ç1</t>
+          <t>2024 Ç4</t>
         </is>
       </c>
       <c r="C189" s="8" t="n">
@@ -12827,28 +12827,28 @@
         <v>0</v>
       </c>
       <c r="E189" s="8" t="n">
-        <v>15636</v>
+        <v>11611</v>
       </c>
       <c r="F189" s="8" t="n">
-        <v>5455</v>
+        <v>5006</v>
       </c>
       <c r="G189" s="8" t="n">
-        <v>10672</v>
+        <v>9950</v>
       </c>
       <c r="H189" s="8" t="n">
-        <v>15224</v>
+        <v>14270</v>
       </c>
       <c r="I189" s="8" t="n">
-        <v>1492</v>
+        <v>1384</v>
       </c>
       <c r="J189" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K189" s="8" t="n">
-        <v>600</v>
+        <v>844</v>
       </c>
       <c r="L189" s="8" t="n">
-        <v>997</v>
+        <v>892</v>
       </c>
       <c r="M189" s="8" t="n">
         <v>0</v>
@@ -12857,25 +12857,25 @@
         <v>0</v>
       </c>
       <c r="O189" s="8" t="n">
-        <v>1492</v>
+        <v>1384</v>
       </c>
       <c r="P189" s="8" t="n">
         <v>0</v>
       </c>
       <c r="Q189" s="8" t="n">
-        <v>16236</v>
+        <v>12456</v>
       </c>
       <c r="R189" s="8" t="n">
-        <v>6452</v>
+        <v>5897</v>
       </c>
       <c r="S189" s="8" t="n">
-        <v>10672</v>
+        <v>9950</v>
       </c>
       <c r="T189" s="8" t="n">
-        <v>15224</v>
+        <v>14270</v>
       </c>
       <c r="U189" s="9" t="n">
-        <v>50076</v>
+        <v>43956</v>
       </c>
     </row>
     <row r="190">
@@ -12886,7 +12886,7 @@
       </c>
       <c r="B190" s="7" t="inlineStr">
         <is>
-          <t>2025 Ç2</t>
+          <t>2025 Ç1</t>
         </is>
       </c>
       <c r="C190" s="8" t="n">
@@ -12896,28 +12896,28 @@
         <v>0</v>
       </c>
       <c r="E190" s="8" t="n">
-        <v>17361</v>
+        <v>15636</v>
       </c>
       <c r="F190" s="8" t="n">
-        <v>5986</v>
+        <v>5455</v>
       </c>
       <c r="G190" s="8" t="n">
-        <v>8524</v>
+        <v>10672</v>
       </c>
       <c r="H190" s="8" t="n">
-        <v>16295</v>
+        <v>15224</v>
       </c>
       <c r="I190" s="8" t="n">
-        <v>1612</v>
+        <v>1492</v>
       </c>
       <c r="J190" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K190" s="8" t="n">
-        <v>507</v>
+        <v>600</v>
       </c>
       <c r="L190" s="8" t="n">
-        <v>1162</v>
+        <v>997</v>
       </c>
       <c r="M190" s="8" t="n">
         <v>0</v>
@@ -12926,25 +12926,25 @@
         <v>0</v>
       </c>
       <c r="O190" s="8" t="n">
-        <v>1612</v>
+        <v>1492</v>
       </c>
       <c r="P190" s="8" t="n">
         <v>0</v>
       </c>
       <c r="Q190" s="8" t="n">
-        <v>17868</v>
+        <v>16236</v>
       </c>
       <c r="R190" s="8" t="n">
-        <v>7149</v>
+        <v>6452</v>
       </c>
       <c r="S190" s="8" t="n">
-        <v>8524</v>
+        <v>10672</v>
       </c>
       <c r="T190" s="8" t="n">
-        <v>16295</v>
+        <v>15224</v>
       </c>
       <c r="U190" s="9" t="n">
-        <v>51448</v>
+        <v>50076</v>
       </c>
     </row>
     <row r="191">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="B191" s="7" t="inlineStr">
         <is>
-          <t>2025 Ç3</t>
+          <t>2025 Ç2</t>
         </is>
       </c>
       <c r="C191" s="8" t="n">
@@ -12965,25 +12965,29 @@
         <v>0</v>
       </c>
       <c r="E191" s="8" t="n">
-        <v>18621</v>
+        <v>17361</v>
       </c>
       <c r="F191" s="8" t="n">
-        <v>6274</v>
+        <v>5986</v>
       </c>
       <c r="G191" s="8" t="n">
-        <v>9115</v>
+        <v>8524</v>
       </c>
       <c r="H191" s="8" t="n">
-        <v>16816</v>
+        <v>16295</v>
       </c>
       <c r="I191" s="8" t="n">
-        <v>1590</v>
+        <v>1612</v>
       </c>
       <c r="J191" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="K191" s="8" t="n"/>
-      <c r="L191" s="8" t="n"/>
+      <c r="K191" s="8" t="n">
+        <v>507</v>
+      </c>
+      <c r="L191" s="8" t="n">
+        <v>1162</v>
+      </c>
       <c r="M191" s="8" t="n">
         <v>0</v>
       </c>
@@ -12991,21 +12995,25 @@
         <v>0</v>
       </c>
       <c r="O191" s="8" t="n">
-        <v>1590</v>
+        <v>1612</v>
       </c>
       <c r="P191" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q191" s="8" t="n"/>
-      <c r="R191" s="8" t="n"/>
+      <c r="Q191" s="8" t="n">
+        <v>17868</v>
+      </c>
+      <c r="R191" s="8" t="n">
+        <v>7149</v>
+      </c>
       <c r="S191" s="8" t="n">
-        <v>9115</v>
+        <v>8524</v>
       </c>
       <c r="T191" s="8" t="n">
-        <v>16816</v>
+        <v>16295</v>
       </c>
       <c r="U191" s="9" t="n">
-        <v>27522</v>
+        <v>51448</v>
       </c>
     </row>
     <row r="192">
@@ -13016,7 +13024,7 @@
       </c>
       <c r="B192" s="7" t="inlineStr">
         <is>
-          <t>2025 Ç4</t>
+          <t>2025 Ç3</t>
         </is>
       </c>
       <c r="C192" s="8" t="n">
@@ -13026,29 +13034,25 @@
         <v>0</v>
       </c>
       <c r="E192" s="8" t="n">
-        <v>18295</v>
+        <v>18621</v>
       </c>
       <c r="F192" s="8" t="n">
-        <v>6496</v>
+        <v>6274</v>
       </c>
       <c r="G192" s="8" t="n">
-        <v>9865</v>
+        <v>9115</v>
       </c>
       <c r="H192" s="8" t="n">
-        <v>17516</v>
+        <v>16816</v>
       </c>
       <c r="I192" s="8" t="n">
-        <v>2890</v>
+        <v>1590</v>
       </c>
       <c r="J192" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="K192" s="8" t="n">
-        <v>708</v>
-      </c>
-      <c r="L192" s="8" t="n">
-        <v>1212</v>
-      </c>
+      <c r="K192" s="8" t="n"/>
+      <c r="L192" s="8" t="n"/>
       <c r="M192" s="8" t="n">
         <v>0</v>
       </c>
@@ -13056,25 +13060,21 @@
         <v>0</v>
       </c>
       <c r="O192" s="8" t="n">
-        <v>2890</v>
+        <v>1590</v>
       </c>
       <c r="P192" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" s="8" t="n">
-        <v>19004</v>
-      </c>
-      <c r="R192" s="8" t="n">
-        <v>7708</v>
-      </c>
+      <c r="Q192" s="8" t="n"/>
+      <c r="R192" s="8" t="n"/>
       <c r="S192" s="8" t="n">
-        <v>9865</v>
+        <v>9115</v>
       </c>
       <c r="T192" s="8" t="n">
-        <v>17516</v>
+        <v>16816</v>
       </c>
       <c r="U192" s="9" t="n">
-        <v>56981</v>
+        <v>27522</v>
       </c>
     </row>
     <row r="193">
@@ -13085,122 +13085,122 @@
       </c>
       <c r="B193" s="7" t="inlineStr">
         <is>
+          <t>2025 Ç4</t>
+        </is>
+      </c>
+      <c r="C193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" s="8" t="n">
+        <v>18295</v>
+      </c>
+      <c r="F193" s="8" t="n">
+        <v>6496</v>
+      </c>
+      <c r="G193" s="8" t="n">
+        <v>9865</v>
+      </c>
+      <c r="H193" s="8" t="n">
+        <v>17516</v>
+      </c>
+      <c r="I193" s="8" t="n">
+        <v>2890</v>
+      </c>
+      <c r="J193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" s="8" t="n">
+        <v>708</v>
+      </c>
+      <c r="L193" s="8" t="n">
+        <v>1212</v>
+      </c>
+      <c r="M193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" s="8" t="n">
+        <v>2890</v>
+      </c>
+      <c r="P193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q193" s="8" t="n">
+        <v>19004</v>
+      </c>
+      <c r="R193" s="8" t="n">
+        <v>7708</v>
+      </c>
+      <c r="S193" s="8" t="n">
+        <v>9865</v>
+      </c>
+      <c r="T193" s="8" t="n">
+        <v>17516</v>
+      </c>
+      <c r="U193" s="9" t="n">
+        <v>56981</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t>TSKB</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="inlineStr">
+        <is>
           <t>2026 Ç1</t>
         </is>
       </c>
-      <c r="C193" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D193" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E193" s="8" t="n"/>
-      <c r="F193" s="8" t="n"/>
-      <c r="G193" s="8" t="n">
+      <c r="C194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" s="8" t="n"/>
+      <c r="F194" s="8" t="n"/>
+      <c r="G194" s="8" t="n">
         <v>10458</v>
       </c>
-      <c r="H193" s="8" t="n">
+      <c r="H194" s="8" t="n">
         <v>17926</v>
       </c>
-      <c r="I193" s="8" t="n">
+      <c r="I194" s="8" t="n">
         <v>3135</v>
       </c>
-      <c r="J193" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K193" s="8" t="n"/>
-      <c r="L193" s="8" t="n"/>
-      <c r="M193" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N193" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O193" s="8" t="n">
+      <c r="J194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" s="8" t="n"/>
+      <c r="L194" s="8" t="n"/>
+      <c r="M194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" s="8" t="n">
         <v>3135</v>
       </c>
-      <c r="P193" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q193" s="8" t="n"/>
-      <c r="R193" s="8" t="n"/>
-      <c r="S193" s="8" t="n">
+      <c r="P194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q194" s="8" t="n"/>
+      <c r="R194" s="8" t="n"/>
+      <c r="S194" s="8" t="n">
         <v>10458</v>
       </c>
-      <c r="T193" s="8" t="n">
+      <c r="T194" s="8" t="n">
         <v>17926</v>
       </c>
-      <c r="U193" s="9" t="n">
+      <c r="U194" s="9" t="n">
         <v>31519</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="10" t="inlineStr">
-        <is>
-          <t>Fiba</t>
-        </is>
-      </c>
-      <c r="B194" s="11" t="inlineStr">
-        <is>
-          <t>2021 Ç1</t>
-        </is>
-      </c>
-      <c r="C194" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D194" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E194" s="12" t="n">
-        <v>483</v>
-      </c>
-      <c r="F194" s="12" t="n">
-        <v>558</v>
-      </c>
-      <c r="G194" s="12" t="n">
-        <v>191</v>
-      </c>
-      <c r="H194" s="12" t="n">
-        <v>3015</v>
-      </c>
-      <c r="I194" s="12" t="n">
-        <v>117</v>
-      </c>
-      <c r="J194" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="K194" s="12" t="n">
-        <v>397</v>
-      </c>
-      <c r="L194" s="12" t="n">
-        <v>639</v>
-      </c>
-      <c r="M194" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N194" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="O194" s="12" t="n">
-        <v>117</v>
-      </c>
-      <c r="P194" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q194" s="12" t="n">
-        <v>880</v>
-      </c>
-      <c r="R194" s="12" t="n">
-        <v>1198</v>
-      </c>
-      <c r="S194" s="12" t="n">
-        <v>191</v>
-      </c>
-      <c r="T194" s="12" t="n">
-        <v>3040</v>
-      </c>
-      <c r="U194" s="13" t="n">
-        <v>5501</v>
       </c>
     </row>
     <row r="195">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>2021 Ç2</t>
+          <t>2021 Ç1</t>
         </is>
       </c>
       <c r="C195" s="12" t="n">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>2021 Ç3</t>
+          <t>2021 Ç2</t>
         </is>
       </c>
       <c r="C196" s="12" t="n">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>2021 Ç4</t>
+          <t>2021 Ç3</t>
         </is>
       </c>
       <c r="C197" s="12" t="n">
@@ -13418,65 +13418,65 @@
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç1</t>
+          <t>2021 Ç4</t>
         </is>
       </c>
       <c r="C198" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D198" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E198" s="12" t="n">
-        <v>1104</v>
+        <v>483</v>
       </c>
       <c r="F198" s="12" t="n">
-        <v>1056</v>
+        <v>558</v>
       </c>
       <c r="G198" s="12" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H198" s="12" t="n">
-        <v>3714</v>
+        <v>3015</v>
       </c>
       <c r="I198" s="12" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="J198" s="12" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K198" s="12" t="n">
-        <v>712</v>
+        <v>397</v>
       </c>
       <c r="L198" s="12" t="n">
-        <v>681</v>
+        <v>639</v>
       </c>
       <c r="M198" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N198" s="12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="O198" s="12" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="P198" s="12" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="Q198" s="12" t="n">
-        <v>1816</v>
+        <v>880</v>
       </c>
       <c r="R198" s="12" t="n">
-        <v>1737</v>
+        <v>1198</v>
       </c>
       <c r="S198" s="12" t="n">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="T198" s="12" t="n">
-        <v>3742</v>
+        <v>3040</v>
       </c>
       <c r="U198" s="13" t="n">
-        <v>7644</v>
+        <v>5501</v>
       </c>
     </row>
     <row r="199">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç2</t>
+          <t>2022 Ç1</t>
         </is>
       </c>
       <c r="C199" s="12" t="n">
@@ -13497,55 +13497,55 @@
         <v>3</v>
       </c>
       <c r="E199" s="12" t="n">
-        <v>1263</v>
+        <v>1104</v>
       </c>
       <c r="F199" s="12" t="n">
-        <v>1097</v>
+        <v>1056</v>
       </c>
       <c r="G199" s="12" t="n">
-        <v>1268</v>
+        <v>193</v>
       </c>
       <c r="H199" s="12" t="n">
-        <v>4140</v>
+        <v>3714</v>
       </c>
       <c r="I199" s="12" t="n">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="J199" s="12" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="K199" s="12" t="n">
-        <v>941</v>
+        <v>712</v>
       </c>
       <c r="L199" s="12" t="n">
-        <v>626</v>
+        <v>681</v>
       </c>
       <c r="M199" s="12" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="N199" s="12" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="O199" s="12" t="n">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="P199" s="12" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="Q199" s="12" t="n">
-        <v>2204</v>
+        <v>1816</v>
       </c>
       <c r="R199" s="12" t="n">
-        <v>1722</v>
+        <v>1737</v>
       </c>
       <c r="S199" s="12" t="n">
-        <v>1353</v>
+        <v>233</v>
       </c>
       <c r="T199" s="12" t="n">
-        <v>4171</v>
+        <v>3742</v>
       </c>
       <c r="U199" s="13" t="n">
-        <v>9609</v>
+        <v>7644</v>
       </c>
     </row>
     <row r="200">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç3</t>
+          <t>2022 Ç2</t>
         </is>
       </c>
       <c r="C200" s="12" t="n">
@@ -13566,55 +13566,55 @@
         <v>3</v>
       </c>
       <c r="E200" s="12" t="n">
-        <v>2049</v>
+        <v>1263</v>
       </c>
       <c r="F200" s="12" t="n">
-        <v>1247</v>
+        <v>1097</v>
       </c>
       <c r="G200" s="12" t="n">
-        <v>1822</v>
+        <v>1268</v>
       </c>
       <c r="H200" s="12" t="n">
-        <v>4509</v>
+        <v>4140</v>
       </c>
       <c r="I200" s="12" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="J200" s="12" t="n">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="K200" s="12" t="n">
-        <v>1043</v>
+        <v>941</v>
       </c>
       <c r="L200" s="12" t="n">
-        <v>501</v>
+        <v>626</v>
       </c>
       <c r="M200" s="12" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="N200" s="12" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O200" s="12" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="P200" s="12" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="Q200" s="12" t="n">
-        <v>3092</v>
+        <v>2204</v>
       </c>
       <c r="R200" s="12" t="n">
-        <v>1749</v>
+        <v>1722</v>
       </c>
       <c r="S200" s="12" t="n">
-        <v>1962</v>
+        <v>1353</v>
       </c>
       <c r="T200" s="12" t="n">
-        <v>4545</v>
+        <v>4171</v>
       </c>
       <c r="U200" s="13" t="n">
-        <v>11565</v>
+        <v>9609</v>
       </c>
     </row>
     <row r="201">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç4</t>
+          <t>2022 Ç3</t>
         </is>
       </c>
       <c r="C201" s="12" t="n">
@@ -13635,55 +13635,55 @@
         <v>3</v>
       </c>
       <c r="E201" s="12" t="n">
-        <v>2533</v>
+        <v>2049</v>
       </c>
       <c r="F201" s="12" t="n">
-        <v>1397</v>
+        <v>1247</v>
       </c>
       <c r="G201" s="12" t="n">
-        <v>2141</v>
+        <v>1822</v>
       </c>
       <c r="H201" s="12" t="n">
-        <v>4652</v>
+        <v>4509</v>
       </c>
       <c r="I201" s="12" t="n">
-        <v>201</v>
+        <v>132</v>
       </c>
       <c r="J201" s="12" t="n">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="K201" s="12" t="n">
-        <v>870</v>
+        <v>1043</v>
       </c>
       <c r="L201" s="12" t="n">
-        <v>341</v>
+        <v>501</v>
       </c>
       <c r="M201" s="12" t="n">
-        <v>239</v>
+        <v>140</v>
       </c>
       <c r="N201" s="12" t="n">
         <v>36</v>
       </c>
       <c r="O201" s="12" t="n">
-        <v>201</v>
+        <v>132</v>
       </c>
       <c r="P201" s="12" t="n">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="Q201" s="12" t="n">
-        <v>3403</v>
+        <v>3092</v>
       </c>
       <c r="R201" s="12" t="n">
-        <v>1738</v>
+        <v>1749</v>
       </c>
       <c r="S201" s="12" t="n">
-        <v>2380</v>
+        <v>1962</v>
       </c>
       <c r="T201" s="12" t="n">
-        <v>4688</v>
+        <v>4545</v>
       </c>
       <c r="U201" s="13" t="n">
-        <v>12538</v>
+        <v>11565</v>
       </c>
     </row>
     <row r="202">
@@ -13694,65 +13694,65 @@
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç1</t>
+          <t>2022 Ç4</t>
         </is>
       </c>
       <c r="C202" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D202" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E202" s="12" t="n">
-        <v>5430</v>
+        <v>2533</v>
       </c>
       <c r="F202" s="12" t="n">
-        <v>2204</v>
+        <v>1397</v>
       </c>
       <c r="G202" s="12" t="n">
-        <v>2198</v>
+        <v>2141</v>
       </c>
       <c r="H202" s="12" t="n">
-        <v>6585</v>
+        <v>4652</v>
       </c>
       <c r="I202" s="12" t="n">
-        <v>3178</v>
+        <v>201</v>
       </c>
       <c r="J202" s="12" t="n">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="K202" s="12" t="n">
-        <v>1447</v>
+        <v>870</v>
       </c>
       <c r="L202" s="12" t="n">
-        <v>76</v>
+        <v>341</v>
       </c>
       <c r="M202" s="12" t="n">
-        <v>468</v>
+        <v>239</v>
       </c>
       <c r="N202" s="12" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="O202" s="12" t="n">
-        <v>3178</v>
+        <v>201</v>
       </c>
       <c r="P202" s="12" t="n">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="Q202" s="12" t="n">
-        <v>6877</v>
+        <v>3403</v>
       </c>
       <c r="R202" s="12" t="n">
-        <v>2280</v>
+        <v>1738</v>
       </c>
       <c r="S202" s="12" t="n">
-        <v>2666</v>
+        <v>2380</v>
       </c>
       <c r="T202" s="12" t="n">
-        <v>6643</v>
+        <v>4688</v>
       </c>
       <c r="U202" s="13" t="n">
-        <v>21782</v>
+        <v>12538</v>
       </c>
     </row>
     <row r="203">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç2</t>
+          <t>2023 Ç1</t>
         </is>
       </c>
       <c r="C203" s="12" t="n">
@@ -13832,63 +13832,65 @@
       </c>
       <c r="B204" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç3</t>
-        </is>
-      </c>
-      <c r="C204" s="12" t="n"/>
+          <t>2023 Ç2</t>
+        </is>
+      </c>
+      <c r="C204" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="D204" s="12" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E204" s="12" t="n">
-        <v>3725</v>
+        <v>5430</v>
       </c>
       <c r="F204" s="12" t="n">
-        <v>2869</v>
+        <v>2204</v>
       </c>
       <c r="G204" s="12" t="n">
-        <v>2814</v>
+        <v>2198</v>
       </c>
       <c r="H204" s="12" t="n">
-        <v>6742</v>
+        <v>6585</v>
       </c>
       <c r="I204" s="12" t="n">
-        <v>304</v>
+        <v>3178</v>
       </c>
       <c r="J204" s="12" t="n">
-        <v>-27</v>
+        <v>136</v>
       </c>
       <c r="K204" s="12" t="n">
-        <v>1477</v>
+        <v>1447</v>
       </c>
       <c r="L204" s="12" t="n">
-        <v>530</v>
+        <v>76</v>
       </c>
       <c r="M204" s="12" t="n">
-        <v>242</v>
+        <v>468</v>
       </c>
       <c r="N204" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O204" s="12" t="n">
-        <v>304</v>
+        <v>3178</v>
       </c>
       <c r="P204" s="12" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="Q204" s="12" t="n">
-        <v>5201</v>
+        <v>6877</v>
       </c>
       <c r="R204" s="12" t="n">
-        <v>3399</v>
+        <v>2280</v>
       </c>
       <c r="S204" s="12" t="n">
-        <v>3056</v>
+        <v>2666</v>
       </c>
       <c r="T204" s="12" t="n">
-        <v>6797</v>
+        <v>6643</v>
       </c>
       <c r="U204" s="13" t="n">
-        <v>18895</v>
+        <v>21782</v>
       </c>
     </row>
     <row r="205">
@@ -13899,65 +13901,63 @@
       </c>
       <c r="B205" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç4</t>
-        </is>
-      </c>
-      <c r="C205" s="12" t="n">
-        <v>0</v>
-      </c>
+          <t>2023 Ç3</t>
+        </is>
+      </c>
+      <c r="C205" s="12" t="n"/>
       <c r="D205" s="12" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="E205" s="12" t="n">
-        <v>5430</v>
+        <v>3725</v>
       </c>
       <c r="F205" s="12" t="n">
-        <v>2204</v>
+        <v>2869</v>
       </c>
       <c r="G205" s="12" t="n">
-        <v>2198</v>
+        <v>2814</v>
       </c>
       <c r="H205" s="12" t="n">
-        <v>6585</v>
+        <v>6742</v>
       </c>
       <c r="I205" s="12" t="n">
-        <v>3178</v>
+        <v>304</v>
       </c>
       <c r="J205" s="12" t="n">
-        <v>136</v>
+        <v>-27</v>
       </c>
       <c r="K205" s="12" t="n">
-        <v>1447</v>
+        <v>1477</v>
       </c>
       <c r="L205" s="12" t="n">
-        <v>76</v>
+        <v>530</v>
       </c>
       <c r="M205" s="12" t="n">
-        <v>468</v>
+        <v>242</v>
       </c>
       <c r="N205" s="12" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="O205" s="12" t="n">
-        <v>3178</v>
+        <v>304</v>
       </c>
       <c r="P205" s="12" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Q205" s="12" t="n">
-        <v>6877</v>
+        <v>5201</v>
       </c>
       <c r="R205" s="12" t="n">
-        <v>2280</v>
+        <v>3399</v>
       </c>
       <c r="S205" s="12" t="n">
-        <v>2666</v>
+        <v>3056</v>
       </c>
       <c r="T205" s="12" t="n">
-        <v>6643</v>
+        <v>6797</v>
       </c>
       <c r="U205" s="13" t="n">
-        <v>21782</v>
+        <v>18895</v>
       </c>
     </row>
     <row r="206">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="B206" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç1</t>
+          <t>2023 Ç4</t>
         </is>
       </c>
       <c r="C206" s="12" t="n">
@@ -13978,55 +13978,55 @@
         <v>0</v>
       </c>
       <c r="E206" s="12" t="n">
-        <v>7843</v>
+        <v>5430</v>
       </c>
       <c r="F206" s="12" t="n">
-        <v>2964</v>
+        <v>2204</v>
       </c>
       <c r="G206" s="12" t="n">
         <v>2198</v>
       </c>
       <c r="H206" s="12" t="n">
-        <v>6770</v>
+        <v>6585</v>
       </c>
       <c r="I206" s="12" t="n">
-        <v>664</v>
+        <v>3178</v>
       </c>
       <c r="J206" s="12" t="n">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="K206" s="12" t="n">
-        <v>3776</v>
+        <v>1447</v>
       </c>
       <c r="L206" s="12" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="M206" s="12" t="n">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="N206" s="12" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="O206" s="12" t="n">
-        <v>664</v>
+        <v>3178</v>
       </c>
       <c r="P206" s="12" t="n">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="Q206" s="12" t="n">
-        <v>11619</v>
+        <v>6877</v>
       </c>
       <c r="R206" s="12" t="n">
-        <v>3054</v>
+        <v>2280</v>
       </c>
       <c r="S206" s="12" t="n">
-        <v>2682</v>
+        <v>2666</v>
       </c>
       <c r="T206" s="12" t="n">
-        <v>6835</v>
+        <v>6643</v>
       </c>
       <c r="U206" s="13" t="n">
-        <v>24918</v>
+        <v>21782</v>
       </c>
     </row>
     <row r="207">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="B207" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç2</t>
+          <t>2024 Ç1</t>
         </is>
       </c>
       <c r="C207" s="12" t="n">
@@ -14047,55 +14047,55 @@
         <v>0</v>
       </c>
       <c r="E207" s="12" t="n">
-        <v>7813</v>
+        <v>7843</v>
       </c>
       <c r="F207" s="12" t="n">
-        <v>3653</v>
+        <v>2964</v>
       </c>
       <c r="G207" s="12" t="n">
-        <v>2276</v>
+        <v>2198</v>
       </c>
       <c r="H207" s="12" t="n">
-        <v>6503</v>
+        <v>6770</v>
       </c>
       <c r="I207" s="12" t="n">
-        <v>1102</v>
+        <v>664</v>
       </c>
       <c r="J207" s="12" t="n">
-        <v>192</v>
+        <v>66</v>
       </c>
       <c r="K207" s="12" t="n">
-        <v>5305</v>
+        <v>3776</v>
       </c>
       <c r="L207" s="12" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="M207" s="12" t="n">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="N207" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="O207" s="12" t="n">
+        <v>664</v>
+      </c>
+      <c r="P207" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="O207" s="12" t="n">
-        <v>1102</v>
-      </c>
-      <c r="P207" s="12" t="n">
-        <v>192</v>
-      </c>
       <c r="Q207" s="12" t="n">
-        <v>13118</v>
+        <v>11619</v>
       </c>
       <c r="R207" s="12" t="n">
-        <v>3753</v>
+        <v>3054</v>
       </c>
       <c r="S207" s="12" t="n">
-        <v>2755</v>
+        <v>2682</v>
       </c>
       <c r="T207" s="12" t="n">
-        <v>6568</v>
+        <v>6835</v>
       </c>
       <c r="U207" s="13" t="n">
-        <v>27488</v>
+        <v>24918</v>
       </c>
     </row>
     <row r="208">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="B208" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç3</t>
+          <t>2024 Ç2</t>
         </is>
       </c>
       <c r="C208" s="12" t="n">
@@ -14116,55 +14116,55 @@
         <v>0</v>
       </c>
       <c r="E208" s="12" t="n">
-        <v>8070</v>
+        <v>7813</v>
       </c>
       <c r="F208" s="12" t="n">
-        <v>4247</v>
+        <v>3653</v>
       </c>
       <c r="G208" s="12" t="n">
-        <v>2250</v>
+        <v>2276</v>
       </c>
       <c r="H208" s="12" t="n">
-        <v>6299</v>
+        <v>6503</v>
       </c>
       <c r="I208" s="12" t="n">
-        <v>865</v>
+        <v>1102</v>
       </c>
       <c r="J208" s="12" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="K208" s="12" t="n">
-        <v>8480</v>
+        <v>5305</v>
       </c>
       <c r="L208" s="12" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="M208" s="12" t="n">
-        <v>829</v>
+        <v>479</v>
       </c>
       <c r="N208" s="12" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O208" s="12" t="n">
-        <v>865</v>
+        <v>1102</v>
       </c>
       <c r="P208" s="12" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q208" s="12" t="n">
-        <v>16550</v>
+        <v>13118</v>
       </c>
       <c r="R208" s="12" t="n">
-        <v>4380</v>
+        <v>3753</v>
       </c>
       <c r="S208" s="12" t="n">
-        <v>3078</v>
+        <v>2755</v>
       </c>
       <c r="T208" s="12" t="n">
-        <v>6369</v>
+        <v>6568</v>
       </c>
       <c r="U208" s="13" t="n">
-        <v>31436</v>
+        <v>27488</v>
       </c>
     </row>
     <row r="209">
@@ -14175,65 +14175,65 @@
       </c>
       <c r="B209" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç4</t>
+          <t>2024 Ç3</t>
         </is>
       </c>
       <c r="C209" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="D209" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E209" s="12" t="n">
-        <v>8087</v>
+        <v>8070</v>
       </c>
       <c r="F209" s="12" t="n">
-        <v>6219</v>
+        <v>4247</v>
       </c>
       <c r="G209" s="12" t="n">
-        <v>1510</v>
+        <v>2250</v>
       </c>
       <c r="H209" s="12" t="n">
-        <v>4495</v>
+        <v>6299</v>
       </c>
       <c r="I209" s="12" t="n">
-        <v>1029</v>
+        <v>865</v>
       </c>
       <c r="J209" s="12" t="n">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="K209" s="12" t="n">
-        <v>15934</v>
+        <v>8480</v>
       </c>
       <c r="L209" s="12" t="n">
-        <v>390</v>
+        <v>133</v>
       </c>
       <c r="M209" s="12" t="n">
-        <v>880</v>
+        <v>829</v>
       </c>
       <c r="N209" s="12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="O209" s="12" t="n">
-        <v>1080</v>
+        <v>865</v>
       </c>
       <c r="P209" s="12" t="n">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="Q209" s="12" t="n">
-        <v>24020</v>
+        <v>16550</v>
       </c>
       <c r="R209" s="12" t="n">
-        <v>6609</v>
+        <v>4380</v>
       </c>
       <c r="S209" s="12" t="n">
-        <v>2390</v>
+        <v>3078</v>
       </c>
       <c r="T209" s="12" t="n">
-        <v>4495</v>
+        <v>6369</v>
       </c>
       <c r="U209" s="13" t="n">
-        <v>38807</v>
+        <v>31436</v>
       </c>
     </row>
     <row r="210">
@@ -14244,65 +14244,65 @@
       </c>
       <c r="B210" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç1</t>
+          <t>2024 Ç4</t>
         </is>
       </c>
       <c r="C210" s="12" t="n">
-        <v>235</v>
+        <v>51</v>
       </c>
       <c r="D210" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E210" s="12" t="n">
-        <v>8449</v>
+        <v>8087</v>
       </c>
       <c r="F210" s="12" t="n">
-        <v>6348</v>
+        <v>6219</v>
       </c>
       <c r="G210" s="12" t="n">
-        <v>1574</v>
+        <v>1510</v>
       </c>
       <c r="H210" s="12" t="n">
-        <v>4442</v>
+        <v>4495</v>
       </c>
       <c r="I210" s="12" t="n">
-        <v>1644</v>
+        <v>1029</v>
       </c>
       <c r="J210" s="12" t="n">
-        <v>350</v>
+        <v>212</v>
       </c>
       <c r="K210" s="12" t="n">
-        <v>21304</v>
+        <v>15934</v>
       </c>
       <c r="L210" s="12" t="n">
-        <v>511</v>
+        <v>390</v>
       </c>
       <c r="M210" s="12" t="n">
-        <v>1235</v>
+        <v>880</v>
       </c>
       <c r="N210" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O210" s="12" t="n">
-        <v>1879</v>
+        <v>1080</v>
       </c>
       <c r="P210" s="12" t="n">
-        <v>350</v>
+        <v>212</v>
       </c>
       <c r="Q210" s="12" t="n">
-        <v>29753</v>
+        <v>24020</v>
       </c>
       <c r="R210" s="12" t="n">
-        <v>6859</v>
+        <v>6609</v>
       </c>
       <c r="S210" s="12" t="n">
-        <v>2809</v>
+        <v>2390</v>
       </c>
       <c r="T210" s="12" t="n">
-        <v>4442</v>
+        <v>4495</v>
       </c>
       <c r="U210" s="13" t="n">
-        <v>46092</v>
+        <v>38807</v>
       </c>
     </row>
     <row r="211">
@@ -14313,65 +14313,65 @@
       </c>
       <c r="B211" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç2</t>
+          <t>2025 Ç1</t>
         </is>
       </c>
       <c r="C211" s="12" t="n">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="D211" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E211" s="12" t="n">
-        <v>8792</v>
+        <v>8449</v>
       </c>
       <c r="F211" s="12" t="n">
-        <v>6770</v>
+        <v>6348</v>
       </c>
       <c r="G211" s="12" t="n">
-        <v>1664</v>
+        <v>1574</v>
       </c>
       <c r="H211" s="12" t="n">
-        <v>4867</v>
+        <v>4442</v>
       </c>
       <c r="I211" s="12" t="n">
-        <v>1291</v>
+        <v>1644</v>
       </c>
       <c r="J211" s="12" t="n">
-        <v>157</v>
+        <v>350</v>
       </c>
       <c r="K211" s="12" t="n">
-        <v>25085</v>
+        <v>21304</v>
       </c>
       <c r="L211" s="12" t="n">
-        <v>541</v>
+        <v>511</v>
       </c>
       <c r="M211" s="12" t="n">
-        <v>1738</v>
+        <v>1235</v>
       </c>
       <c r="N211" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O211" s="12" t="n">
-        <v>1552</v>
+        <v>1879</v>
       </c>
       <c r="P211" s="12" t="n">
-        <v>157</v>
+        <v>350</v>
       </c>
       <c r="Q211" s="12" t="n">
-        <v>33877</v>
+        <v>29753</v>
       </c>
       <c r="R211" s="12" t="n">
-        <v>7312</v>
+        <v>6859</v>
       </c>
       <c r="S211" s="12" t="n">
-        <v>3401</v>
+        <v>2809</v>
       </c>
       <c r="T211" s="12" t="n">
-        <v>4867</v>
+        <v>4442</v>
       </c>
       <c r="U211" s="13" t="n">
-        <v>51165</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="212">
@@ -14382,65 +14382,65 @@
       </c>
       <c r="B212" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç4</t>
+          <t>2025 Ç2</t>
         </is>
       </c>
       <c r="C212" s="12" t="n">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="D212" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E212" s="12" t="n">
-        <v>9350</v>
+        <v>8792</v>
       </c>
       <c r="F212" s="12" t="n">
-        <v>6884</v>
+        <v>6770</v>
       </c>
       <c r="G212" s="12" t="n">
-        <v>1784</v>
+        <v>1664</v>
       </c>
       <c r="H212" s="12" t="n">
-        <v>4245</v>
+        <v>4867</v>
       </c>
       <c r="I212" s="12" t="n">
-        <v>1199</v>
+        <v>1291</v>
       </c>
       <c r="J212" s="12" t="n">
-        <v>358</v>
+        <v>157</v>
       </c>
       <c r="K212" s="12" t="n">
-        <v>24631</v>
+        <v>25085</v>
       </c>
       <c r="L212" s="12" t="n">
-        <v>599</v>
+        <v>541</v>
       </c>
       <c r="M212" s="12" t="n">
-        <v>2672</v>
+        <v>1738</v>
       </c>
       <c r="N212" s="12" t="n">
-        <v>1348</v>
+        <v>0</v>
       </c>
       <c r="O212" s="12" t="n">
-        <v>1471</v>
+        <v>1552</v>
       </c>
       <c r="P212" s="12" t="n">
-        <v>358</v>
+        <v>157</v>
       </c>
       <c r="Q212" s="12" t="n">
-        <v>33981</v>
+        <v>33877</v>
       </c>
       <c r="R212" s="12" t="n">
-        <v>7483</v>
+        <v>7312</v>
       </c>
       <c r="S212" s="12" t="n">
-        <v>4456</v>
+        <v>3401</v>
       </c>
       <c r="T212" s="12" t="n">
-        <v>5593</v>
+        <v>4867</v>
       </c>
       <c r="U212" s="13" t="n">
-        <v>53343</v>
+        <v>51165</v>
       </c>
     </row>
     <row r="213">
@@ -14451,63 +14451,65 @@
       </c>
       <c r="B213" s="11" t="inlineStr">
         <is>
-          <t>2026 Ç1</t>
-        </is>
-      </c>
-      <c r="C213" s="12" t="n"/>
+          <t>2025 Ç4</t>
+        </is>
+      </c>
+      <c r="C213" s="12" t="n">
+        <v>272</v>
+      </c>
       <c r="D213" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E213" s="12" t="n">
-        <v>8469</v>
+        <v>9350</v>
       </c>
       <c r="F213" s="12" t="n">
-        <v>9312</v>
+        <v>6884</v>
       </c>
       <c r="G213" s="12" t="n">
-        <v>1414</v>
+        <v>1784</v>
       </c>
       <c r="H213" s="12" t="n">
-        <v>2359</v>
+        <v>4245</v>
       </c>
       <c r="I213" s="12" t="n">
-        <v>1709</v>
+        <v>1199</v>
       </c>
       <c r="J213" s="12" t="n">
-        <v>274</v>
+        <v>358</v>
       </c>
       <c r="K213" s="12" t="n">
-        <v>24808</v>
+        <v>24631</v>
       </c>
       <c r="L213" s="12" t="n">
-        <v>565</v>
+        <v>599</v>
       </c>
       <c r="M213" s="12" t="n">
-        <v>3314</v>
+        <v>2672</v>
       </c>
       <c r="N213" s="12" t="n">
-        <v>1370</v>
+        <v>1348</v>
       </c>
       <c r="O213" s="12" t="n">
-        <v>1709</v>
+        <v>1471</v>
       </c>
       <c r="P213" s="12" t="n">
-        <v>320</v>
+        <v>358</v>
       </c>
       <c r="Q213" s="12" t="n">
-        <v>33277</v>
+        <v>33981</v>
       </c>
       <c r="R213" s="12" t="n">
-        <v>9876</v>
+        <v>7483</v>
       </c>
       <c r="S213" s="12" t="n">
-        <v>4728</v>
+        <v>4456</v>
       </c>
       <c r="T213" s="12" t="n">
-        <v>3729</v>
+        <v>5593</v>
       </c>
       <c r="U213" s="13" t="n">
-        <v>53640</v>
+        <v>53343</v>
       </c>
     </row>
     <row r="214">
@@ -14518,122 +14520,132 @@
       </c>
       <c r="B214" s="11" t="inlineStr">
         <is>
+          <t>2026 Ç1</t>
+        </is>
+      </c>
+      <c r="C214" s="12" t="n"/>
+      <c r="D214" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="E214" s="12" t="n">
+        <v>8469</v>
+      </c>
+      <c r="F214" s="12" t="n">
+        <v>9312</v>
+      </c>
+      <c r="G214" s="12" t="n">
+        <v>1414</v>
+      </c>
+      <c r="H214" s="12" t="n">
+        <v>2359</v>
+      </c>
+      <c r="I214" s="12" t="n">
+        <v>1709</v>
+      </c>
+      <c r="J214" s="12" t="n">
+        <v>274</v>
+      </c>
+      <c r="K214" s="12" t="n">
+        <v>24808</v>
+      </c>
+      <c r="L214" s="12" t="n">
+        <v>565</v>
+      </c>
+      <c r="M214" s="12" t="n">
+        <v>3314</v>
+      </c>
+      <c r="N214" s="12" t="n">
+        <v>1370</v>
+      </c>
+      <c r="O214" s="12" t="n">
+        <v>1709</v>
+      </c>
+      <c r="P214" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q214" s="12" t="n">
+        <v>33277</v>
+      </c>
+      <c r="R214" s="12" t="n">
+        <v>9876</v>
+      </c>
+      <c r="S214" s="12" t="n">
+        <v>4728</v>
+      </c>
+      <c r="T214" s="12" t="n">
+        <v>3729</v>
+      </c>
+      <c r="U214" s="13" t="n">
+        <v>53640</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="10" t="inlineStr">
+        <is>
+          <t>Fiba</t>
+        </is>
+      </c>
+      <c r="B215" s="11" t="inlineStr">
+        <is>
           <t>2026 Ç2</t>
         </is>
       </c>
-      <c r="C214" s="12" t="n">
+      <c r="C215" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="D214" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E214" s="12" t="n">
+      <c r="D215" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" s="12" t="n">
         <v>8986</v>
       </c>
-      <c r="F214" s="12" t="n">
+      <c r="F215" s="12" t="n">
         <v>9173</v>
       </c>
-      <c r="G214" s="12" t="n">
+      <c r="G215" s="12" t="n">
         <v>1438</v>
       </c>
-      <c r="H214" s="12" t="n">
+      <c r="H215" s="12" t="n">
         <v>2457</v>
       </c>
-      <c r="I214" s="12" t="n">
+      <c r="I215" s="12" t="n">
         <v>1881</v>
       </c>
-      <c r="J214" s="12" t="n">
+      <c r="J215" s="12" t="n">
         <v>344</v>
       </c>
-      <c r="K214" s="12" t="n">
+      <c r="K215" s="12" t="n">
         <v>26140</v>
       </c>
-      <c r="L214" s="12" t="n">
+      <c r="L215" s="12" t="n">
         <v>446</v>
       </c>
-      <c r="M214" s="12" t="n">
+      <c r="M215" s="12" t="n">
         <v>5334</v>
       </c>
-      <c r="N214" s="12" t="n">
+      <c r="N215" s="12" t="n">
         <v>1464</v>
       </c>
-      <c r="O214" s="12" t="n">
+      <c r="O215" s="12" t="n">
         <v>1901</v>
       </c>
-      <c r="P214" s="12" t="n">
+      <c r="P215" s="12" t="n">
         <v>344</v>
       </c>
-      <c r="Q214" s="12" t="n">
+      <c r="Q215" s="12" t="n">
         <v>35126</v>
       </c>
-      <c r="R214" s="12" t="n">
+      <c r="R215" s="12" t="n">
         <v>9619</v>
       </c>
-      <c r="S214" s="12" t="n">
+      <c r="S215" s="12" t="n">
         <v>6772</v>
       </c>
-      <c r="T214" s="12" t="n">
+      <c r="T215" s="12" t="n">
         <v>3921</v>
       </c>
-      <c r="U214" s="13" t="n">
+      <c r="U215" s="13" t="n">
         <v>57683</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="6" t="inlineStr">
-        <is>
-          <t>ING</t>
-        </is>
-      </c>
-      <c r="B215" s="7" t="inlineStr">
-        <is>
-          <t>2021 Ç1</t>
-        </is>
-      </c>
-      <c r="C215" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="D215" s="8" t="n">
-        <v>140</v>
-      </c>
-      <c r="E215" s="8" t="n">
-        <v>1330</v>
-      </c>
-      <c r="F215" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G215" s="8" t="n"/>
-      <c r="H215" s="8" t="n"/>
-      <c r="I215" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J215" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K215" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="L215" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M215" s="8" t="n"/>
-      <c r="N215" s="8" t="n"/>
-      <c r="O215" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="P215" s="8" t="n">
-        <v>140</v>
-      </c>
-      <c r="Q215" s="8" t="n">
-        <v>1340</v>
-      </c>
-      <c r="R215" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S215" s="8" t="n"/>
-      <c r="T215" s="8" t="n"/>
-      <c r="U215" s="9" t="n">
-        <v>1516</v>
       </c>
     </row>
     <row r="216">
@@ -14644,7 +14656,7 @@
       </c>
       <c r="B216" s="7" t="inlineStr">
         <is>
-          <t>2021 Ç2</t>
+          <t>2021 Ç1</t>
         </is>
       </c>
       <c r="C216" s="8" t="n">
@@ -14701,7 +14713,7 @@
       </c>
       <c r="B217" s="7" t="inlineStr">
         <is>
-          <t>2021 Ç3</t>
+          <t>2021 Ç2</t>
         </is>
       </c>
       <c r="C217" s="8" t="n">
@@ -14758,7 +14770,7 @@
       </c>
       <c r="B218" s="7" t="inlineStr">
         <is>
-          <t>2021 Ç4</t>
+          <t>2021 Ç3</t>
         </is>
       </c>
       <c r="C218" s="8" t="n">
@@ -14815,17 +14827,17 @@
       </c>
       <c r="B219" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç1</t>
+          <t>2021 Ç4</t>
         </is>
       </c>
       <c r="C219" s="8" t="n">
-        <v>133</v>
+        <v>35</v>
       </c>
       <c r="D219" s="8" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E219" s="8" t="n">
-        <v>1191</v>
+        <v>1330</v>
       </c>
       <c r="F219" s="8" t="n">
         <v>0</v>
@@ -14839,7 +14851,7 @@
         <v>0</v>
       </c>
       <c r="K219" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L219" s="8" t="n">
         <v>1</v>
@@ -14847,13 +14859,13 @@
       <c r="M219" s="8" t="n"/>
       <c r="N219" s="8" t="n"/>
       <c r="O219" s="8" t="n">
-        <v>133</v>
+        <v>35</v>
       </c>
       <c r="P219" s="8" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="Q219" s="8" t="n">
-        <v>1202</v>
+        <v>1340</v>
       </c>
       <c r="R219" s="8" t="n">
         <v>1</v>
@@ -14861,7 +14873,7 @@
       <c r="S219" s="8" t="n"/>
       <c r="T219" s="8" t="n"/>
       <c r="U219" s="9" t="n">
-        <v>1463</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="220">
@@ -14872,17 +14884,17 @@
       </c>
       <c r="B220" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç2</t>
+          <t>2022 Ç1</t>
         </is>
       </c>
       <c r="C220" s="8" t="n">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="D220" s="8" t="n">
-        <v>190</v>
+        <v>126</v>
       </c>
       <c r="E220" s="8" t="n">
-        <v>1204</v>
+        <v>1191</v>
       </c>
       <c r="F220" s="8" t="n">
         <v>0</v>
@@ -14904,13 +14916,13 @@
       <c r="M220" s="8" t="n"/>
       <c r="N220" s="8" t="n"/>
       <c r="O220" s="8" t="n">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="P220" s="8" t="n">
-        <v>190</v>
+        <v>126</v>
       </c>
       <c r="Q220" s="8" t="n">
-        <v>1216</v>
+        <v>1202</v>
       </c>
       <c r="R220" s="8" t="n">
         <v>1</v>
@@ -14918,7 +14930,7 @@
       <c r="S220" s="8" t="n"/>
       <c r="T220" s="8" t="n"/>
       <c r="U220" s="9" t="n">
-        <v>1461</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="221">
@@ -14929,17 +14941,17 @@
       </c>
       <c r="B221" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç3</t>
+          <t>2022 Ç2</t>
         </is>
       </c>
       <c r="C221" s="8" t="n">
-        <v>408</v>
+        <v>54</v>
       </c>
       <c r="D221" s="8" t="n">
-        <v>274</v>
+        <v>190</v>
       </c>
       <c r="E221" s="8" t="n">
-        <v>1810</v>
+        <v>1204</v>
       </c>
       <c r="F221" s="8" t="n">
         <v>0</v>
@@ -14953,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="K221" s="8" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="L221" s="8" t="n">
         <v>1</v>
@@ -14961,13 +14973,13 @@
       <c r="M221" s="8" t="n"/>
       <c r="N221" s="8" t="n"/>
       <c r="O221" s="8" t="n">
-        <v>408</v>
+        <v>54</v>
       </c>
       <c r="P221" s="8" t="n">
-        <v>274</v>
+        <v>190</v>
       </c>
       <c r="Q221" s="8" t="n">
-        <v>1851</v>
+        <v>1216</v>
       </c>
       <c r="R221" s="8" t="n">
         <v>1</v>
@@ -14975,7 +14987,7 @@
       <c r="S221" s="8" t="n"/>
       <c r="T221" s="8" t="n"/>
       <c r="U221" s="9" t="n">
-        <v>2534</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="222">
@@ -14986,17 +14998,17 @@
       </c>
       <c r="B222" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç4</t>
+          <t>2022 Ç3</t>
         </is>
       </c>
       <c r="C222" s="8" t="n">
-        <v>162</v>
+        <v>408</v>
       </c>
       <c r="D222" s="8" t="n">
-        <v>433</v>
+        <v>274</v>
       </c>
       <c r="E222" s="8" t="n">
-        <v>4294</v>
+        <v>1810</v>
       </c>
       <c r="F222" s="8" t="n">
         <v>0</v>
@@ -15010,7 +15022,7 @@
         <v>0</v>
       </c>
       <c r="K222" s="8" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="L222" s="8" t="n">
         <v>1</v>
@@ -15018,13 +15030,13 @@
       <c r="M222" s="8" t="n"/>
       <c r="N222" s="8" t="n"/>
       <c r="O222" s="8" t="n">
-        <v>162</v>
+        <v>408</v>
       </c>
       <c r="P222" s="8" t="n">
-        <v>433</v>
+        <v>274</v>
       </c>
       <c r="Q222" s="8" t="n">
-        <v>4359</v>
+        <v>1851</v>
       </c>
       <c r="R222" s="8" t="n">
         <v>1</v>
@@ -15032,7 +15044,7 @@
       <c r="S222" s="8" t="n"/>
       <c r="T222" s="8" t="n"/>
       <c r="U222" s="9" t="n">
-        <v>4956</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="223">
@@ -15043,17 +15055,17 @@
       </c>
       <c r="B223" s="7" t="inlineStr">
         <is>
-          <t>2023 Ç1</t>
+          <t>2022 Ç4</t>
         </is>
       </c>
       <c r="C223" s="8" t="n">
-        <v>22</v>
+        <v>162</v>
       </c>
       <c r="D223" s="8" t="n">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="E223" s="8" t="n">
-        <v>3219</v>
+        <v>4294</v>
       </c>
       <c r="F223" s="8" t="n">
         <v>0</v>
@@ -15075,13 +15087,13 @@
       <c r="M223" s="8" t="n"/>
       <c r="N223" s="8" t="n"/>
       <c r="O223" s="8" t="n">
-        <v>22</v>
+        <v>162</v>
       </c>
       <c r="P223" s="8" t="n">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="Q223" s="8" t="n">
-        <v>3283</v>
+        <v>4359</v>
       </c>
       <c r="R223" s="8" t="n">
         <v>1</v>
@@ -15089,7 +15101,7 @@
       <c r="S223" s="8" t="n"/>
       <c r="T223" s="8" t="n"/>
       <c r="U223" s="9" t="n">
-        <v>3735</v>
+        <v>4956</v>
       </c>
     </row>
     <row r="224">
@@ -15100,17 +15112,17 @@
       </c>
       <c r="B224" s="7" t="inlineStr">
         <is>
-          <t>2023 Ç2</t>
+          <t>2023 Ç1</t>
         </is>
       </c>
       <c r="C224" s="8" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D224" s="8" t="n">
-        <v>581</v>
+        <v>428</v>
       </c>
       <c r="E224" s="8" t="n">
-        <v>4439</v>
+        <v>3219</v>
       </c>
       <c r="F224" s="8" t="n">
         <v>0</v>
@@ -15127,26 +15139,26 @@
         <v>65</v>
       </c>
       <c r="L224" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M224" s="8" t="n"/>
       <c r="N224" s="8" t="n"/>
       <c r="O224" s="8" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="P224" s="8" t="n">
-        <v>581</v>
+        <v>428</v>
       </c>
       <c r="Q224" s="8" t="n">
-        <v>4504</v>
+        <v>3283</v>
       </c>
       <c r="R224" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S224" s="8" t="n"/>
       <c r="T224" s="8" t="n"/>
       <c r="U224" s="9" t="n">
-        <v>5098</v>
+        <v>3735</v>
       </c>
     </row>
     <row r="225">
@@ -15157,17 +15169,17 @@
       </c>
       <c r="B225" s="7" t="inlineStr">
         <is>
-          <t>2023 Ç3</t>
+          <t>2023 Ç2</t>
         </is>
       </c>
       <c r="C225" s="8" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D225" s="8" t="n">
-        <v>403</v>
+        <v>581</v>
       </c>
       <c r="E225" s="8" t="n">
-        <v>3978</v>
+        <v>4439</v>
       </c>
       <c r="F225" s="8" t="n">
         <v>0</v>
@@ -15189,13 +15201,13 @@
       <c r="M225" s="8" t="n"/>
       <c r="N225" s="8" t="n"/>
       <c r="O225" s="8" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="P225" s="8" t="n">
-        <v>403</v>
+        <v>581</v>
       </c>
       <c r="Q225" s="8" t="n">
-        <v>4043</v>
+        <v>4504</v>
       </c>
       <c r="R225" s="8" t="n">
         <v>2</v>
@@ -15203,7 +15215,7 @@
       <c r="S225" s="8" t="n"/>
       <c r="T225" s="8" t="n"/>
       <c r="U225" s="9" t="n">
-        <v>4473</v>
+        <v>5098</v>
       </c>
     </row>
     <row r="226">
@@ -15214,17 +15226,17 @@
       </c>
       <c r="B226" s="7" t="inlineStr">
         <is>
-          <t>2023 Ç4</t>
+          <t>2023 Ç3</t>
         </is>
       </c>
       <c r="C226" s="8" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D226" s="8" t="n">
-        <v>430</v>
+        <v>403</v>
       </c>
       <c r="E226" s="8" t="n">
-        <v>3747</v>
+        <v>3978</v>
       </c>
       <c r="F226" s="8" t="n">
         <v>0</v>
@@ -15246,13 +15258,13 @@
       <c r="M226" s="8" t="n"/>
       <c r="N226" s="8" t="n"/>
       <c r="O226" s="8" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="P226" s="8" t="n">
-        <v>430</v>
+        <v>403</v>
       </c>
       <c r="Q226" s="8" t="n">
-        <v>3812</v>
+        <v>4043</v>
       </c>
       <c r="R226" s="8" t="n">
         <v>2</v>
@@ -15260,7 +15272,7 @@
       <c r="S226" s="8" t="n"/>
       <c r="T226" s="8" t="n"/>
       <c r="U226" s="9" t="n">
-        <v>4256</v>
+        <v>4473</v>
       </c>
     </row>
     <row r="227">
@@ -15271,17 +15283,17 @@
       </c>
       <c r="B227" s="7" t="inlineStr">
         <is>
-          <t>2024 Ç2</t>
+          <t>2023 Ç4</t>
         </is>
       </c>
       <c r="C227" s="8" t="n">
-        <v>890</v>
+        <v>12</v>
       </c>
       <c r="D227" s="8" t="n">
-        <v>897</v>
+        <v>430</v>
       </c>
       <c r="E227" s="8" t="n">
-        <v>5226</v>
+        <v>3747</v>
       </c>
       <c r="F227" s="8" t="n">
         <v>0</v>
@@ -15289,35 +15301,35 @@
       <c r="G227" s="8" t="n"/>
       <c r="H227" s="8" t="n"/>
       <c r="I227" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J227" s="8" t="n">
         <v>0</v>
       </c>
       <c r="K227" s="8" t="n">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="L227" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M227" s="8" t="n"/>
       <c r="N227" s="8" t="n"/>
       <c r="O227" s="8" t="n">
-        <v>891</v>
+        <v>12</v>
       </c>
       <c r="P227" s="8" t="n">
-        <v>897</v>
+        <v>430</v>
       </c>
       <c r="Q227" s="8" t="n">
-        <v>5338</v>
+        <v>3812</v>
       </c>
       <c r="R227" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S227" s="8" t="n"/>
       <c r="T227" s="8" t="n"/>
       <c r="U227" s="9" t="n">
-        <v>7128</v>
+        <v>4256</v>
       </c>
     </row>
     <row r="228">
@@ -15328,17 +15340,17 @@
       </c>
       <c r="B228" s="7" t="inlineStr">
         <is>
-          <t>2025 Ç2</t>
+          <t>2024 Ç2</t>
         </is>
       </c>
       <c r="C228" s="8" t="n">
-        <v>1318</v>
+        <v>890</v>
       </c>
       <c r="D228" s="8" t="n">
-        <v>1344</v>
+        <v>897</v>
       </c>
       <c r="E228" s="8" t="n">
-        <v>9794</v>
+        <v>5226</v>
       </c>
       <c r="F228" s="8" t="n">
         <v>0</v>
@@ -15352,98 +15364,86 @@
         <v>0</v>
       </c>
       <c r="K228" s="8" t="n">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="L228" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M228" s="8" t="n"/>
       <c r="N228" s="8" t="n"/>
       <c r="O228" s="8" t="n">
-        <v>1319</v>
+        <v>891</v>
       </c>
       <c r="P228" s="8" t="n">
-        <v>1344</v>
+        <v>897</v>
       </c>
       <c r="Q228" s="8" t="n">
-        <v>9927</v>
+        <v>5338</v>
       </c>
       <c r="R228" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S228" s="8" t="n"/>
       <c r="T228" s="8" t="n"/>
       <c r="U228" s="9" t="n">
+        <v>7128</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="inlineStr">
+        <is>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="B229" s="7" t="inlineStr">
+        <is>
+          <t>2025 Ç2</t>
+        </is>
+      </c>
+      <c r="C229" s="8" t="n">
+        <v>1318</v>
+      </c>
+      <c r="D229" s="8" t="n">
+        <v>1344</v>
+      </c>
+      <c r="E229" s="8" t="n">
+        <v>9794</v>
+      </c>
+      <c r="F229" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" s="8" t="n"/>
+      <c r="H229" s="8" t="n"/>
+      <c r="I229" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J229" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" s="8" t="n">
+        <v>133</v>
+      </c>
+      <c r="L229" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="M229" s="8" t="n"/>
+      <c r="N229" s="8" t="n"/>
+      <c r="O229" s="8" t="n">
+        <v>1319</v>
+      </c>
+      <c r="P229" s="8" t="n">
+        <v>1344</v>
+      </c>
+      <c r="Q229" s="8" t="n">
+        <v>9927</v>
+      </c>
+      <c r="R229" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="S229" s="8" t="n"/>
+      <c r="T229" s="8" t="n"/>
+      <c r="U229" s="9" t="n">
         <v>12594</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="10" t="inlineStr">
-        <is>
-          <t>Burgan</t>
-        </is>
-      </c>
-      <c r="B229" s="11" t="inlineStr">
-        <is>
-          <t>2021 Ç1</t>
-        </is>
-      </c>
-      <c r="C229" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D229" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E229" s="12" t="n">
-        <v>566</v>
-      </c>
-      <c r="F229" s="12" t="n">
-        <v>93</v>
-      </c>
-      <c r="G229" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H229" s="12" t="n">
-        <v>1024</v>
-      </c>
-      <c r="I229" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="J229" s="12" t="n">
-        <v>117</v>
-      </c>
-      <c r="K229" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L229" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M229" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N229" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O229" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="P229" s="12" t="n">
-        <v>119</v>
-      </c>
-      <c r="Q229" s="12" t="n">
-        <v>574</v>
-      </c>
-      <c r="R229" s="12" t="n">
-        <v>93</v>
-      </c>
-      <c r="S229" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T229" s="12" t="n">
-        <v>1024</v>
-      </c>
-      <c r="U229" s="13" t="n">
-        <v>1826</v>
       </c>
     </row>
     <row r="230">
@@ -15454,7 +15454,7 @@
       </c>
       <c r="B230" s="11" t="inlineStr">
         <is>
-          <t>2021 Ç2</t>
+          <t>2021 Ç1</t>
         </is>
       </c>
       <c r="C230" s="12" t="n">
@@ -15523,7 +15523,7 @@
       </c>
       <c r="B231" s="11" t="inlineStr">
         <is>
-          <t>2021 Ç3</t>
+          <t>2021 Ç2</t>
         </is>
       </c>
       <c r="C231" s="12" t="n">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="B232" s="11" t="inlineStr">
         <is>
-          <t>2021 Ç4</t>
+          <t>2021 Ç3</t>
         </is>
       </c>
       <c r="C232" s="12" t="n">
@@ -15661,32 +15661,32 @@
       </c>
       <c r="B233" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç1</t>
+          <t>2021 Ç4</t>
         </is>
       </c>
       <c r="C233" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D233" s="12" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="E233" s="12" t="n">
-        <v>733</v>
+        <v>566</v>
       </c>
       <c r="F233" s="12" t="n">
-        <v>190</v>
+        <v>93</v>
       </c>
       <c r="G233" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H233" s="12" t="n">
-        <v>1443</v>
+        <v>1024</v>
       </c>
       <c r="I233" s="12" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="J233" s="12" t="n">
-        <v>314</v>
+        <v>117</v>
       </c>
       <c r="K233" s="12" t="n">
         <v>8</v>
@@ -15701,25 +15701,25 @@
         <v>0</v>
       </c>
       <c r="O233" s="12" t="n">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="P233" s="12" t="n">
-        <v>353</v>
+        <v>119</v>
       </c>
       <c r="Q233" s="12" t="n">
-        <v>740</v>
+        <v>574</v>
       </c>
       <c r="R233" s="12" t="n">
-        <v>190</v>
+        <v>93</v>
       </c>
       <c r="S233" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T233" s="12" t="n">
-        <v>1443</v>
+        <v>1024</v>
       </c>
       <c r="U233" s="13" t="n">
-        <v>2783</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="234">
@@ -15730,32 +15730,32 @@
       </c>
       <c r="B234" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç2</t>
+          <t>2022 Ç1</t>
         </is>
       </c>
       <c r="C234" s="12" t="n">
         <v>3</v>
       </c>
       <c r="D234" s="12" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="E234" s="12" t="n">
-        <v>920</v>
+        <v>733</v>
       </c>
       <c r="F234" s="12" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="G234" s="12" t="n">
-        <v>1083</v>
+        <v>0</v>
       </c>
       <c r="H234" s="12" t="n">
-        <v>1634</v>
+        <v>1443</v>
       </c>
       <c r="I234" s="12" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="J234" s="12" t="n">
-        <v>5</v>
+        <v>314</v>
       </c>
       <c r="K234" s="12" t="n">
         <v>8</v>
@@ -15770,25 +15770,25 @@
         <v>0</v>
       </c>
       <c r="O234" s="12" t="n">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="P234" s="12" t="n">
-        <v>7</v>
+        <v>353</v>
       </c>
       <c r="Q234" s="12" t="n">
-        <v>928</v>
+        <v>740</v>
       </c>
       <c r="R234" s="12" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="S234" s="12" t="n">
-        <v>1083</v>
+        <v>0</v>
       </c>
       <c r="T234" s="12" t="n">
-        <v>1634</v>
+        <v>1443</v>
       </c>
       <c r="U234" s="13" t="n">
-        <v>3917</v>
+        <v>2783</v>
       </c>
     </row>
     <row r="235">
@@ -15799,32 +15799,32 @@
       </c>
       <c r="B235" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç3</t>
+          <t>2022 Ç2</t>
         </is>
       </c>
       <c r="C235" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D235" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E235" s="12" t="n">
-        <v>1117</v>
+        <v>920</v>
       </c>
       <c r="F235" s="12" t="n">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="G235" s="12" t="n">
-        <v>1694</v>
+        <v>1083</v>
       </c>
       <c r="H235" s="12" t="n">
-        <v>1558</v>
+        <v>1634</v>
       </c>
       <c r="I235" s="12" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J235" s="12" t="n">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="K235" s="12" t="n">
         <v>8</v>
@@ -15839,25 +15839,25 @@
         <v>0</v>
       </c>
       <c r="O235" s="12" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="P235" s="12" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="Q235" s="12" t="n">
-        <v>1125</v>
+        <v>928</v>
       </c>
       <c r="R235" s="12" t="n">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="S235" s="12" t="n">
-        <v>1694</v>
+        <v>1083</v>
       </c>
       <c r="T235" s="12" t="n">
-        <v>1558</v>
+        <v>1634</v>
       </c>
       <c r="U235" s="13" t="n">
-        <v>4736</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="236">
@@ -15868,32 +15868,32 @@
       </c>
       <c r="B236" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç4</t>
+          <t>2022 Ç3</t>
         </is>
       </c>
       <c r="C236" s="12" t="n">
-        <v>383</v>
+        <v>4</v>
       </c>
       <c r="D236" s="12" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E236" s="12" t="n">
-        <v>1334</v>
+        <v>1117</v>
       </c>
       <c r="F236" s="12" t="n">
-        <v>262</v>
+        <v>194</v>
       </c>
       <c r="G236" s="12" t="n">
-        <v>3679</v>
+        <v>1694</v>
       </c>
       <c r="H236" s="12" t="n">
-        <v>1702</v>
+        <v>1558</v>
       </c>
       <c r="I236" s="12" t="n">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J236" s="12" t="n">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="K236" s="12" t="n">
         <v>8</v>
@@ -15908,25 +15908,25 @@
         <v>0</v>
       </c>
       <c r="O236" s="12" t="n">
-        <v>479</v>
+        <v>87</v>
       </c>
       <c r="P236" s="12" t="n">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="Q236" s="12" t="n">
-        <v>1342</v>
+        <v>1125</v>
       </c>
       <c r="R236" s="12" t="n">
-        <v>262</v>
+        <v>194</v>
       </c>
       <c r="S236" s="12" t="n">
-        <v>3679</v>
+        <v>1694</v>
       </c>
       <c r="T236" s="12" t="n">
-        <v>1702</v>
+        <v>1558</v>
       </c>
       <c r="U236" s="13" t="n">
-        <v>7588</v>
+        <v>4736</v>
       </c>
     </row>
     <row r="237">
@@ -15937,32 +15937,32 @@
       </c>
       <c r="B237" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç1</t>
+          <t>2022 Ç4</t>
         </is>
       </c>
       <c r="C237" s="12" t="n">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="D237" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="E237" s="12" t="n">
+        <v>1334</v>
+      </c>
+      <c r="F237" s="12" t="n">
+        <v>262</v>
+      </c>
+      <c r="G237" s="12" t="n">
+        <v>3679</v>
+      </c>
+      <c r="H237" s="12" t="n">
+        <v>1702</v>
+      </c>
+      <c r="I237" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="J237" s="12" t="n">
         <v>106</v>
-      </c>
-      <c r="E237" s="12" t="n">
-        <v>1426</v>
-      </c>
-      <c r="F237" s="12" t="n">
-        <v>476</v>
-      </c>
-      <c r="G237" s="12" t="n">
-        <v>3616</v>
-      </c>
-      <c r="H237" s="12" t="n">
-        <v>1834</v>
-      </c>
-      <c r="I237" s="12" t="n">
-        <v>111</v>
-      </c>
-      <c r="J237" s="12" t="n">
-        <v>186</v>
       </c>
       <c r="K237" s="12" t="n">
         <v>8</v>
@@ -15977,25 +15977,25 @@
         <v>0</v>
       </c>
       <c r="O237" s="12" t="n">
-        <v>111</v>
+        <v>479</v>
       </c>
       <c r="P237" s="12" t="n">
-        <v>292</v>
+        <v>125</v>
       </c>
       <c r="Q237" s="12" t="n">
-        <v>1433</v>
+        <v>1342</v>
       </c>
       <c r="R237" s="12" t="n">
-        <v>476</v>
+        <v>262</v>
       </c>
       <c r="S237" s="12" t="n">
-        <v>3616</v>
+        <v>3679</v>
       </c>
       <c r="T237" s="12" t="n">
-        <v>1834</v>
+        <v>1702</v>
       </c>
       <c r="U237" s="13" t="n">
-        <v>7761</v>
+        <v>7588</v>
       </c>
     </row>
     <row r="238">
@@ -16006,32 +16006,32 @@
       </c>
       <c r="B238" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç2</t>
+          <t>2023 Ç1</t>
         </is>
       </c>
       <c r="C238" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D238" s="12" t="n">
-        <v>14</v>
+        <v>106</v>
       </c>
       <c r="E238" s="12" t="n">
-        <v>2067</v>
+        <v>1426</v>
       </c>
       <c r="F238" s="12" t="n">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="G238" s="12" t="n">
-        <v>3871</v>
+        <v>3616</v>
       </c>
       <c r="H238" s="12" t="n">
-        <v>2504</v>
+        <v>1834</v>
       </c>
       <c r="I238" s="12" t="n">
-        <v>168</v>
+        <v>111</v>
       </c>
       <c r="J238" s="12" t="n">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="K238" s="12" t="n">
         <v>8</v>
@@ -16046,25 +16046,25 @@
         <v>0</v>
       </c>
       <c r="O238" s="12" t="n">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="P238" s="12" t="n">
-        <v>225</v>
+        <v>292</v>
       </c>
       <c r="Q238" s="12" t="n">
-        <v>2075</v>
+        <v>1433</v>
       </c>
       <c r="R238" s="12" t="n">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="S238" s="12" t="n">
-        <v>3871</v>
+        <v>3616</v>
       </c>
       <c r="T238" s="12" t="n">
-        <v>2504</v>
+        <v>1834</v>
       </c>
       <c r="U238" s="13" t="n">
-        <v>9333</v>
+        <v>7761</v>
       </c>
     </row>
     <row r="239">
@@ -16075,38 +16075,38 @@
       </c>
       <c r="B239" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç3</t>
+          <t>2023 Ç2</t>
         </is>
       </c>
       <c r="C239" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D239" s="12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E239" s="12" t="n">
-        <v>2172</v>
+        <v>2067</v>
       </c>
       <c r="F239" s="12" t="n">
-        <v>736</v>
+        <v>489</v>
       </c>
       <c r="G239" s="12" t="n">
-        <v>4868</v>
+        <v>3871</v>
       </c>
       <c r="H239" s="12" t="n">
-        <v>2770</v>
+        <v>2504</v>
       </c>
       <c r="I239" s="12" t="n">
-        <v>2582</v>
+        <v>168</v>
       </c>
       <c r="J239" s="12" t="n">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="K239" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L239" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M239" s="12" t="n">
         <v>0</v>
@@ -16115,25 +16115,25 @@
         <v>0</v>
       </c>
       <c r="O239" s="12" t="n">
-        <v>2582</v>
+        <v>169</v>
       </c>
       <c r="P239" s="12" t="n">
-        <v>259</v>
+        <v>225</v>
       </c>
       <c r="Q239" s="12" t="n">
-        <v>2179</v>
+        <v>2075</v>
       </c>
       <c r="R239" s="12" t="n">
-        <v>790</v>
+        <v>489</v>
       </c>
       <c r="S239" s="12" t="n">
-        <v>4868</v>
+        <v>3871</v>
       </c>
       <c r="T239" s="12" t="n">
-        <v>2770</v>
+        <v>2504</v>
       </c>
       <c r="U239" s="13" t="n">
-        <v>13448</v>
+        <v>9333</v>
       </c>
     </row>
     <row r="240">
@@ -16144,38 +16144,38 @@
       </c>
       <c r="B240" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç4</t>
+          <t>2023 Ç3</t>
         </is>
       </c>
       <c r="C240" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D240" s="12" t="n">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="E240" s="12" t="n">
-        <v>2013</v>
+        <v>2172</v>
       </c>
       <c r="F240" s="12" t="n">
-        <v>989</v>
+        <v>736</v>
       </c>
       <c r="G240" s="12" t="n">
-        <v>6432</v>
+        <v>4868</v>
       </c>
       <c r="H240" s="12" t="n">
-        <v>3233</v>
+        <v>2770</v>
       </c>
       <c r="I240" s="12" t="n">
-        <v>750</v>
+        <v>2582</v>
       </c>
       <c r="J240" s="12" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="K240" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L240" s="12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M240" s="12" t="n">
         <v>0</v>
@@ -16184,25 +16184,25 @@
         <v>0</v>
       </c>
       <c r="O240" s="12" t="n">
-        <v>751</v>
+        <v>2582</v>
       </c>
       <c r="P240" s="12" t="n">
-        <v>65</v>
+        <v>259</v>
       </c>
       <c r="Q240" s="12" t="n">
-        <v>2021</v>
+        <v>2179</v>
       </c>
       <c r="R240" s="12" t="n">
-        <v>989</v>
+        <v>790</v>
       </c>
       <c r="S240" s="12" t="n">
-        <v>6432</v>
+        <v>4868</v>
       </c>
       <c r="T240" s="12" t="n">
-        <v>3233</v>
+        <v>2770</v>
       </c>
       <c r="U240" s="13" t="n">
-        <v>13491</v>
+        <v>13448</v>
       </c>
     </row>
     <row r="241">
@@ -16213,65 +16213,65 @@
       </c>
       <c r="B241" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç1</t>
+          <t>2023 Ç4</t>
         </is>
       </c>
       <c r="C241" s="12" t="n">
-        <v>341</v>
+        <v>2</v>
       </c>
       <c r="D241" s="12" t="n">
-        <v>563</v>
+        <v>65</v>
       </c>
       <c r="E241" s="12" t="n">
-        <v>5997</v>
+        <v>2013</v>
       </c>
       <c r="F241" s="12" t="n">
-        <v>4196</v>
+        <v>989</v>
       </c>
       <c r="G241" s="12" t="n">
-        <v>8715</v>
+        <v>6432</v>
       </c>
       <c r="H241" s="12" t="n">
-        <v>5110</v>
+        <v>3233</v>
       </c>
       <c r="I241" s="12" t="n">
-        <v>370</v>
+        <v>750</v>
       </c>
       <c r="J241" s="12" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="K241" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L241" s="12" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="M241" s="12" t="n">
-        <v>549</v>
+        <v>0</v>
       </c>
       <c r="N241" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O241" s="12" t="n">
-        <v>711</v>
+        <v>751</v>
       </c>
       <c r="P241" s="12" t="n">
-        <v>1283</v>
+        <v>65</v>
       </c>
       <c r="Q241" s="12" t="n">
-        <v>6005</v>
+        <v>2021</v>
       </c>
       <c r="R241" s="12" t="n">
-        <v>4588</v>
+        <v>989</v>
       </c>
       <c r="S241" s="12" t="n">
-        <v>9264</v>
+        <v>6432</v>
       </c>
       <c r="T241" s="12" t="n">
-        <v>5110</v>
+        <v>3233</v>
       </c>
       <c r="U241" s="13" t="n">
-        <v>26960</v>
+        <v>13491</v>
       </c>
     </row>
     <row r="242">
@@ -16282,65 +16282,65 @@
       </c>
       <c r="B242" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç2</t>
+          <t>2024 Ç1</t>
         </is>
       </c>
       <c r="C242" s="12" t="n">
-        <v>170</v>
+        <v>341</v>
       </c>
       <c r="D242" s="12" t="n">
-        <v>600</v>
+        <v>563</v>
       </c>
       <c r="E242" s="12" t="n">
-        <v>4171</v>
+        <v>5997</v>
       </c>
       <c r="F242" s="12" t="n">
-        <v>2250</v>
+        <v>4196</v>
       </c>
       <c r="G242" s="12" t="n">
-        <v>7530</v>
+        <v>8715</v>
       </c>
       <c r="H242" s="12" t="n">
-        <v>3686</v>
+        <v>5110</v>
       </c>
       <c r="I242" s="12" t="n">
-        <v>292</v>
+        <v>370</v>
       </c>
       <c r="J242" s="12" t="n">
-        <v>976</v>
+        <v>720</v>
       </c>
       <c r="K242" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L242" s="12" t="n">
-        <v>475</v>
+        <v>392</v>
       </c>
       <c r="M242" s="12" t="n">
-        <v>1245</v>
+        <v>549</v>
       </c>
       <c r="N242" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O242" s="12" t="n">
-        <v>462</v>
+        <v>711</v>
       </c>
       <c r="P242" s="12" t="n">
-        <v>1576</v>
+        <v>1283</v>
       </c>
       <c r="Q242" s="12" t="n">
-        <v>4178</v>
+        <v>6005</v>
       </c>
       <c r="R242" s="12" t="n">
-        <v>2724</v>
+        <v>4588</v>
       </c>
       <c r="S242" s="12" t="n">
-        <v>8774</v>
+        <v>9264</v>
       </c>
       <c r="T242" s="12" t="n">
-        <v>3686</v>
+        <v>5110</v>
       </c>
       <c r="U242" s="13" t="n">
-        <v>21401</v>
+        <v>26960</v>
       </c>
     </row>
     <row r="243">
@@ -16351,65 +16351,65 @@
       </c>
       <c r="B243" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç3</t>
+          <t>2024 Ç2</t>
         </is>
       </c>
       <c r="C243" s="12" t="n">
-        <v>350</v>
+        <v>170</v>
       </c>
       <c r="D243" s="12" t="n">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="E243" s="12" t="n">
-        <v>4788</v>
+        <v>4171</v>
       </c>
       <c r="F243" s="12" t="n">
-        <v>3549</v>
+        <v>2250</v>
       </c>
       <c r="G243" s="12" t="n">
-        <v>8069</v>
+        <v>7530</v>
       </c>
       <c r="H243" s="12" t="n">
-        <v>4732</v>
+        <v>3686</v>
       </c>
       <c r="I243" s="12" t="n">
-        <v>340</v>
+        <v>292</v>
       </c>
       <c r="J243" s="12" t="n">
-        <v>991</v>
+        <v>976</v>
       </c>
       <c r="K243" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L243" s="12" t="n">
-        <v>0</v>
+        <v>475</v>
       </c>
       <c r="M243" s="12" t="n">
-        <v>455</v>
+        <v>1245</v>
       </c>
       <c r="N243" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O243" s="12" t="n">
-        <v>689</v>
+        <v>462</v>
       </c>
       <c r="P243" s="12" t="n">
-        <v>1583</v>
+        <v>1576</v>
       </c>
       <c r="Q243" s="12" t="n">
-        <v>4796</v>
+        <v>4178</v>
       </c>
       <c r="R243" s="12" t="n">
-        <v>3549</v>
+        <v>2724</v>
       </c>
       <c r="S243" s="12" t="n">
-        <v>8524</v>
+        <v>8774</v>
       </c>
       <c r="T243" s="12" t="n">
-        <v>4732</v>
+        <v>3686</v>
       </c>
       <c r="U243" s="13" t="n">
-        <v>23873</v>
+        <v>21401</v>
       </c>
     </row>
     <row r="244">
@@ -16420,65 +16420,65 @@
       </c>
       <c r="B244" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç4</t>
+          <t>2024 Ç3</t>
         </is>
       </c>
       <c r="C244" s="12" t="n">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="D244" s="12" t="n">
-        <v>563</v>
+        <v>592</v>
       </c>
       <c r="E244" s="12" t="n">
-        <v>5997</v>
+        <v>4788</v>
       </c>
       <c r="F244" s="12" t="n">
-        <v>4196</v>
+        <v>3549</v>
       </c>
       <c r="G244" s="12" t="n">
-        <v>8715</v>
+        <v>8069</v>
       </c>
       <c r="H244" s="12" t="n">
-        <v>5110</v>
+        <v>4732</v>
       </c>
       <c r="I244" s="12" t="n">
-        <v>370</v>
+        <v>340</v>
       </c>
       <c r="J244" s="12" t="n">
-        <v>720</v>
+        <v>991</v>
       </c>
       <c r="K244" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L244" s="12" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="M244" s="12" t="n">
-        <v>549</v>
+        <v>455</v>
       </c>
       <c r="N244" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O244" s="12" t="n">
-        <v>711</v>
+        <v>689</v>
       </c>
       <c r="P244" s="12" t="n">
-        <v>1283</v>
+        <v>1583</v>
       </c>
       <c r="Q244" s="12" t="n">
-        <v>6005</v>
+        <v>4796</v>
       </c>
       <c r="R244" s="12" t="n">
-        <v>4588</v>
+        <v>3549</v>
       </c>
       <c r="S244" s="12" t="n">
-        <v>9264</v>
+        <v>8524</v>
       </c>
       <c r="T244" s="12" t="n">
-        <v>5110</v>
+        <v>4732</v>
       </c>
       <c r="U244" s="13" t="n">
-        <v>26960</v>
+        <v>23873</v>
       </c>
     </row>
     <row r="245">
@@ -16489,65 +16489,65 @@
       </c>
       <c r="B245" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç1</t>
+          <t>2024 Ç4</t>
         </is>
       </c>
       <c r="C245" s="12" t="n">
-        <v>965</v>
+        <v>341</v>
       </c>
       <c r="D245" s="12" t="n">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="E245" s="12" t="n">
-        <v>5063</v>
+        <v>5997</v>
       </c>
       <c r="F245" s="12" t="n">
-        <v>3502</v>
+        <v>4196</v>
       </c>
       <c r="G245" s="12" t="n">
-        <v>10006</v>
+        <v>8715</v>
       </c>
       <c r="H245" s="12" t="n">
-        <v>5700</v>
+        <v>5110</v>
       </c>
       <c r="I245" s="12" t="n">
-        <v>905</v>
+        <v>370</v>
       </c>
       <c r="J245" s="12" t="n">
-        <v>847</v>
+        <v>720</v>
       </c>
       <c r="K245" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L245" s="12" t="n">
-        <v>942</v>
+        <v>392</v>
       </c>
       <c r="M245" s="12" t="n">
-        <v>167</v>
+        <v>549</v>
       </c>
       <c r="N245" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O245" s="12" t="n">
-        <v>1870</v>
+        <v>711</v>
       </c>
       <c r="P245" s="12" t="n">
-        <v>1404</v>
+        <v>1283</v>
       </c>
       <c r="Q245" s="12" t="n">
-        <v>5070</v>
+        <v>6005</v>
       </c>
       <c r="R245" s="12" t="n">
-        <v>4444</v>
+        <v>4588</v>
       </c>
       <c r="S245" s="12" t="n">
-        <v>10173</v>
+        <v>9264</v>
       </c>
       <c r="T245" s="12" t="n">
-        <v>5700</v>
+        <v>5110</v>
       </c>
       <c r="U245" s="13" t="n">
-        <v>28661</v>
+        <v>26960</v>
       </c>
     </row>
     <row r="246">
@@ -16558,65 +16558,65 @@
       </c>
       <c r="B246" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç2</t>
+          <t>2025 Ç1</t>
         </is>
       </c>
       <c r="C246" s="12" t="n">
-        <v>2813</v>
+        <v>965</v>
       </c>
       <c r="D246" s="12" t="n">
-        <v>442</v>
+        <v>557</v>
       </c>
       <c r="E246" s="12" t="n">
-        <v>4675</v>
+        <v>5063</v>
       </c>
       <c r="F246" s="12" t="n">
-        <v>3426</v>
+        <v>3502</v>
       </c>
       <c r="G246" s="12" t="n">
-        <v>8391</v>
+        <v>10006</v>
       </c>
       <c r="H246" s="12" t="n">
-        <v>6663</v>
+        <v>5700</v>
       </c>
       <c r="I246" s="12" t="n">
-        <v>464</v>
+        <v>905</v>
       </c>
       <c r="J246" s="12" t="n">
-        <v>1024</v>
+        <v>847</v>
       </c>
       <c r="K246" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L246" s="12" t="n">
-        <v>1017</v>
+        <v>942</v>
       </c>
       <c r="M246" s="12" t="n">
-        <v>620</v>
+        <v>167</v>
       </c>
       <c r="N246" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O246" s="12" t="n">
-        <v>3277</v>
+        <v>1870</v>
       </c>
       <c r="P246" s="12" t="n">
-        <v>1466</v>
+        <v>1404</v>
       </c>
       <c r="Q246" s="12" t="n">
-        <v>4682</v>
+        <v>5070</v>
       </c>
       <c r="R246" s="12" t="n">
         <v>4444</v>
       </c>
       <c r="S246" s="12" t="n">
-        <v>9011</v>
+        <v>10173</v>
       </c>
       <c r="T246" s="12" t="n">
-        <v>6663</v>
+        <v>5700</v>
       </c>
       <c r="U246" s="13" t="n">
-        <v>29543</v>
+        <v>28661</v>
       </c>
     </row>
     <row r="247">
@@ -16627,65 +16627,65 @@
       </c>
       <c r="B247" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç3</t>
+          <t>2025 Ç2</t>
         </is>
       </c>
       <c r="C247" s="12" t="n">
-        <v>2601</v>
+        <v>2813</v>
       </c>
       <c r="D247" s="12" t="n">
-        <v>821</v>
+        <v>442</v>
       </c>
       <c r="E247" s="12" t="n">
-        <v>5579</v>
+        <v>4675</v>
       </c>
       <c r="F247" s="12" t="n">
-        <v>3830</v>
+        <v>3426</v>
       </c>
       <c r="G247" s="12" t="n">
-        <v>8621</v>
+        <v>8391</v>
       </c>
       <c r="H247" s="12" t="n">
-        <v>7421</v>
+        <v>6663</v>
       </c>
       <c r="I247" s="12" t="n">
-        <v>536</v>
+        <v>464</v>
       </c>
       <c r="J247" s="12" t="n">
-        <v>1703</v>
+        <v>1024</v>
       </c>
       <c r="K247" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L247" s="12" t="n">
-        <v>737</v>
+        <v>1017</v>
       </c>
       <c r="M247" s="12" t="n">
-        <v>839</v>
+        <v>620</v>
       </c>
       <c r="N247" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O247" s="12" t="n">
-        <v>3137</v>
+        <v>3277</v>
       </c>
       <c r="P247" s="12" t="n">
-        <v>2524</v>
+        <v>1466</v>
       </c>
       <c r="Q247" s="12" t="n">
-        <v>5586</v>
+        <v>4682</v>
       </c>
       <c r="R247" s="12" t="n">
-        <v>4567</v>
+        <v>4444</v>
       </c>
       <c r="S247" s="12" t="n">
-        <v>9460</v>
+        <v>9011</v>
       </c>
       <c r="T247" s="12" t="n">
-        <v>7421</v>
+        <v>6663</v>
       </c>
       <c r="U247" s="13" t="n">
-        <v>32695</v>
+        <v>29543</v>
       </c>
     </row>
     <row r="248">
@@ -16696,65 +16696,65 @@
       </c>
       <c r="B248" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç4</t>
+          <t>2025 Ç3</t>
         </is>
       </c>
       <c r="C248" s="12" t="n">
-        <v>2401</v>
+        <v>2601</v>
       </c>
       <c r="D248" s="12" t="n">
-        <v>728</v>
+        <v>821</v>
       </c>
       <c r="E248" s="12" t="n">
-        <v>7036</v>
+        <v>5579</v>
       </c>
       <c r="F248" s="12" t="n">
-        <v>3425</v>
+        <v>3830</v>
       </c>
       <c r="G248" s="12" t="n">
-        <v>9122</v>
+        <v>8621</v>
       </c>
       <c r="H248" s="12" t="n">
-        <v>7747</v>
+        <v>7421</v>
       </c>
       <c r="I248" s="12" t="n">
-        <v>1590</v>
+        <v>536</v>
       </c>
       <c r="J248" s="12" t="n">
-        <v>1674</v>
+        <v>1703</v>
       </c>
       <c r="K248" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L248" s="12" t="n">
-        <v>284</v>
+        <v>737</v>
       </c>
       <c r="M248" s="12" t="n">
-        <v>663</v>
+        <v>839</v>
       </c>
       <c r="N248" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O248" s="12" t="n">
-        <v>3991</v>
+        <v>3137</v>
       </c>
       <c r="P248" s="12" t="n">
-        <v>2401</v>
+        <v>2524</v>
       </c>
       <c r="Q248" s="12" t="n">
-        <v>7044</v>
+        <v>5586</v>
       </c>
       <c r="R248" s="12" t="n">
-        <v>3709</v>
+        <v>4567</v>
       </c>
       <c r="S248" s="12" t="n">
-        <v>9785</v>
+        <v>9460</v>
       </c>
       <c r="T248" s="12" t="n">
-        <v>7747</v>
+        <v>7421</v>
       </c>
       <c r="U248" s="13" t="n">
-        <v>34678</v>
+        <v>32695</v>
       </c>
     </row>
     <row r="249">
@@ -16765,65 +16765,65 @@
       </c>
       <c r="B249" s="11" t="inlineStr">
         <is>
-          <t>2026 Ç1</t>
+          <t>2025 Ç4</t>
         </is>
       </c>
       <c r="C249" s="12" t="n">
-        <v>1290</v>
+        <v>2401</v>
       </c>
       <c r="D249" s="12" t="n">
-        <v>1556</v>
+        <v>728</v>
       </c>
       <c r="E249" s="12" t="n">
-        <v>6010</v>
+        <v>7036</v>
       </c>
       <c r="F249" s="12" t="n">
-        <v>4762</v>
+        <v>3425</v>
       </c>
       <c r="G249" s="12" t="n">
-        <v>10668</v>
+        <v>9122</v>
       </c>
       <c r="H249" s="12" t="n">
-        <v>8099</v>
+        <v>7747</v>
       </c>
       <c r="I249" s="12" t="n">
-        <v>700</v>
+        <v>1590</v>
       </c>
       <c r="J249" s="12" t="n">
-        <v>1828</v>
+        <v>1674</v>
       </c>
       <c r="K249" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L249" s="12" t="n">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="M249" s="12" t="n">
-        <v>466</v>
+        <v>663</v>
       </c>
       <c r="N249" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O249" s="12" t="n">
-        <v>1990</v>
+        <v>3991</v>
       </c>
       <c r="P249" s="12" t="n">
-        <v>3383</v>
+        <v>2401</v>
       </c>
       <c r="Q249" s="12" t="n">
-        <v>6017</v>
+        <v>7044</v>
       </c>
       <c r="R249" s="12" t="n">
-        <v>5042</v>
+        <v>3709</v>
       </c>
       <c r="S249" s="12" t="n">
-        <v>11133</v>
+        <v>9785</v>
       </c>
       <c r="T249" s="12" t="n">
-        <v>8099</v>
+        <v>7747</v>
       </c>
       <c r="U249" s="13" t="n">
-        <v>35664</v>
+        <v>34678</v>
       </c>
     </row>
     <row r="250">
@@ -16834,110 +16834,134 @@
       </c>
       <c r="B250" s="11" t="inlineStr">
         <is>
-          <t>2026 Ç2</t>
+          <t>2026 Ç1</t>
         </is>
       </c>
       <c r="C250" s="12" t="n">
-        <v>2109</v>
+        <v>1290</v>
       </c>
       <c r="D250" s="12" t="n">
-        <v>1615</v>
+        <v>1556</v>
       </c>
       <c r="E250" s="12" t="n">
-        <v>6599</v>
+        <v>6010</v>
       </c>
       <c r="F250" s="12" t="n">
-        <v>5219</v>
+        <v>4762</v>
       </c>
       <c r="G250" s="12" t="n">
-        <v>11008</v>
+        <v>10668</v>
       </c>
       <c r="H250" s="12" t="n">
-        <v>8520</v>
+        <v>8099</v>
       </c>
       <c r="I250" s="12" t="n">
-        <v>717</v>
+        <v>700</v>
       </c>
       <c r="J250" s="12" t="n">
-        <v>1698</v>
+        <v>1828</v>
       </c>
       <c r="K250" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L250" s="12" t="n">
+        <v>279</v>
+      </c>
+      <c r="M250" s="12" t="n">
+        <v>466</v>
+      </c>
+      <c r="N250" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O250" s="12" t="n">
+        <v>1990</v>
+      </c>
+      <c r="P250" s="12" t="n">
+        <v>3383</v>
+      </c>
+      <c r="Q250" s="12" t="n">
+        <v>6017</v>
+      </c>
+      <c r="R250" s="12" t="n">
+        <v>5042</v>
+      </c>
+      <c r="S250" s="12" t="n">
+        <v>11133</v>
+      </c>
+      <c r="T250" s="12" t="n">
+        <v>8099</v>
+      </c>
+      <c r="U250" s="13" t="n">
+        <v>35664</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="10" t="inlineStr">
+        <is>
+          <t>Burgan</t>
+        </is>
+      </c>
+      <c r="B251" s="11" t="inlineStr">
+        <is>
+          <t>2026 Ç2</t>
+        </is>
+      </c>
+      <c r="C251" s="12" t="n">
+        <v>2109</v>
+      </c>
+      <c r="D251" s="12" t="n">
+        <v>1615</v>
+      </c>
+      <c r="E251" s="12" t="n">
+        <v>6599</v>
+      </c>
+      <c r="F251" s="12" t="n">
+        <v>5219</v>
+      </c>
+      <c r="G251" s="12" t="n">
+        <v>11008</v>
+      </c>
+      <c r="H251" s="12" t="n">
+        <v>8520</v>
+      </c>
+      <c r="I251" s="12" t="n">
+        <v>717</v>
+      </c>
+      <c r="J251" s="12" t="n">
+        <v>1698</v>
+      </c>
+      <c r="K251" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L251" s="12" t="n">
         <v>301</v>
       </c>
-      <c r="M250" s="12" t="n">
+      <c r="M251" s="12" t="n">
         <v>446</v>
       </c>
-      <c r="N250" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O250" s="12" t="n">
+      <c r="N251" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O251" s="12" t="n">
         <v>2826</v>
       </c>
-      <c r="P250" s="12" t="n">
+      <c r="P251" s="12" t="n">
         <v>3313</v>
       </c>
-      <c r="Q250" s="12" t="n">
+      <c r="Q251" s="12" t="n">
         <v>6607</v>
       </c>
-      <c r="R250" s="12" t="n">
+      <c r="R251" s="12" t="n">
         <v>5520</v>
       </c>
-      <c r="S250" s="12" t="n">
+      <c r="S251" s="12" t="n">
         <v>11454</v>
       </c>
-      <c r="T250" s="12" t="n">
+      <c r="T251" s="12" t="n">
         <v>8520</v>
       </c>
-      <c r="U250" s="13" t="n">
+      <c r="U251" s="13" t="n">
         <v>38240</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="6" t="inlineStr">
-        <is>
-          <t>Odea</t>
-        </is>
-      </c>
-      <c r="B251" s="7" t="inlineStr">
-        <is>
-          <t>2021 Ç1</t>
-        </is>
-      </c>
-      <c r="C251" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D251" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E251" s="8" t="n"/>
-      <c r="F251" s="8" t="n"/>
-      <c r="G251" s="8" t="n"/>
-      <c r="H251" s="8" t="n"/>
-      <c r="I251" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="J251" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="K251" s="8" t="n"/>
-      <c r="L251" s="8" t="n"/>
-      <c r="M251" s="8" t="n"/>
-      <c r="N251" s="8" t="n"/>
-      <c r="O251" s="8" t="n">
-        <v>83</v>
-      </c>
-      <c r="P251" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q251" s="8" t="n"/>
-      <c r="R251" s="8" t="n"/>
-      <c r="S251" s="8" t="n"/>
-      <c r="T251" s="8" t="n"/>
-      <c r="U251" s="9" t="n">
-        <v>102</v>
       </c>
     </row>
     <row r="252">
@@ -16948,7 +16972,7 @@
       </c>
       <c r="B252" s="7" t="inlineStr">
         <is>
-          <t>2021 Ç2</t>
+          <t>2021 Ç1</t>
         </is>
       </c>
       <c r="C252" s="8" t="n">
@@ -16993,41 +17017,41 @@
       </c>
       <c r="B253" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç1</t>
+          <t>2021 Ç2</t>
         </is>
       </c>
       <c r="C253" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D253" s="8" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E253" s="8" t="n"/>
       <c r="F253" s="8" t="n"/>
       <c r="G253" s="8" t="n"/>
       <c r="H253" s="8" t="n"/>
       <c r="I253" s="8" t="n">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="J253" s="8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K253" s="8" t="n"/>
       <c r="L253" s="8" t="n"/>
       <c r="M253" s="8" t="n"/>
       <c r="N253" s="8" t="n"/>
       <c r="O253" s="8" t="n">
-        <v>352</v>
+        <v>83</v>
       </c>
       <c r="P253" s="8" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="Q253" s="8" t="n"/>
       <c r="R253" s="8" t="n"/>
       <c r="S253" s="8" t="n"/>
       <c r="T253" s="8" t="n"/>
       <c r="U253" s="9" t="n">
-        <v>394</v>
+        <v>102</v>
       </c>
     </row>
     <row r="254">
@@ -17038,21 +17062,21 @@
       </c>
       <c r="B254" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç2</t>
+          <t>2022 Ç1</t>
         </is>
       </c>
       <c r="C254" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D254" s="8" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E254" s="8" t="n"/>
       <c r="F254" s="8" t="n"/>
       <c r="G254" s="8" t="n"/>
       <c r="H254" s="8" t="n"/>
       <c r="I254" s="8" t="n">
-        <v>245</v>
+        <v>351</v>
       </c>
       <c r="J254" s="8" t="n">
         <v>21</v>
@@ -17062,17 +17086,17 @@
       <c r="M254" s="8" t="n"/>
       <c r="N254" s="8" t="n"/>
       <c r="O254" s="8" t="n">
-        <v>246</v>
+        <v>352</v>
       </c>
       <c r="P254" s="8" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q254" s="8" t="n"/>
       <c r="R254" s="8" t="n"/>
       <c r="S254" s="8" t="n"/>
       <c r="T254" s="8" t="n"/>
       <c r="U254" s="9" t="n">
-        <v>292</v>
+        <v>394</v>
       </c>
     </row>
     <row r="255">
@@ -17083,41 +17107,41 @@
       </c>
       <c r="B255" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç3</t>
+          <t>2022 Ç2</t>
         </is>
       </c>
       <c r="C255" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D255" s="8" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E255" s="8" t="n"/>
       <c r="F255" s="8" t="n"/>
       <c r="G255" s="8" t="n"/>
       <c r="H255" s="8" t="n"/>
       <c r="I255" s="8" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="J255" s="8" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K255" s="8" t="n"/>
       <c r="L255" s="8" t="n"/>
       <c r="M255" s="8" t="n"/>
       <c r="N255" s="8" t="n"/>
       <c r="O255" s="8" t="n">
-        <v>2</v>
+        <v>246</v>
       </c>
       <c r="P255" s="8" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Q255" s="8" t="n"/>
       <c r="R255" s="8" t="n"/>
       <c r="S255" s="8" t="n"/>
       <c r="T255" s="8" t="n"/>
       <c r="U255" s="9" t="n">
-        <v>36</v>
+        <v>292</v>
       </c>
     </row>
     <row r="256">
@@ -17128,41 +17152,41 @@
       </c>
       <c r="B256" s="7" t="inlineStr">
         <is>
-          <t>2023 Ç3</t>
+          <t>2022 Ç3</t>
         </is>
       </c>
       <c r="C256" s="8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D256" s="8" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E256" s="8" t="n"/>
       <c r="F256" s="8" t="n"/>
       <c r="G256" s="8" t="n"/>
       <c r="H256" s="8" t="n"/>
       <c r="I256" s="8" t="n">
-        <v>880</v>
+        <v>0</v>
       </c>
       <c r="J256" s="8" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="K256" s="8" t="n"/>
       <c r="L256" s="8" t="n"/>
       <c r="M256" s="8" t="n"/>
       <c r="N256" s="8" t="n"/>
       <c r="O256" s="8" t="n">
-        <v>880</v>
+        <v>2</v>
       </c>
       <c r="P256" s="8" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="Q256" s="8" t="n"/>
       <c r="R256" s="8" t="n"/>
       <c r="S256" s="8" t="n"/>
       <c r="T256" s="8" t="n"/>
       <c r="U256" s="9" t="n">
-        <v>945</v>
+        <v>36</v>
       </c>
     </row>
     <row r="257">
@@ -17173,41 +17197,41 @@
       </c>
       <c r="B257" s="7" t="inlineStr">
         <is>
-          <t>2024 Ç1</t>
-        </is>
-      </c>
-      <c r="C257" s="8" t="n"/>
-      <c r="D257" s="8" t="n"/>
-      <c r="E257" s="8" t="n">
-        <v>3059</v>
-      </c>
-      <c r="F257" s="8" t="n">
-        <v>6006</v>
-      </c>
+          <t>2023 Ç3</t>
+        </is>
+      </c>
+      <c r="C257" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D257" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E257" s="8" t="n"/>
+      <c r="F257" s="8" t="n"/>
       <c r="G257" s="8" t="n"/>
       <c r="H257" s="8" t="n"/>
-      <c r="I257" s="8" t="n"/>
-      <c r="J257" s="8" t="n"/>
-      <c r="K257" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="L257" s="8" t="n">
-        <v>2</v>
-      </c>
+      <c r="I257" s="8" t="n">
+        <v>880</v>
+      </c>
+      <c r="J257" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="K257" s="8" t="n"/>
+      <c r="L257" s="8" t="n"/>
       <c r="M257" s="8" t="n"/>
       <c r="N257" s="8" t="n"/>
-      <c r="O257" s="8" t="n"/>
-      <c r="P257" s="8" t="n"/>
-      <c r="Q257" s="8" t="n">
-        <v>3078</v>
-      </c>
-      <c r="R257" s="8" t="n">
-        <v>6008</v>
-      </c>
+      <c r="O257" s="8" t="n">
+        <v>880</v>
+      </c>
+      <c r="P257" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q257" s="8" t="n"/>
+      <c r="R257" s="8" t="n"/>
       <c r="S257" s="8" t="n"/>
       <c r="T257" s="8" t="n"/>
       <c r="U257" s="9" t="n">
-        <v>9087</v>
+        <v>945</v>
       </c>
     </row>
     <row r="258">
@@ -17218,16 +17242,16 @@
       </c>
       <c r="B258" s="7" t="inlineStr">
         <is>
-          <t>2025 Ç1</t>
+          <t>2024 Ç1</t>
         </is>
       </c>
       <c r="C258" s="8" t="n"/>
       <c r="D258" s="8" t="n"/>
       <c r="E258" s="8" t="n">
-        <v>2925</v>
+        <v>3059</v>
       </c>
       <c r="F258" s="8" t="n">
-        <v>5543</v>
+        <v>6006</v>
       </c>
       <c r="G258" s="8" t="n"/>
       <c r="H258" s="8" t="n"/>
@@ -17244,84 +17268,60 @@
       <c r="O258" s="8" t="n"/>
       <c r="P258" s="8" t="n"/>
       <c r="Q258" s="8" t="n">
-        <v>2944</v>
+        <v>3078</v>
       </c>
       <c r="R258" s="8" t="n">
-        <v>5545</v>
+        <v>6008</v>
       </c>
       <c r="S258" s="8" t="n"/>
       <c r="T258" s="8" t="n"/>
       <c r="U258" s="9" t="n">
+        <v>9087</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="6" t="inlineStr">
+        <is>
+          <t>Odea</t>
+        </is>
+      </c>
+      <c r="B259" s="7" t="inlineStr">
+        <is>
+          <t>2025 Ç1</t>
+        </is>
+      </c>
+      <c r="C259" s="8" t="n"/>
+      <c r="D259" s="8" t="n"/>
+      <c r="E259" s="8" t="n">
+        <v>2925</v>
+      </c>
+      <c r="F259" s="8" t="n">
+        <v>5543</v>
+      </c>
+      <c r="G259" s="8" t="n"/>
+      <c r="H259" s="8" t="n"/>
+      <c r="I259" s="8" t="n"/>
+      <c r="J259" s="8" t="n"/>
+      <c r="K259" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="L259" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M259" s="8" t="n"/>
+      <c r="N259" s="8" t="n"/>
+      <c r="O259" s="8" t="n"/>
+      <c r="P259" s="8" t="n"/>
+      <c r="Q259" s="8" t="n">
+        <v>2944</v>
+      </c>
+      <c r="R259" s="8" t="n">
+        <v>5545</v>
+      </c>
+      <c r="S259" s="8" t="n"/>
+      <c r="T259" s="8" t="n"/>
+      <c r="U259" s="9" t="n">
         <v>8490</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="10" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="B259" s="11" t="inlineStr">
-        <is>
-          <t>2021 Ç1</t>
-        </is>
-      </c>
-      <c r="C259" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D259" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E259" s="12" t="n">
-        <v>2166</v>
-      </c>
-      <c r="F259" s="12" t="n">
-        <v>1663</v>
-      </c>
-      <c r="G259" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H259" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I259" s="12" t="n">
-        <v>546</v>
-      </c>
-      <c r="J259" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K259" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="L259" s="12" t="n">
-        <v>2277</v>
-      </c>
-      <c r="M259" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="N259" s="12" t="n">
-        <v>622</v>
-      </c>
-      <c r="O259" s="12" t="n">
-        <v>546</v>
-      </c>
-      <c r="P259" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q259" s="12" t="n">
-        <v>4056</v>
-      </c>
-      <c r="R259" s="12" t="n">
-        <v>3940</v>
-      </c>
-      <c r="S259" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="T259" s="12" t="n">
-        <v>622</v>
-      </c>
-      <c r="U259" s="13" t="n">
-        <v>9236</v>
       </c>
     </row>
     <row r="260">
@@ -17332,7 +17332,7 @@
       </c>
       <c r="B260" s="11" t="inlineStr">
         <is>
-          <t>2021 Ç2</t>
+          <t>2021 Ç1</t>
         </is>
       </c>
       <c r="C260" s="12" t="n">
@@ -17401,7 +17401,7 @@
       </c>
       <c r="B261" s="11" t="inlineStr">
         <is>
-          <t>2021 Ç3</t>
+          <t>2021 Ç2</t>
         </is>
       </c>
       <c r="C261" s="12" t="n">
@@ -17470,7 +17470,7 @@
       </c>
       <c r="B262" s="11" t="inlineStr">
         <is>
-          <t>2021 Ç4</t>
+          <t>2021 Ç3</t>
         </is>
       </c>
       <c r="C262" s="12" t="n">
@@ -17539,7 +17539,7 @@
       </c>
       <c r="B263" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç1</t>
+          <t>2021 Ç4</t>
         </is>
       </c>
       <c r="C263" s="12" t="n">
@@ -17549,55 +17549,55 @@
         <v>3</v>
       </c>
       <c r="E263" s="12" t="n">
-        <v>2941</v>
+        <v>2166</v>
       </c>
       <c r="F263" s="12" t="n">
-        <v>2316</v>
+        <v>1663</v>
       </c>
       <c r="G263" s="12" t="n">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="H263" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I263" s="12" t="n">
-        <v>805</v>
+        <v>546</v>
       </c>
       <c r="J263" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K263" s="12" t="n">
-        <v>1593</v>
+        <v>1890</v>
       </c>
       <c r="L263" s="12" t="n">
-        <v>2075</v>
+        <v>2277</v>
       </c>
       <c r="M263" s="12" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="N263" s="12" t="n">
-        <v>694</v>
+        <v>622</v>
       </c>
       <c r="O263" s="12" t="n">
-        <v>805</v>
+        <v>546</v>
       </c>
       <c r="P263" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q263" s="12" t="n">
-        <v>4534</v>
+        <v>4056</v>
       </c>
       <c r="R263" s="12" t="n">
-        <v>4392</v>
+        <v>3940</v>
       </c>
       <c r="S263" s="12" t="n">
-        <v>641</v>
+        <v>65</v>
       </c>
       <c r="T263" s="12" t="n">
-        <v>694</v>
+        <v>622</v>
       </c>
       <c r="U263" s="13" t="n">
-        <v>11080</v>
+        <v>9236</v>
       </c>
     </row>
     <row r="264">
@@ -17608,65 +17608,65 @@
       </c>
       <c r="B264" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç2</t>
+          <t>2022 Ç1</t>
         </is>
       </c>
       <c r="C264" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D264" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E264" s="12" t="n">
-        <v>2881</v>
+        <v>2941</v>
       </c>
       <c r="F264" s="12" t="n">
-        <v>2483</v>
+        <v>2316</v>
       </c>
       <c r="G264" s="12" t="n">
-        <v>686</v>
+        <v>590</v>
       </c>
       <c r="H264" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I264" s="12" t="n">
-        <v>1614</v>
+        <v>805</v>
       </c>
       <c r="J264" s="12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K264" s="12" t="n">
-        <v>2504</v>
+        <v>1593</v>
       </c>
       <c r="L264" s="12" t="n">
-        <v>1298</v>
+        <v>2075</v>
       </c>
       <c r="M264" s="12" t="n">
-        <v>640</v>
+        <v>51</v>
       </c>
       <c r="N264" s="12" t="n">
-        <v>900</v>
+        <v>694</v>
       </c>
       <c r="O264" s="12" t="n">
-        <v>1614</v>
+        <v>805</v>
       </c>
       <c r="P264" s="12" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="Q264" s="12" t="n">
-        <v>5385</v>
+        <v>4534</v>
       </c>
       <c r="R264" s="12" t="n">
-        <v>3780</v>
+        <v>4392</v>
       </c>
       <c r="S264" s="12" t="n">
-        <v>1326</v>
+        <v>641</v>
       </c>
       <c r="T264" s="12" t="n">
-        <v>900</v>
+        <v>694</v>
       </c>
       <c r="U264" s="13" t="n">
-        <v>13030</v>
+        <v>11080</v>
       </c>
     </row>
     <row r="265">
@@ -17677,7 +17677,7 @@
       </c>
       <c r="B265" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç3</t>
+          <t>2022 Ç2</t>
         </is>
       </c>
       <c r="C265" s="12" t="n">
@@ -17687,55 +17687,55 @@
         <v>4</v>
       </c>
       <c r="E265" s="12" t="n">
-        <v>3321</v>
+        <v>2881</v>
       </c>
       <c r="F265" s="12" t="n">
-        <v>3009</v>
+        <v>2483</v>
       </c>
       <c r="G265" s="12" t="n">
-        <v>953</v>
+        <v>686</v>
       </c>
       <c r="H265" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I265" s="12" t="n">
-        <v>1669</v>
+        <v>1614</v>
       </c>
       <c r="J265" s="12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K265" s="12" t="n">
-        <v>2248</v>
+        <v>2504</v>
       </c>
       <c r="L265" s="12" t="n">
-        <v>1732</v>
+        <v>1298</v>
       </c>
       <c r="M265" s="12" t="n">
-        <v>610</v>
+        <v>640</v>
       </c>
       <c r="N265" s="12" t="n">
-        <v>1168</v>
+        <v>900</v>
       </c>
       <c r="O265" s="12" t="n">
-        <v>1669</v>
+        <v>1614</v>
       </c>
       <c r="P265" s="12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Q265" s="12" t="n">
-        <v>5570</v>
+        <v>5385</v>
       </c>
       <c r="R265" s="12" t="n">
-        <v>4741</v>
+        <v>3780</v>
       </c>
       <c r="S265" s="12" t="n">
-        <v>1563</v>
+        <v>1326</v>
       </c>
       <c r="T265" s="12" t="n">
-        <v>1185</v>
+        <v>900</v>
       </c>
       <c r="U265" s="13" t="n">
-        <v>14755</v>
+        <v>13030</v>
       </c>
     </row>
     <row r="266">
@@ -17746,65 +17746,65 @@
       </c>
       <c r="B266" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç4</t>
+          <t>2022 Ç3</t>
         </is>
       </c>
       <c r="C266" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D266" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E266" s="12" t="n">
-        <v>3574</v>
+        <v>3321</v>
       </c>
       <c r="F266" s="12" t="n">
-        <v>3328</v>
+        <v>3009</v>
       </c>
       <c r="G266" s="12" t="n">
-        <v>1007</v>
+        <v>953</v>
       </c>
       <c r="H266" s="12" t="n">
-        <v>270</v>
+        <v>17</v>
       </c>
       <c r="I266" s="12" t="n">
-        <v>2316</v>
+        <v>1669</v>
       </c>
       <c r="J266" s="12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K266" s="12" t="n">
-        <v>2141</v>
+        <v>2248</v>
       </c>
       <c r="L266" s="12" t="n">
-        <v>2336</v>
+        <v>1732</v>
       </c>
       <c r="M266" s="12" t="n">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="N266" s="12" t="n">
-        <v>1357</v>
+        <v>1168</v>
       </c>
       <c r="O266" s="12" t="n">
-        <v>2316</v>
+        <v>1669</v>
       </c>
       <c r="P266" s="12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Q266" s="12" t="n">
-        <v>5716</v>
+        <v>5570</v>
       </c>
       <c r="R266" s="12" t="n">
-        <v>5664</v>
+        <v>4741</v>
       </c>
       <c r="S266" s="12" t="n">
-        <v>1609</v>
+        <v>1563</v>
       </c>
       <c r="T266" s="12" t="n">
-        <v>1627</v>
+        <v>1185</v>
       </c>
       <c r="U266" s="13" t="n">
-        <v>16961</v>
+        <v>14755</v>
       </c>
     </row>
     <row r="267">
@@ -17815,65 +17815,65 @@
       </c>
       <c r="B267" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç1</t>
+          <t>2022 Ç4</t>
         </is>
       </c>
       <c r="C267" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D267" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E267" s="12" t="n">
-        <v>2531</v>
+        <v>3574</v>
       </c>
       <c r="F267" s="12" t="n">
-        <v>3102</v>
+        <v>3328</v>
       </c>
       <c r="G267" s="12" t="n">
-        <v>1080</v>
+        <v>1007</v>
       </c>
       <c r="H267" s="12" t="n">
-        <v>1257</v>
+        <v>270</v>
       </c>
       <c r="I267" s="12" t="n">
-        <v>2393</v>
+        <v>2316</v>
       </c>
       <c r="J267" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K267" s="12" t="n">
-        <v>1994</v>
+        <v>2141</v>
       </c>
       <c r="L267" s="12" t="n">
-        <v>2404</v>
+        <v>2336</v>
       </c>
       <c r="M267" s="12" t="n">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="N267" s="12" t="n">
-        <v>1465</v>
+        <v>1357</v>
       </c>
       <c r="O267" s="12" t="n">
-        <v>2393</v>
+        <v>2316</v>
       </c>
       <c r="P267" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q267" s="12" t="n">
-        <v>4525</v>
+        <v>5716</v>
       </c>
       <c r="R267" s="12" t="n">
-        <v>5506</v>
+        <v>5664</v>
       </c>
       <c r="S267" s="12" t="n">
-        <v>1674</v>
+        <v>1609</v>
       </c>
       <c r="T267" s="12" t="n">
-        <v>2722</v>
+        <v>1627</v>
       </c>
       <c r="U267" s="13" t="n">
-        <v>16850</v>
+        <v>16961</v>
       </c>
     </row>
     <row r="268">
@@ -17884,65 +17884,65 @@
       </c>
       <c r="B268" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç2</t>
+          <t>2023 Ç1</t>
         </is>
       </c>
       <c r="C268" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D268" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E268" s="12" t="n">
-        <v>2164</v>
+        <v>2531</v>
       </c>
       <c r="F268" s="12" t="n">
-        <v>4521</v>
+        <v>3102</v>
       </c>
       <c r="G268" s="12" t="n">
-        <v>1305</v>
+        <v>1080</v>
       </c>
       <c r="H268" s="12" t="n">
-        <v>2307</v>
+        <v>1257</v>
       </c>
       <c r="I268" s="12" t="n">
-        <v>2481</v>
+        <v>2393</v>
       </c>
       <c r="J268" s="12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="K268" s="12" t="n">
-        <v>1672</v>
+        <v>1994</v>
       </c>
       <c r="L268" s="12" t="n">
-        <v>3253</v>
+        <v>2404</v>
       </c>
       <c r="M268" s="12" t="n">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="N268" s="12" t="n">
-        <v>1480</v>
+        <v>1465</v>
       </c>
       <c r="O268" s="12" t="n">
-        <v>2481</v>
+        <v>2393</v>
       </c>
       <c r="P268" s="12" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="Q268" s="12" t="n">
-        <v>3836</v>
+        <v>4525</v>
       </c>
       <c r="R268" s="12" t="n">
-        <v>7774</v>
+        <v>5506</v>
       </c>
       <c r="S268" s="12" t="n">
-        <v>1891</v>
+        <v>1674</v>
       </c>
       <c r="T268" s="12" t="n">
-        <v>3787</v>
+        <v>2722</v>
       </c>
       <c r="U268" s="13" t="n">
-        <v>19814</v>
+        <v>16850</v>
       </c>
     </row>
     <row r="269">
@@ -17953,7 +17953,7 @@
       </c>
       <c r="B269" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç3</t>
+          <t>2023 Ç2</t>
         </is>
       </c>
       <c r="C269" s="12" t="n">
@@ -17963,55 +17963,55 @@
         <v>10</v>
       </c>
       <c r="E269" s="12" t="n">
-        <v>2329</v>
+        <v>2164</v>
       </c>
       <c r="F269" s="12" t="n">
-        <v>4615</v>
+        <v>4521</v>
       </c>
       <c r="G269" s="12" t="n">
-        <v>1753</v>
+        <v>1305</v>
       </c>
       <c r="H269" s="12" t="n">
-        <v>2398</v>
+        <v>2307</v>
       </c>
       <c r="I269" s="12" t="n">
-        <v>2897</v>
+        <v>2481</v>
       </c>
       <c r="J269" s="12" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K269" s="12" t="n">
-        <v>1544</v>
+        <v>1672</v>
       </c>
       <c r="L269" s="12" t="n">
-        <v>3118</v>
+        <v>3253</v>
       </c>
       <c r="M269" s="12" t="n">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="N269" s="12" t="n">
-        <v>577</v>
+        <v>1480</v>
       </c>
       <c r="O269" s="12" t="n">
-        <v>2897</v>
+        <v>2481</v>
       </c>
       <c r="P269" s="12" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="Q269" s="12" t="n">
-        <v>3873</v>
+        <v>3836</v>
       </c>
       <c r="R269" s="12" t="n">
-        <v>7734</v>
+        <v>7774</v>
       </c>
       <c r="S269" s="12" t="n">
-        <v>2336</v>
+        <v>1891</v>
       </c>
       <c r="T269" s="12" t="n">
-        <v>2974</v>
+        <v>3787</v>
       </c>
       <c r="U269" s="13" t="n">
-        <v>19861</v>
+        <v>19814</v>
       </c>
     </row>
     <row r="270">
@@ -18022,65 +18022,65 @@
       </c>
       <c r="B270" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç4</t>
+          <t>2023 Ç3</t>
         </is>
       </c>
       <c r="C270" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D270" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E270" s="12" t="n">
-        <v>3672</v>
+        <v>2329</v>
       </c>
       <c r="F270" s="12" t="n">
-        <v>5386</v>
+        <v>4615</v>
       </c>
       <c r="G270" s="12" t="n">
-        <v>2642</v>
+        <v>1753</v>
       </c>
       <c r="H270" s="12" t="n">
-        <v>2633</v>
+        <v>2398</v>
       </c>
       <c r="I270" s="12" t="n">
-        <v>3988</v>
+        <v>2897</v>
       </c>
       <c r="J270" s="12" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="K270" s="12" t="n">
-        <v>1819</v>
+        <v>1544</v>
       </c>
       <c r="L270" s="12" t="n">
-        <v>3499</v>
+        <v>3118</v>
       </c>
       <c r="M270" s="12" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N270" s="12" t="n">
-        <v>295</v>
+        <v>577</v>
       </c>
       <c r="O270" s="12" t="n">
-        <v>3988</v>
+        <v>2897</v>
       </c>
       <c r="P270" s="12" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="Q270" s="12" t="n">
-        <v>5491</v>
+        <v>3873</v>
       </c>
       <c r="R270" s="12" t="n">
-        <v>8885</v>
+        <v>7734</v>
       </c>
       <c r="S270" s="12" t="n">
-        <v>3223</v>
+        <v>2336</v>
       </c>
       <c r="T270" s="12" t="n">
-        <v>2928</v>
+        <v>2974</v>
       </c>
       <c r="U270" s="13" t="n">
-        <v>24550</v>
+        <v>19861</v>
       </c>
     </row>
     <row r="271">
@@ -18091,65 +18091,65 @@
       </c>
       <c r="B271" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç1</t>
+          <t>2023 Ç4</t>
         </is>
       </c>
       <c r="C271" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D271" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E271" s="12" t="n">
-        <v>5597</v>
+        <v>3672</v>
       </c>
       <c r="F271" s="12" t="n">
-        <v>6274</v>
+        <v>5386</v>
       </c>
       <c r="G271" s="12" t="n">
-        <v>3134</v>
+        <v>2642</v>
       </c>
       <c r="H271" s="12" t="n">
-        <v>2832</v>
+        <v>2633</v>
       </c>
       <c r="I271" s="12" t="n">
-        <v>4117</v>
+        <v>3988</v>
       </c>
       <c r="J271" s="12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K271" s="12" t="n">
-        <v>1846</v>
+        <v>1819</v>
       </c>
       <c r="L271" s="12" t="n">
-        <v>4464</v>
+        <v>3499</v>
       </c>
       <c r="M271" s="12" t="n">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N271" s="12" t="n">
-        <v>329</v>
+        <v>295</v>
       </c>
       <c r="O271" s="12" t="n">
-        <v>4134</v>
+        <v>3988</v>
       </c>
       <c r="P271" s="12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="Q271" s="12" t="n">
-        <v>7444</v>
+        <v>5491</v>
       </c>
       <c r="R271" s="12" t="n">
-        <v>10738</v>
+        <v>8885</v>
       </c>
       <c r="S271" s="12" t="n">
-        <v>3713</v>
+        <v>3223</v>
       </c>
       <c r="T271" s="12" t="n">
-        <v>3161</v>
+        <v>2928</v>
       </c>
       <c r="U271" s="13" t="n">
-        <v>29228</v>
+        <v>24550</v>
       </c>
     </row>
     <row r="272">
@@ -18160,65 +18160,65 @@
       </c>
       <c r="B272" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç2</t>
+          <t>2024 Ç1</t>
         </is>
       </c>
       <c r="C272" s="12" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D272" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E272" s="12" t="n">
-        <v>5898</v>
+        <v>5597</v>
       </c>
       <c r="F272" s="12" t="n">
-        <v>6215</v>
+        <v>6274</v>
       </c>
       <c r="G272" s="12" t="n">
-        <v>3555</v>
+        <v>3134</v>
       </c>
       <c r="H272" s="12" t="n">
-        <v>2940</v>
+        <v>2832</v>
       </c>
       <c r="I272" s="12" t="n">
-        <v>3805</v>
+        <v>4117</v>
       </c>
       <c r="J272" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K272" s="12" t="n">
-        <v>1596</v>
+        <v>1846</v>
       </c>
       <c r="L272" s="12" t="n">
-        <v>1977</v>
+        <v>4464</v>
       </c>
       <c r="M272" s="12" t="n">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="N272" s="12" t="n">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="O272" s="12" t="n">
-        <v>3840</v>
+        <v>4134</v>
       </c>
       <c r="P272" s="12" t="n">
         <v>38</v>
       </c>
       <c r="Q272" s="12" t="n">
-        <v>7494</v>
+        <v>7444</v>
       </c>
       <c r="R272" s="12" t="n">
-        <v>8192</v>
+        <v>10738</v>
       </c>
       <c r="S272" s="12" t="n">
-        <v>4132</v>
+        <v>3713</v>
       </c>
       <c r="T272" s="12" t="n">
-        <v>3280</v>
+        <v>3161</v>
       </c>
       <c r="U272" s="13" t="n">
-        <v>26976</v>
+        <v>29228</v>
       </c>
     </row>
     <row r="273">
@@ -18229,65 +18229,65 @@
       </c>
       <c r="B273" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç3</t>
+          <t>2024 Ç2</t>
         </is>
       </c>
       <c r="C273" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D273" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E273" s="12" t="n">
-        <v>6672</v>
+        <v>5898</v>
       </c>
       <c r="F273" s="12" t="n">
-        <v>6599</v>
+        <v>6215</v>
       </c>
       <c r="G273" s="12" t="n">
-        <v>3769</v>
+        <v>3555</v>
       </c>
       <c r="H273" s="12" t="n">
-        <v>2997</v>
+        <v>2940</v>
       </c>
       <c r="I273" s="12" t="n">
-        <v>4514</v>
+        <v>3805</v>
       </c>
       <c r="J273" s="12" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K273" s="12" t="n">
-        <v>1439</v>
+        <v>1596</v>
       </c>
       <c r="L273" s="12" t="n">
-        <v>1231</v>
+        <v>1977</v>
       </c>
       <c r="M273" s="12" t="n">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N273" s="12" t="n">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="O273" s="12" t="n">
-        <v>4534</v>
+        <v>3840</v>
       </c>
       <c r="P273" s="12" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="Q273" s="12" t="n">
-        <v>8110</v>
+        <v>7494</v>
       </c>
       <c r="R273" s="12" t="n">
-        <v>7830</v>
+        <v>8192</v>
       </c>
       <c r="S273" s="12" t="n">
-        <v>4345</v>
+        <v>4132</v>
       </c>
       <c r="T273" s="12" t="n">
-        <v>3356</v>
+        <v>3280</v>
       </c>
       <c r="U273" s="13" t="n">
-        <v>28216</v>
+        <v>26976</v>
       </c>
     </row>
     <row r="274">
@@ -18298,65 +18298,65 @@
       </c>
       <c r="B274" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç4</t>
+          <t>2024 Ç3</t>
         </is>
       </c>
       <c r="C274" s="12" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D274" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E274" s="12" t="n">
-        <v>8060</v>
+        <v>6672</v>
       </c>
       <c r="F274" s="12" t="n">
-        <v>6427</v>
+        <v>6599</v>
       </c>
       <c r="G274" s="12" t="n">
-        <v>3918</v>
+        <v>3769</v>
       </c>
       <c r="H274" s="12" t="n">
-        <v>3164</v>
+        <v>2997</v>
       </c>
       <c r="I274" s="12" t="n">
-        <v>5692</v>
+        <v>4514</v>
       </c>
       <c r="J274" s="12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K274" s="12" t="n">
-        <v>1348</v>
+        <v>1439</v>
       </c>
       <c r="L274" s="12" t="n">
-        <v>1661</v>
+        <v>1231</v>
       </c>
       <c r="M274" s="12" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N274" s="12" t="n">
-        <v>0</v>
+        <v>359</v>
       </c>
       <c r="O274" s="12" t="n">
-        <v>5724</v>
+        <v>4534</v>
       </c>
       <c r="P274" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q274" s="12" t="n">
-        <v>9409</v>
+        <v>8110</v>
       </c>
       <c r="R274" s="12" t="n">
-        <v>8088</v>
+        <v>7830</v>
       </c>
       <c r="S274" s="12" t="n">
-        <v>4493</v>
+        <v>4345</v>
       </c>
       <c r="T274" s="12" t="n">
-        <v>3164</v>
+        <v>3356</v>
       </c>
       <c r="U274" s="13" t="n">
-        <v>30915</v>
+        <v>28216</v>
       </c>
     </row>
     <row r="275">
@@ -18367,65 +18367,65 @@
       </c>
       <c r="B275" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç1</t>
+          <t>2024 Ç4</t>
         </is>
       </c>
       <c r="C275" s="12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D275" s="12" t="n">
         <v>8</v>
       </c>
       <c r="E275" s="12" t="n">
-        <v>9734</v>
+        <v>8060</v>
       </c>
       <c r="F275" s="12" t="n">
-        <v>6509</v>
+        <v>6427</v>
       </c>
       <c r="G275" s="12" t="n">
-        <v>4158</v>
+        <v>3918</v>
       </c>
       <c r="H275" s="12" t="n">
-        <v>3322</v>
+        <v>3164</v>
       </c>
       <c r="I275" s="12" t="n">
-        <v>4809</v>
+        <v>5692</v>
       </c>
       <c r="J275" s="12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K275" s="12" t="n">
-        <v>1334</v>
+        <v>1348</v>
       </c>
       <c r="L275" s="12" t="n">
-        <v>2172</v>
+        <v>1661</v>
       </c>
       <c r="M275" s="12" t="n">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N275" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O275" s="12" t="n">
-        <v>4834</v>
+        <v>5724</v>
       </c>
       <c r="P275" s="12" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="Q275" s="12" t="n">
-        <v>11068</v>
+        <v>9409</v>
       </c>
       <c r="R275" s="12" t="n">
-        <v>8681</v>
+        <v>8088</v>
       </c>
       <c r="S275" s="12" t="n">
-        <v>4732</v>
+        <v>4493</v>
       </c>
       <c r="T275" s="12" t="n">
-        <v>3322</v>
+        <v>3164</v>
       </c>
       <c r="U275" s="13" t="n">
-        <v>32678</v>
+        <v>30915</v>
       </c>
     </row>
     <row r="276">
@@ -18436,38 +18436,38 @@
       </c>
       <c r="B276" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç2</t>
+          <t>2025 Ç1</t>
         </is>
       </c>
       <c r="C276" s="12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D276" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E276" s="12" t="n">
-        <v>11294</v>
+        <v>9734</v>
       </c>
       <c r="F276" s="12" t="n">
-        <v>7122</v>
+        <v>6509</v>
       </c>
       <c r="G276" s="12" t="n">
-        <v>2001</v>
+        <v>4158</v>
       </c>
       <c r="H276" s="12" t="n">
-        <v>2474</v>
+        <v>3322</v>
       </c>
       <c r="I276" s="12" t="n">
-        <v>5259</v>
+        <v>4809</v>
       </c>
       <c r="J276" s="12" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K276" s="12" t="n">
-        <v>972</v>
+        <v>1334</v>
       </c>
       <c r="L276" s="12" t="n">
-        <v>2157</v>
+        <v>2172</v>
       </c>
       <c r="M276" s="12" t="n">
         <v>574</v>
@@ -18476,25 +18476,25 @@
         <v>0</v>
       </c>
       <c r="O276" s="12" t="n">
-        <v>5259</v>
+        <v>4834</v>
       </c>
       <c r="P276" s="12" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q276" s="12" t="n">
-        <v>12266</v>
+        <v>11068</v>
       </c>
       <c r="R276" s="12" t="n">
-        <v>9280</v>
+        <v>8681</v>
       </c>
       <c r="S276" s="12" t="n">
-        <v>2575</v>
+        <v>4732</v>
       </c>
       <c r="T276" s="12" t="n">
-        <v>2474</v>
+        <v>3322</v>
       </c>
       <c r="U276" s="13" t="n">
-        <v>31898</v>
+        <v>32678</v>
       </c>
     </row>
     <row r="277">
@@ -18505,7 +18505,7 @@
       </c>
       <c r="B277" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç3</t>
+          <t>2025 Ç2</t>
         </is>
       </c>
       <c r="C277" s="12" t="n">
@@ -18515,55 +18515,55 @@
         <v>10</v>
       </c>
       <c r="E277" s="12" t="n">
-        <v>13376</v>
+        <v>11294</v>
       </c>
       <c r="F277" s="12" t="n">
-        <v>7919</v>
+        <v>7122</v>
       </c>
       <c r="G277" s="12" t="n">
-        <v>3269</v>
+        <v>2001</v>
       </c>
       <c r="H277" s="12" t="n">
-        <v>2539</v>
+        <v>2474</v>
       </c>
       <c r="I277" s="12" t="n">
-        <v>5683</v>
+        <v>5259</v>
       </c>
       <c r="J277" s="12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K277" s="12" t="n">
-        <v>450</v>
+        <v>972</v>
       </c>
       <c r="L277" s="12" t="n">
-        <v>2126</v>
+        <v>2157</v>
       </c>
       <c r="M277" s="12" t="n">
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="N277" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O277" s="12" t="n">
-        <v>5683</v>
+        <v>5259</v>
       </c>
       <c r="P277" s="12" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="Q277" s="12" t="n">
-        <v>13827</v>
+        <v>12266</v>
       </c>
       <c r="R277" s="12" t="n">
-        <v>10045</v>
+        <v>9280</v>
       </c>
       <c r="S277" s="12" t="n">
-        <v>3269</v>
+        <v>2575</v>
       </c>
       <c r="T277" s="12" t="n">
-        <v>2539</v>
+        <v>2474</v>
       </c>
       <c r="U277" s="13" t="n">
-        <v>35410</v>
+        <v>31898</v>
       </c>
     </row>
     <row r="278">
@@ -18574,38 +18574,38 @@
       </c>
       <c r="B278" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç4</t>
+          <t>2025 Ç3</t>
         </is>
       </c>
       <c r="C278" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D278" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E278" s="12" t="n">
-        <v>16627</v>
+        <v>13376</v>
       </c>
       <c r="F278" s="12" t="n">
-        <v>8691</v>
+        <v>7919</v>
       </c>
       <c r="G278" s="12" t="n">
-        <v>3263</v>
+        <v>3269</v>
       </c>
       <c r="H278" s="12" t="n">
-        <v>2673</v>
+        <v>2539</v>
       </c>
       <c r="I278" s="12" t="n">
-        <v>6366</v>
+        <v>5683</v>
       </c>
       <c r="J278" s="12" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K278" s="12" t="n">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="L278" s="12" t="n">
-        <v>3764</v>
+        <v>2126</v>
       </c>
       <c r="M278" s="12" t="n">
         <v>0</v>
@@ -18614,25 +18614,25 @@
         <v>0</v>
       </c>
       <c r="O278" s="12" t="n">
-        <v>6366</v>
+        <v>5683</v>
       </c>
       <c r="P278" s="12" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="Q278" s="12" t="n">
-        <v>16978</v>
+        <v>13827</v>
       </c>
       <c r="R278" s="12" t="n">
-        <v>12455</v>
+        <v>10045</v>
       </c>
       <c r="S278" s="12" t="n">
-        <v>3263</v>
+        <v>3269</v>
       </c>
       <c r="T278" s="12" t="n">
-        <v>2673</v>
+        <v>2539</v>
       </c>
       <c r="U278" s="13" t="n">
-        <v>41795</v>
+        <v>35410</v>
       </c>
     </row>
     <row r="279">
@@ -18643,7 +18643,7 @@
       </c>
       <c r="B279" s="11" t="inlineStr">
         <is>
-          <t>2026 Ç1</t>
+          <t>2025 Ç4</t>
         </is>
       </c>
       <c r="C279" s="12" t="n">
@@ -18653,55 +18653,55 @@
         <v>11</v>
       </c>
       <c r="E279" s="12" t="n">
-        <v>13091</v>
+        <v>16627</v>
       </c>
       <c r="F279" s="12" t="n">
-        <v>8627</v>
+        <v>8691</v>
       </c>
       <c r="G279" s="12" t="n">
-        <v>3729</v>
+        <v>3263</v>
       </c>
       <c r="H279" s="12" t="n">
-        <v>2248</v>
+        <v>2673</v>
       </c>
       <c r="I279" s="12" t="n">
-        <v>6794</v>
+        <v>6366</v>
       </c>
       <c r="J279" s="12" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="K279" s="12" t="n">
         <v>350</v>
       </c>
       <c r="L279" s="12" t="n">
-        <v>2825</v>
+        <v>3764</v>
       </c>
       <c r="M279" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N279" s="12" t="n">
-        <v>446</v>
+        <v>0</v>
       </c>
       <c r="O279" s="12" t="n">
-        <v>6794</v>
+        <v>6366</v>
       </c>
       <c r="P279" s="12" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="Q279" s="12" t="n">
-        <v>13441</v>
+        <v>16978</v>
       </c>
       <c r="R279" s="12" t="n">
-        <v>11452</v>
+        <v>12455</v>
       </c>
       <c r="S279" s="12" t="n">
-        <v>3729</v>
+        <v>3263</v>
       </c>
       <c r="T279" s="12" t="n">
-        <v>2694</v>
+        <v>2673</v>
       </c>
       <c r="U279" s="13" t="n">
-        <v>38163</v>
+        <v>41795</v>
       </c>
     </row>
     <row r="280">
@@ -18712,7 +18712,7 @@
       </c>
       <c r="B280" s="11" t="inlineStr">
         <is>
-          <t>2026 Ç2</t>
+          <t>2026 Ç1</t>
         </is>
       </c>
       <c r="C280" s="12" t="n">
@@ -18722,120 +18722,120 @@
         <v>11</v>
       </c>
       <c r="E280" s="12" t="n">
+        <v>13091</v>
+      </c>
+      <c r="F280" s="12" t="n">
+        <v>8627</v>
+      </c>
+      <c r="G280" s="12" t="n">
+        <v>3729</v>
+      </c>
+      <c r="H280" s="12" t="n">
+        <v>2248</v>
+      </c>
+      <c r="I280" s="12" t="n">
+        <v>6794</v>
+      </c>
+      <c r="J280" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="K280" s="12" t="n">
+        <v>350</v>
+      </c>
+      <c r="L280" s="12" t="n">
+        <v>2825</v>
+      </c>
+      <c r="M280" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" s="12" t="n">
+        <v>446</v>
+      </c>
+      <c r="O280" s="12" t="n">
+        <v>6794</v>
+      </c>
+      <c r="P280" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q280" s="12" t="n">
+        <v>13441</v>
+      </c>
+      <c r="R280" s="12" t="n">
+        <v>11452</v>
+      </c>
+      <c r="S280" s="12" t="n">
+        <v>3729</v>
+      </c>
+      <c r="T280" s="12" t="n">
+        <v>2694</v>
+      </c>
+      <c r="U280" s="13" t="n">
+        <v>38163</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="10" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="B281" s="11" t="inlineStr">
+        <is>
+          <t>2026 Ç2</t>
+        </is>
+      </c>
+      <c r="C281" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D281" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E281" s="12" t="n">
         <v>15117</v>
       </c>
-      <c r="F280" s="12" t="n">
+      <c r="F281" s="12" t="n">
         <v>9079</v>
       </c>
-      <c r="G280" s="12" t="n">
+      <c r="G281" s="12" t="n">
         <v>4446</v>
       </c>
-      <c r="H280" s="12" t="n">
+      <c r="H281" s="12" t="n">
         <v>2406</v>
       </c>
-      <c r="I280" s="12" t="n"/>
-      <c r="J280" s="12" t="n">
+      <c r="I281" s="12" t="n"/>
+      <c r="J281" s="12" t="n">
         <v>-13</v>
       </c>
-      <c r="K280" s="12" t="n">
+      <c r="K281" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L280" s="12" t="n">
+      <c r="L281" s="12" t="n">
         <v>2879</v>
       </c>
-      <c r="M280" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N280" s="12" t="n">
+      <c r="M281" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N281" s="12" t="n">
         <v>468</v>
       </c>
-      <c r="O280" s="12" t="n"/>
-      <c r="P280" s="12" t="n">
+      <c r="O281" s="12" t="n"/>
+      <c r="P281" s="12" t="n">
         <v>-2</v>
       </c>
-      <c r="Q280" s="12" t="n">
+      <c r="Q281" s="12" t="n">
         <v>15139</v>
       </c>
-      <c r="R280" s="12" t="n">
+      <c r="R281" s="12" t="n">
         <v>11958</v>
       </c>
-      <c r="S280" s="12" t="n">
+      <c r="S281" s="12" t="n">
         <v>4446</v>
       </c>
-      <c r="T280" s="12" t="n">
+      <c r="T281" s="12" t="n">
         <v>2874</v>
       </c>
-      <c r="U280" s="13" t="n">
+      <c r="U281" s="13" t="n">
         <v>41788</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="6" t="inlineStr">
-        <is>
-          <t>HSBC</t>
-        </is>
-      </c>
-      <c r="B281" s="7" t="inlineStr">
-        <is>
-          <t>2022 Ç3</t>
-        </is>
-      </c>
-      <c r="C281" s="8" t="n">
-        <v>312</v>
-      </c>
-      <c r="D281" s="8" t="n">
-        <v>222</v>
-      </c>
-      <c r="E281" s="8" t="n">
-        <v>3528</v>
-      </c>
-      <c r="F281" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G281" s="8" t="n">
-        <v>2432</v>
-      </c>
-      <c r="H281" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I281" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J281" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K281" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L281" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M281" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N281" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O281" s="8" t="n">
-        <v>316</v>
-      </c>
-      <c r="P281" s="8" t="n">
-        <v>222</v>
-      </c>
-      <c r="Q281" s="8" t="n">
-        <v>3528</v>
-      </c>
-      <c r="R281" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S281" s="8" t="n">
-        <v>2432</v>
-      </c>
-      <c r="T281" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U281" s="9" t="n">
-        <v>6498</v>
       </c>
     </row>
     <row r="282">
@@ -18846,23 +18846,23 @@
       </c>
       <c r="B282" s="7" t="inlineStr">
         <is>
-          <t>2023 Ç3</t>
+          <t>2022 Ç3</t>
         </is>
       </c>
       <c r="C282" s="8" t="n">
-        <v>568</v>
+        <v>312</v>
       </c>
       <c r="D282" s="8" t="n">
-        <v>272</v>
+        <v>222</v>
       </c>
       <c r="E282" s="8" t="n">
-        <v>5967</v>
+        <v>3528</v>
       </c>
       <c r="F282" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G282" s="8" t="n">
-        <v>3500</v>
+        <v>2432</v>
       </c>
       <c r="H282" s="8" t="n">
         <v>0</v>
@@ -18886,82 +18886,94 @@
         <v>0</v>
       </c>
       <c r="O282" s="8" t="n">
+        <v>316</v>
+      </c>
+      <c r="P282" s="8" t="n">
+        <v>222</v>
+      </c>
+      <c r="Q282" s="8" t="n">
+        <v>3528</v>
+      </c>
+      <c r="R282" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S282" s="8" t="n">
+        <v>2432</v>
+      </c>
+      <c r="T282" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U282" s="9" t="n">
+        <v>6498</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="6" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="B283" s="7" t="inlineStr">
+        <is>
+          <t>2023 Ç3</t>
+        </is>
+      </c>
+      <c r="C283" s="8" t="n">
+        <v>568</v>
+      </c>
+      <c r="D283" s="8" t="n">
+        <v>272</v>
+      </c>
+      <c r="E283" s="8" t="n">
+        <v>5967</v>
+      </c>
+      <c r="F283" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" s="8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H283" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I283" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J283" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K283" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L283" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M283" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N283" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" s="8" t="n">
         <v>572</v>
       </c>
-      <c r="P282" s="8" t="n">
+      <c r="P283" s="8" t="n">
         <v>272</v>
       </c>
-      <c r="Q282" s="8" t="n">
+      <c r="Q283" s="8" t="n">
         <v>5967</v>
       </c>
-      <c r="R282" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S282" s="8" t="n">
+      <c r="R283" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S283" s="8" t="n">
         <v>3500</v>
       </c>
-      <c r="T282" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U282" s="9" t="n">
+      <c r="T283" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U283" s="9" t="n">
         <v>10311</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="10" t="inlineStr">
-        <is>
-          <t>ABank</t>
-        </is>
-      </c>
-      <c r="B283" s="11" t="inlineStr">
-        <is>
-          <t>2021 Ç1</t>
-        </is>
-      </c>
-      <c r="C283" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="D283" s="12" t="n">
-        <v>315</v>
-      </c>
-      <c r="E283" s="12" t="n"/>
-      <c r="F283" s="12" t="n"/>
-      <c r="G283" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="H283" s="12" t="n">
-        <v>5807</v>
-      </c>
-      <c r="I283" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J283" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K283" s="12" t="n"/>
-      <c r="L283" s="12" t="n"/>
-      <c r="M283" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N283" s="12" t="n">
-        <v>95</v>
-      </c>
-      <c r="O283" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="P283" s="12" t="n">
-        <v>315</v>
-      </c>
-      <c r="Q283" s="12" t="n"/>
-      <c r="R283" s="12" t="n"/>
-      <c r="S283" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="T283" s="12" t="n">
-        <v>5903</v>
-      </c>
-      <c r="U283" s="13" t="n">
-        <v>5993</v>
       </c>
     </row>
     <row r="284">
@@ -18972,11 +18984,11 @@
       </c>
       <c r="B284" s="11" t="inlineStr">
         <is>
-          <t>2021 Ç2</t>
+          <t>2021 Ç1</t>
         </is>
       </c>
       <c r="C284" s="12" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D284" s="12" t="n">
         <v>315</v>
@@ -19004,7 +19016,7 @@
         <v>95</v>
       </c>
       <c r="O284" s="12" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="P284" s="12" t="n">
         <v>315</v>
@@ -19029,11 +19041,11 @@
       </c>
       <c r="B285" s="11" t="inlineStr">
         <is>
-          <t>2021 Ç3</t>
+          <t>2021 Ç2</t>
         </is>
       </c>
       <c r="C285" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D285" s="12" t="n">
         <v>315</v>
@@ -19061,7 +19073,7 @@
         <v>95</v>
       </c>
       <c r="O285" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P285" s="12" t="n">
         <v>315</v>
@@ -19086,21 +19098,17 @@
       </c>
       <c r="B286" s="11" t="inlineStr">
         <is>
-          <t>2021 Ç4</t>
+          <t>2021 Ç3</t>
         </is>
       </c>
       <c r="C286" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D286" s="12" t="n">
         <v>315</v>
       </c>
-      <c r="E286" s="12" t="n">
-        <v>1134</v>
-      </c>
-      <c r="F286" s="12" t="n">
-        <v>1517</v>
-      </c>
+      <c r="E286" s="12" t="n"/>
+      <c r="F286" s="12" t="n"/>
       <c r="G286" s="12" t="n">
         <v>76</v>
       </c>
@@ -19113,12 +19121,8 @@
       <c r="J286" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K286" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="L286" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="K286" s="12" t="n"/>
+      <c r="L286" s="12" t="n"/>
       <c r="M286" s="12" t="n">
         <v>0</v>
       </c>
@@ -19126,17 +19130,13 @@
         <v>95</v>
       </c>
       <c r="O286" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P286" s="12" t="n">
         <v>315</v>
       </c>
-      <c r="Q286" s="12" t="n">
-        <v>1185</v>
-      </c>
-      <c r="R286" s="12" t="n">
-        <v>1517</v>
-      </c>
+      <c r="Q286" s="12" t="n"/>
+      <c r="R286" s="12" t="n"/>
       <c r="S286" s="12" t="n">
         <v>76</v>
       </c>
@@ -19144,7 +19144,7 @@
         <v>5903</v>
       </c>
       <c r="U286" s="13" t="n">
-        <v>8695</v>
+        <v>5993</v>
       </c>
     </row>
     <row r="287">
@@ -19155,47 +19155,65 @@
       </c>
       <c r="B287" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç1</t>
-        </is>
-      </c>
-      <c r="C287" s="12" t="n"/>
+          <t>2021 Ç4</t>
+        </is>
+      </c>
+      <c r="C287" s="12" t="n">
+        <v>23</v>
+      </c>
       <c r="D287" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E287" s="12" t="n"/>
-      <c r="F287" s="12" t="n"/>
+        <v>315</v>
+      </c>
+      <c r="E287" s="12" t="n">
+        <v>1134</v>
+      </c>
+      <c r="F287" s="12" t="n">
+        <v>1517</v>
+      </c>
       <c r="G287" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H287" s="12" t="n">
-        <v>6130</v>
-      </c>
-      <c r="I287" s="12" t="n"/>
+        <v>5807</v>
+      </c>
+      <c r="I287" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="J287" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K287" s="12" t="n"/>
-      <c r="L287" s="12" t="n"/>
+      <c r="K287" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="L287" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="M287" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N287" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O287" s="12" t="n"/>
+        <v>95</v>
+      </c>
+      <c r="O287" s="12" t="n">
+        <v>23</v>
+      </c>
       <c r="P287" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q287" s="12" t="n"/>
-      <c r="R287" s="12" t="n"/>
+        <v>315</v>
+      </c>
+      <c r="Q287" s="12" t="n">
+        <v>1185</v>
+      </c>
+      <c r="R287" s="12" t="n">
+        <v>1517</v>
+      </c>
       <c r="S287" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="T287" s="12" t="n">
-        <v>6130</v>
+        <v>5903</v>
       </c>
       <c r="U287" s="13" t="n">
-        <v>6228</v>
+        <v>8695</v>
       </c>
     </row>
     <row r="288">
@@ -19206,21 +19224,25 @@
       </c>
       <c r="B288" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç2</t>
+          <t>2022 Ç1</t>
         </is>
       </c>
       <c r="C288" s="12" t="n"/>
-      <c r="D288" s="12" t="n"/>
+      <c r="D288" s="12" t="n">
+        <v>5</v>
+      </c>
       <c r="E288" s="12" t="n"/>
       <c r="F288" s="12" t="n"/>
       <c r="G288" s="12" t="n">
-        <v>182</v>
+        <v>74</v>
       </c>
       <c r="H288" s="12" t="n">
-        <v>7056</v>
+        <v>6130</v>
       </c>
       <c r="I288" s="12" t="n"/>
-      <c r="J288" s="12" t="n"/>
+      <c r="J288" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="K288" s="12" t="n"/>
       <c r="L288" s="12" t="n"/>
       <c r="M288" s="12" t="n">
@@ -19230,17 +19252,19 @@
         <v>0</v>
       </c>
       <c r="O288" s="12" t="n"/>
-      <c r="P288" s="12" t="n"/>
+      <c r="P288" s="12" t="n">
+        <v>5</v>
+      </c>
       <c r="Q288" s="12" t="n"/>
       <c r="R288" s="12" t="n"/>
       <c r="S288" s="12" t="n">
-        <v>182</v>
+        <v>74</v>
       </c>
       <c r="T288" s="12" t="n">
-        <v>7056</v>
+        <v>6130</v>
       </c>
       <c r="U288" s="13" t="n">
-        <v>7658</v>
+        <v>6228</v>
       </c>
     </row>
     <row r="289">
@@ -19251,7 +19275,7 @@
       </c>
       <c r="B289" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç3</t>
+          <t>2022 Ç2</t>
         </is>
       </c>
       <c r="C289" s="12" t="n"/>
@@ -19259,10 +19283,10 @@
       <c r="E289" s="12" t="n"/>
       <c r="F289" s="12" t="n"/>
       <c r="G289" s="12" t="n">
-        <v>796</v>
+        <v>182</v>
       </c>
       <c r="H289" s="12" t="n">
-        <v>5128</v>
+        <v>7056</v>
       </c>
       <c r="I289" s="12" t="n"/>
       <c r="J289" s="12" t="n"/>
@@ -19279,13 +19303,13 @@
       <c r="Q289" s="12" t="n"/>
       <c r="R289" s="12" t="n"/>
       <c r="S289" s="12" t="n">
-        <v>796</v>
+        <v>182</v>
       </c>
       <c r="T289" s="12" t="n">
-        <v>5128</v>
+        <v>7056</v>
       </c>
       <c r="U289" s="13" t="n">
-        <v>6446</v>
+        <v>7658</v>
       </c>
     </row>
     <row r="290">
@@ -19296,53 +19320,41 @@
       </c>
       <c r="B290" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç4</t>
+          <t>2022 Ç3</t>
         </is>
       </c>
       <c r="C290" s="12" t="n"/>
       <c r="D290" s="12" t="n"/>
-      <c r="E290" s="12" t="n">
-        <v>2048</v>
-      </c>
-      <c r="F290" s="12" t="n">
-        <v>2049</v>
-      </c>
+      <c r="E290" s="12" t="n"/>
+      <c r="F290" s="12" t="n"/>
       <c r="G290" s="12" t="n">
-        <v>1502</v>
+        <v>796</v>
       </c>
       <c r="H290" s="12" t="n">
-        <v>5146</v>
+        <v>5128</v>
       </c>
       <c r="I290" s="12" t="n"/>
       <c r="J290" s="12" t="n"/>
-      <c r="K290" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="L290" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="K290" s="12" t="n"/>
+      <c r="L290" s="12" t="n"/>
       <c r="M290" s="12" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="N290" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O290" s="12" t="n"/>
       <c r="P290" s="12" t="n"/>
-      <c r="Q290" s="12" t="n">
-        <v>2086</v>
-      </c>
-      <c r="R290" s="12" t="n">
-        <v>2049</v>
-      </c>
+      <c r="Q290" s="12" t="n"/>
+      <c r="R290" s="12" t="n"/>
       <c r="S290" s="12" t="n">
-        <v>1862</v>
+        <v>796</v>
       </c>
       <c r="T290" s="12" t="n">
-        <v>5146</v>
+        <v>5128</v>
       </c>
       <c r="U290" s="13" t="n">
-        <v>11766</v>
+        <v>6446</v>
       </c>
     </row>
     <row r="291">
@@ -19353,47 +19365,53 @@
       </c>
       <c r="B291" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç1</t>
+          <t>2022 Ç4</t>
         </is>
       </c>
       <c r="C291" s="12" t="n"/>
-      <c r="D291" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="E291" s="12" t="n"/>
-      <c r="F291" s="12" t="n"/>
+      <c r="D291" s="12" t="n"/>
+      <c r="E291" s="12" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F291" s="12" t="n">
+        <v>2049</v>
+      </c>
       <c r="G291" s="12" t="n">
-        <v>1542</v>
+        <v>1502</v>
       </c>
       <c r="H291" s="12" t="n">
-        <v>5294</v>
+        <v>5146</v>
       </c>
       <c r="I291" s="12" t="n"/>
-      <c r="J291" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K291" s="12" t="n"/>
-      <c r="L291" s="12" t="n"/>
+      <c r="J291" s="12" t="n"/>
+      <c r="K291" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="L291" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="M291" s="12" t="n">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="N291" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O291" s="12" t="n"/>
-      <c r="P291" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q291" s="12" t="n"/>
-      <c r="R291" s="12" t="n"/>
+      <c r="P291" s="12" t="n"/>
+      <c r="Q291" s="12" t="n">
+        <v>2086</v>
+      </c>
+      <c r="R291" s="12" t="n">
+        <v>2049</v>
+      </c>
       <c r="S291" s="12" t="n">
-        <v>1893</v>
+        <v>1862</v>
       </c>
       <c r="T291" s="12" t="n">
-        <v>5294</v>
+        <v>5146</v>
       </c>
       <c r="U291" s="13" t="n">
-        <v>7219</v>
+        <v>11766</v>
       </c>
     </row>
     <row r="292">
@@ -19404,20 +19422,20 @@
       </c>
       <c r="B292" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç2</t>
+          <t>2023 Ç1</t>
         </is>
       </c>
       <c r="C292" s="12" t="n"/>
       <c r="D292" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E292" s="12" t="n"/>
       <c r="F292" s="12" t="n"/>
       <c r="G292" s="12" t="n">
-        <v>1300</v>
+        <v>1542</v>
       </c>
       <c r="H292" s="12" t="n">
-        <v>7093</v>
+        <v>5294</v>
       </c>
       <c r="I292" s="12" t="n"/>
       <c r="J292" s="12" t="n">
@@ -19426,25 +19444,25 @@
       <c r="K292" s="12" t="n"/>
       <c r="L292" s="12" t="n"/>
       <c r="M292" s="12" t="n">
-        <v>230</v>
+        <v>351</v>
       </c>
       <c r="N292" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O292" s="12" t="n"/>
       <c r="P292" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q292" s="12" t="n"/>
       <c r="R292" s="12" t="n"/>
       <c r="S292" s="12" t="n">
-        <v>1530</v>
+        <v>1893</v>
       </c>
       <c r="T292" s="12" t="n">
-        <v>7093</v>
+        <v>5294</v>
       </c>
       <c r="U292" s="13" t="n">
-        <v>8668</v>
+        <v>7219</v>
       </c>
     </row>
     <row r="293">
@@ -19455,7 +19473,7 @@
       </c>
       <c r="B293" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç3</t>
+          <t>2023 Ç2</t>
         </is>
       </c>
       <c r="C293" s="12" t="n"/>
@@ -19465,10 +19483,10 @@
       <c r="E293" s="12" t="n"/>
       <c r="F293" s="12" t="n"/>
       <c r="G293" s="12" t="n">
-        <v>1393</v>
+        <v>1300</v>
       </c>
       <c r="H293" s="12" t="n">
-        <v>7554</v>
+        <v>7093</v>
       </c>
       <c r="I293" s="12" t="n"/>
       <c r="J293" s="12" t="n">
@@ -19477,7 +19495,7 @@
       <c r="K293" s="12" t="n"/>
       <c r="L293" s="12" t="n"/>
       <c r="M293" s="12" t="n">
-        <v>102</v>
+        <v>230</v>
       </c>
       <c r="N293" s="12" t="n">
         <v>0</v>
@@ -19489,13 +19507,13 @@
       <c r="Q293" s="12" t="n"/>
       <c r="R293" s="12" t="n"/>
       <c r="S293" s="12" t="n">
-        <v>1495</v>
+        <v>1530</v>
       </c>
       <c r="T293" s="12" t="n">
-        <v>7554</v>
+        <v>7093</v>
       </c>
       <c r="U293" s="13" t="n">
-        <v>9068</v>
+        <v>8668</v>
       </c>
     </row>
     <row r="294">
@@ -19506,59 +19524,47 @@
       </c>
       <c r="B294" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç4</t>
+          <t>2023 Ç3</t>
         </is>
       </c>
       <c r="C294" s="12" t="n"/>
       <c r="D294" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="E294" s="12" t="n">
-        <v>3284</v>
-      </c>
-      <c r="F294" s="12" t="n">
-        <v>3523</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E294" s="12" t="n"/>
+      <c r="F294" s="12" t="n"/>
       <c r="G294" s="12" t="n">
-        <v>1448</v>
+        <v>1393</v>
       </c>
       <c r="H294" s="12" t="n">
-        <v>8073</v>
+        <v>7554</v>
       </c>
       <c r="I294" s="12" t="n"/>
       <c r="J294" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K294" s="12" t="n">
-        <v>167</v>
-      </c>
-      <c r="L294" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="K294" s="12" t="n"/>
+      <c r="L294" s="12" t="n"/>
       <c r="M294" s="12" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="N294" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O294" s="12" t="n"/>
       <c r="P294" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q294" s="12" t="n">
-        <v>3451</v>
-      </c>
-      <c r="R294" s="12" t="n">
-        <v>3523</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q294" s="12" t="n"/>
+      <c r="R294" s="12" t="n"/>
       <c r="S294" s="12" t="n">
-        <v>1529</v>
+        <v>1495</v>
       </c>
       <c r="T294" s="12" t="n">
-        <v>8073</v>
+        <v>7554</v>
       </c>
       <c r="U294" s="13" t="n">
-        <v>16605</v>
+        <v>9068</v>
       </c>
     </row>
     <row r="295">
@@ -19569,53 +19575,59 @@
       </c>
       <c r="B295" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç1</t>
-        </is>
-      </c>
-      <c r="C295" s="12" t="n">
-        <v>19</v>
-      </c>
+          <t>2023 Ç4</t>
+        </is>
+      </c>
+      <c r="C295" s="12" t="n"/>
       <c r="D295" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="E295" s="12" t="n"/>
-      <c r="F295" s="12" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="E295" s="12" t="n">
+        <v>3284</v>
+      </c>
+      <c r="F295" s="12" t="n">
+        <v>3523</v>
+      </c>
       <c r="G295" s="12" t="n">
-        <v>1533</v>
+        <v>1448</v>
       </c>
       <c r="H295" s="12" t="n">
-        <v>8086</v>
-      </c>
-      <c r="I295" s="12" t="n">
-        <v>0</v>
-      </c>
+        <v>8073</v>
+      </c>
+      <c r="I295" s="12" t="n"/>
       <c r="J295" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K295" s="12" t="n"/>
-      <c r="L295" s="12" t="n"/>
+      <c r="K295" s="12" t="n">
+        <v>167</v>
+      </c>
+      <c r="L295" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="M295" s="12" t="n">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="N295" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="O295" s="12" t="n">
-        <v>19</v>
-      </c>
+      <c r="O295" s="12" t="n"/>
       <c r="P295" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q295" s="12" t="n"/>
-      <c r="R295" s="12" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="Q295" s="12" t="n">
+        <v>3451</v>
+      </c>
+      <c r="R295" s="12" t="n">
+        <v>3523</v>
+      </c>
       <c r="S295" s="12" t="n">
-        <v>1566</v>
+        <v>1529</v>
       </c>
       <c r="T295" s="12" t="n">
-        <v>8086</v>
+        <v>8073</v>
       </c>
       <c r="U295" s="13" t="n">
-        <v>9718</v>
+        <v>16605</v>
       </c>
     </row>
     <row r="296">
@@ -19626,22 +19638,22 @@
       </c>
       <c r="B296" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç2</t>
+          <t>2024 Ç1</t>
         </is>
       </c>
       <c r="C296" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D296" s="12" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E296" s="12" t="n"/>
       <c r="F296" s="12" t="n"/>
       <c r="G296" s="12" t="n">
-        <v>1612</v>
+        <v>1533</v>
       </c>
       <c r="H296" s="12" t="n">
-        <v>8155</v>
+        <v>8086</v>
       </c>
       <c r="I296" s="12" t="n">
         <v>0</v>
@@ -19652,27 +19664,27 @@
       <c r="K296" s="12" t="n"/>
       <c r="L296" s="12" t="n"/>
       <c r="M296" s="12" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="N296" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O296" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="P296" s="12" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="Q296" s="12" t="n"/>
       <c r="R296" s="12" t="n"/>
       <c r="S296" s="12" t="n">
-        <v>1650</v>
+        <v>1566</v>
       </c>
       <c r="T296" s="12" t="n">
-        <v>8155</v>
+        <v>8086</v>
       </c>
       <c r="U296" s="13" t="n">
-        <v>9839</v>
+        <v>9718</v>
       </c>
     </row>
     <row r="297">
@@ -19683,22 +19695,22 @@
       </c>
       <c r="B297" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç3</t>
+          <t>2024 Ç2</t>
         </is>
       </c>
       <c r="C297" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D297" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E297" s="12" t="n"/>
       <c r="F297" s="12" t="n"/>
       <c r="G297" s="12" t="n">
-        <v>1675</v>
+        <v>1612</v>
       </c>
       <c r="H297" s="12" t="n">
-        <v>8536</v>
+        <v>8155</v>
       </c>
       <c r="I297" s="12" t="n">
         <v>0</v>
@@ -19709,7 +19721,7 @@
       <c r="K297" s="12" t="n"/>
       <c r="L297" s="12" t="n"/>
       <c r="M297" s="12" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="N297" s="12" t="n">
         <v>0</v>
@@ -19718,18 +19730,18 @@
         <v>0</v>
       </c>
       <c r="P297" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q297" s="12" t="n"/>
       <c r="R297" s="12" t="n"/>
       <c r="S297" s="12" t="n">
-        <v>1737</v>
+        <v>1650</v>
       </c>
       <c r="T297" s="12" t="n">
-        <v>8536</v>
+        <v>8155</v>
       </c>
       <c r="U297" s="13" t="n">
-        <v>10302</v>
+        <v>9839</v>
       </c>
     </row>
     <row r="298">
@@ -19740,26 +19752,22 @@
       </c>
       <c r="B298" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç1</t>
+          <t>2024 Ç3</t>
         </is>
       </c>
       <c r="C298" s="12" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="D298" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E298" s="12" t="n">
-        <v>3011</v>
-      </c>
-      <c r="F298" s="12" t="n">
-        <v>4383</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="E298" s="12" t="n"/>
+      <c r="F298" s="12" t="n"/>
       <c r="G298" s="12" t="n">
-        <v>1816</v>
+        <v>1675</v>
       </c>
       <c r="H298" s="12" t="n">
-        <v>8103</v>
+        <v>8536</v>
       </c>
       <c r="I298" s="12" t="n">
         <v>0</v>
@@ -19767,38 +19775,30 @@
       <c r="J298" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K298" s="12" t="n">
-        <v>615</v>
-      </c>
-      <c r="L298" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="K298" s="12" t="n"/>
+      <c r="L298" s="12" t="n"/>
       <c r="M298" s="12" t="n">
-        <v>1326</v>
+        <v>62</v>
       </c>
       <c r="N298" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O298" s="12" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="P298" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q298" s="12" t="n">
-        <v>3626</v>
-      </c>
-      <c r="R298" s="12" t="n">
-        <v>4383</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="Q298" s="12" t="n"/>
+      <c r="R298" s="12" t="n"/>
       <c r="S298" s="12" t="n">
-        <v>3142</v>
+        <v>1737</v>
       </c>
       <c r="T298" s="12" t="n">
-        <v>8103</v>
+        <v>8536</v>
       </c>
       <c r="U298" s="13" t="n">
-        <v>19308</v>
+        <v>10302</v>
       </c>
     </row>
     <row r="299">
@@ -19809,134 +19809,134 @@
       </c>
       <c r="B299" s="11" t="inlineStr">
         <is>
+          <t>2025 Ç1</t>
+        </is>
+      </c>
+      <c r="C299" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="D299" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E299" s="12" t="n">
+        <v>3011</v>
+      </c>
+      <c r="F299" s="12" t="n">
+        <v>4383</v>
+      </c>
+      <c r="G299" s="12" t="n">
+        <v>1816</v>
+      </c>
+      <c r="H299" s="12" t="n">
+        <v>8103</v>
+      </c>
+      <c r="I299" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J299" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" s="12" t="n">
+        <v>615</v>
+      </c>
+      <c r="L299" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M299" s="12" t="n">
+        <v>1326</v>
+      </c>
+      <c r="N299" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O299" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="P299" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q299" s="12" t="n">
+        <v>3626</v>
+      </c>
+      <c r="R299" s="12" t="n">
+        <v>4383</v>
+      </c>
+      <c r="S299" s="12" t="n">
+        <v>3142</v>
+      </c>
+      <c r="T299" s="12" t="n">
+        <v>8103</v>
+      </c>
+      <c r="U299" s="13" t="n">
+        <v>19308</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="10" t="inlineStr">
+        <is>
+          <t>ABank</t>
+        </is>
+      </c>
+      <c r="B300" s="11" t="inlineStr">
+        <is>
           <t>2025 Ç2</t>
         </is>
       </c>
-      <c r="C299" s="12" t="n">
+      <c r="C300" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="D299" s="12" t="n">
+      <c r="D300" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E299" s="12" t="n">
+      <c r="E300" s="12" t="n">
         <v>2624</v>
       </c>
-      <c r="F299" s="12" t="n">
+      <c r="F300" s="12" t="n">
         <v>4641</v>
       </c>
-      <c r="G299" s="12" t="n">
+      <c r="G300" s="12" t="n">
         <v>1821</v>
       </c>
-      <c r="H299" s="12" t="n">
+      <c r="H300" s="12" t="n">
         <v>8441</v>
       </c>
-      <c r="I299" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J299" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K299" s="12" t="n">
+      <c r="I300" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K300" s="12" t="n">
         <v>152</v>
       </c>
-      <c r="L299" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M299" s="12" t="n">
+      <c r="L300" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M300" s="12" t="n">
         <v>1630</v>
       </c>
-      <c r="N299" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O299" s="12" t="n">
+      <c r="N300" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O300" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="P299" s="12" t="n">
+      <c r="P300" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="Q299" s="12" t="n">
+      <c r="Q300" s="12" t="n">
         <v>2776</v>
       </c>
-      <c r="R299" s="12" t="n">
+      <c r="R300" s="12" t="n">
         <v>4641</v>
       </c>
-      <c r="S299" s="12" t="n">
+      <c r="S300" s="12" t="n">
         <v>3450</v>
       </c>
-      <c r="T299" s="12" t="n">
+      <c r="T300" s="12" t="n">
         <v>8441</v>
       </c>
-      <c r="U299" s="13" t="n">
+      <c r="U300" s="13" t="n">
         <v>19365</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="6" t="inlineStr">
-        <is>
-          <t>Şeker</t>
-        </is>
-      </c>
-      <c r="B300" s="7" t="inlineStr">
-        <is>
-          <t>2021 Ç1</t>
-        </is>
-      </c>
-      <c r="C300" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D300" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E300" s="8" t="n">
-        <v>517</v>
-      </c>
-      <c r="F300" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G300" s="8" t="n">
-        <v>2583</v>
-      </c>
-      <c r="H300" s="8" t="n">
-        <v>1266</v>
-      </c>
-      <c r="I300" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J300" s="8" t="n">
-        <v>62</v>
-      </c>
-      <c r="K300" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="L300" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M300" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N300" s="8" t="n">
-        <v>1503</v>
-      </c>
-      <c r="O300" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P300" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="Q300" s="8" t="n">
-        <v>524</v>
-      </c>
-      <c r="R300" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S300" s="8" t="n">
-        <v>2583</v>
-      </c>
-      <c r="T300" s="8" t="n">
-        <v>2768</v>
-      </c>
-      <c r="U300" s="9" t="n">
-        <v>5947</v>
       </c>
     </row>
     <row r="301">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="B301" s="7" t="inlineStr">
         <is>
-          <t>2021 Ç2</t>
+          <t>2021 Ç1</t>
         </is>
       </c>
       <c r="C301" s="8" t="n">
@@ -20016,7 +20016,7 @@
       </c>
       <c r="B302" s="7" t="inlineStr">
         <is>
-          <t>2021 Ç3</t>
+          <t>2021 Ç2</t>
         </is>
       </c>
       <c r="C302" s="8" t="n">
@@ -20085,7 +20085,7 @@
       </c>
       <c r="B303" s="7" t="inlineStr">
         <is>
-          <t>2021 Ç4</t>
+          <t>2021 Ç3</t>
         </is>
       </c>
       <c r="C303" s="8" t="n">
@@ -20154,32 +20154,32 @@
       </c>
       <c r="B304" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç1</t>
+          <t>2021 Ç4</t>
         </is>
       </c>
       <c r="C304" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D304" s="8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E304" s="8" t="n">
-        <v>320</v>
+        <v>517</v>
       </c>
       <c r="F304" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G304" s="8" t="n">
-        <v>2708</v>
+        <v>2583</v>
       </c>
       <c r="H304" s="8" t="n">
-        <v>1892</v>
+        <v>1266</v>
       </c>
       <c r="I304" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J304" s="8" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="K304" s="8" t="n">
         <v>7</v>
@@ -20188,31 +20188,31 @@
         <v>0</v>
       </c>
       <c r="M304" s="8" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="N304" s="8" t="n">
-        <v>1365</v>
+        <v>1503</v>
       </c>
       <c r="O304" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P304" s="8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="Q304" s="8" t="n">
-        <v>328</v>
+        <v>524</v>
       </c>
       <c r="R304" s="8" t="n">
         <v>0</v>
       </c>
       <c r="S304" s="8" t="n">
-        <v>2931</v>
+        <v>2583</v>
       </c>
       <c r="T304" s="8" t="n">
-        <v>3257</v>
+        <v>2768</v>
       </c>
       <c r="U304" s="9" t="n">
-        <v>6598</v>
+        <v>5947</v>
       </c>
     </row>
     <row r="305">
@@ -20223,26 +20223,26 @@
       </c>
       <c r="B305" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç2</t>
+          <t>2022 Ç1</t>
         </is>
       </c>
       <c r="C305" s="8" t="n">
         <v>2</v>
       </c>
       <c r="D305" s="8" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E305" s="8" t="n">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="F305" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G305" s="8" t="n">
-        <v>3127</v>
+        <v>2708</v>
       </c>
       <c r="H305" s="8" t="n">
-        <v>2266</v>
+        <v>1892</v>
       </c>
       <c r="I305" s="8" t="n">
         <v>0</v>
@@ -20257,31 +20257,31 @@
         <v>0</v>
       </c>
       <c r="M305" s="8" t="n">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="N305" s="8" t="n">
-        <v>614</v>
+        <v>1365</v>
       </c>
       <c r="O305" s="8" t="n">
         <v>2</v>
       </c>
       <c r="P305" s="8" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="Q305" s="8" t="n">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="R305" s="8" t="n">
         <v>0</v>
       </c>
       <c r="S305" s="8" t="n">
-        <v>3368</v>
+        <v>2931</v>
       </c>
       <c r="T305" s="8" t="n">
-        <v>2880</v>
+        <v>3257</v>
       </c>
       <c r="U305" s="9" t="n">
-        <v>6681</v>
+        <v>6598</v>
       </c>
     </row>
     <row r="306">
@@ -20292,26 +20292,26 @@
       </c>
       <c r="B306" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç3</t>
+          <t>2022 Ç2</t>
         </is>
       </c>
       <c r="C306" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D306" s="8" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E306" s="8" t="n">
-        <v>103</v>
+        <v>335</v>
       </c>
       <c r="F306" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G306" s="8" t="n">
-        <v>4463</v>
+        <v>3127</v>
       </c>
       <c r="H306" s="8" t="n">
-        <v>2488</v>
+        <v>2266</v>
       </c>
       <c r="I306" s="8" t="n">
         <v>0</v>
@@ -20320,37 +20320,37 @@
         <v>70</v>
       </c>
       <c r="K306" s="8" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L306" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M306" s="8" t="n">
-        <v>750</v>
+        <v>241</v>
       </c>
       <c r="N306" s="8" t="n">
-        <v>686</v>
+        <v>614</v>
       </c>
       <c r="O306" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P306" s="8" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="Q306" s="8" t="n">
-        <v>116</v>
+        <v>342</v>
       </c>
       <c r="R306" s="8" t="n">
         <v>0</v>
       </c>
       <c r="S306" s="8" t="n">
-        <v>5213</v>
+        <v>3368</v>
       </c>
       <c r="T306" s="8" t="n">
-        <v>3175</v>
+        <v>2880</v>
       </c>
       <c r="U306" s="9" t="n">
-        <v>8605</v>
+        <v>6681</v>
       </c>
     </row>
     <row r="307">
@@ -20361,32 +20361,32 @@
       </c>
       <c r="B307" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç4</t>
+          <t>2022 Ç3</t>
         </is>
       </c>
       <c r="C307" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D307" s="8" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E307" s="8" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F307" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G307" s="8" t="n">
-        <v>5735</v>
+        <v>4463</v>
       </c>
       <c r="H307" s="8" t="n">
-        <v>2545</v>
+        <v>2488</v>
       </c>
       <c r="I307" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J307" s="8" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K307" s="8" t="n">
         <v>14</v>
@@ -20395,31 +20395,31 @@
         <v>0</v>
       </c>
       <c r="M307" s="8" t="n">
-        <v>2617</v>
+        <v>750</v>
       </c>
       <c r="N307" s="8" t="n">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="O307" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P307" s="8" t="n">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="Q307" s="8" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="R307" s="8" t="n">
         <v>0</v>
       </c>
       <c r="S307" s="8" t="n">
-        <v>8352</v>
+        <v>5213</v>
       </c>
       <c r="T307" s="8" t="n">
-        <v>3233</v>
+        <v>3175</v>
       </c>
       <c r="U307" s="9" t="n">
-        <v>11826</v>
+        <v>8605</v>
       </c>
     </row>
     <row r="308">
@@ -20430,65 +20430,65 @@
       </c>
       <c r="B308" s="7" t="inlineStr">
         <is>
-          <t>2023 Ç2</t>
+          <t>2022 Ç4</t>
         </is>
       </c>
       <c r="C308" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D308" s="8" t="n">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="E308" s="8" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="F308" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G308" s="8" t="n">
-        <v>6203</v>
+        <v>5735</v>
       </c>
       <c r="H308" s="8" t="n">
-        <v>3518</v>
+        <v>2545</v>
       </c>
       <c r="I308" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J308" s="8" t="n">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="K308" s="8" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L308" s="8" t="n">
         <v>0</v>
       </c>
       <c r="M308" s="8" t="n">
-        <v>519</v>
+        <v>2617</v>
       </c>
       <c r="N308" s="8" t="n">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="O308" s="8" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P308" s="8" t="n">
-        <v>227</v>
+        <v>110</v>
       </c>
       <c r="Q308" s="8" t="n">
-        <v>19</v>
+        <v>120</v>
       </c>
       <c r="R308" s="8" t="n">
         <v>0</v>
       </c>
       <c r="S308" s="8" t="n">
-        <v>6722</v>
+        <v>8352</v>
       </c>
       <c r="T308" s="8" t="n">
-        <v>4202</v>
+        <v>3233</v>
       </c>
       <c r="U308" s="9" t="n">
-        <v>11170</v>
+        <v>11826</v>
       </c>
     </row>
     <row r="309">
@@ -20499,14 +20499,14 @@
       </c>
       <c r="B309" s="7" t="inlineStr">
         <is>
-          <t>2023 Ç3</t>
+          <t>2023 Ç2</t>
         </is>
       </c>
       <c r="C309" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D309" s="8" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E309" s="8" t="n">
         <v>0</v>
@@ -20515,16 +20515,16 @@
         <v>0</v>
       </c>
       <c r="G309" s="8" t="n">
-        <v>6716</v>
+        <v>6203</v>
       </c>
       <c r="H309" s="8" t="n">
-        <v>3684</v>
+        <v>3518</v>
       </c>
       <c r="I309" s="8" t="n">
         <v>0</v>
       </c>
       <c r="J309" s="8" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K309" s="8" t="n">
         <v>19</v>
@@ -20533,16 +20533,16 @@
         <v>0</v>
       </c>
       <c r="M309" s="8" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="N309" s="8" t="n">
-        <v>735</v>
+        <v>684</v>
       </c>
       <c r="O309" s="8" t="n">
         <v>1</v>
       </c>
       <c r="P309" s="8" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="Q309" s="8" t="n">
         <v>19</v>
@@ -20551,13 +20551,13 @@
         <v>0</v>
       </c>
       <c r="S309" s="8" t="n">
-        <v>7228</v>
+        <v>6722</v>
       </c>
       <c r="T309" s="8" t="n">
-        <v>4419</v>
+        <v>4202</v>
       </c>
       <c r="U309" s="9" t="n">
-        <v>11898</v>
+        <v>11170</v>
       </c>
     </row>
     <row r="310">
@@ -20568,69 +20568,138 @@
       </c>
       <c r="B310" s="7" t="inlineStr">
         <is>
+          <t>2023 Ç3</t>
+        </is>
+      </c>
+      <c r="C310" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D310" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="E310" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F310" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G310" s="8" t="n">
+        <v>6716</v>
+      </c>
+      <c r="H310" s="8" t="n">
+        <v>3684</v>
+      </c>
+      <c r="I310" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J310" s="8" t="n">
+        <v>135</v>
+      </c>
+      <c r="K310" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="L310" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M310" s="8" t="n">
+        <v>512</v>
+      </c>
+      <c r="N310" s="8" t="n">
+        <v>735</v>
+      </c>
+      <c r="O310" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P310" s="8" t="n">
+        <v>231</v>
+      </c>
+      <c r="Q310" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="R310" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S310" s="8" t="n">
+        <v>7228</v>
+      </c>
+      <c r="T310" s="8" t="n">
+        <v>4419</v>
+      </c>
+      <c r="U310" s="9" t="n">
+        <v>11898</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="6" t="inlineStr">
+        <is>
+          <t>Şeker</t>
+        </is>
+      </c>
+      <c r="B311" s="7" t="inlineStr">
+        <is>
           <t>2024 Ç2</t>
         </is>
       </c>
-      <c r="C310" s="8" t="n">
+      <c r="C311" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="D310" s="8" t="n">
+      <c r="D311" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="E310" s="8" t="n">
+      <c r="E311" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="F310" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G310" s="8" t="n">
+      <c r="F311" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G311" s="8" t="n">
         <v>8057</v>
       </c>
-      <c r="H310" s="8" t="n">
+      <c r="H311" s="8" t="n">
         <v>4557</v>
       </c>
-      <c r="I310" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J310" s="8" t="n">
+      <c r="I311" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" s="8" t="n">
         <v>184</v>
       </c>
-      <c r="K310" s="8" t="n">
+      <c r="K311" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="L310" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M310" s="8" t="n">
+      <c r="L311" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M311" s="8" t="n">
         <v>231</v>
       </c>
-      <c r="N310" s="8" t="n">
+      <c r="N311" s="8" t="n">
         <v>525</v>
       </c>
-      <c r="O310" s="8" t="n">
+      <c r="O311" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="P310" s="8" t="n">
+      <c r="P311" s="8" t="n">
         <v>263</v>
       </c>
-      <c r="Q310" s="8" t="n">
+      <c r="Q311" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="R310" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S310" s="8" t="n">
+      <c r="R311" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S311" s="8" t="n">
         <v>8288</v>
       </c>
-      <c r="T310" s="8" t="n">
+      <c r="T311" s="8" t="n">
         <v>5082</v>
       </c>
-      <c r="U310" s="9" t="n">
+      <c r="U311" s="9" t="n">
         <v>13732</v>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" s="2" t="inlineStr">
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
         <is>
           <t>Kaynak: bankaların solo BDDK formatlı bilançoları. ASA = GUD farkı kâr/zarara yansıtılan (1.2), SH = GUD farkı diğer kapsamlı gelire yansıtılan (1.3), VKET = itfa edilmiş maliyetle ölçülen diğer finansal varlıklar (2.4); DİBS = devlet borçlanma senetleri alt satırı, DİĞER = kalan. Yalnız PDF'i yüklenmiş banka-dönemler yer alır.</t>
         </is>

--- a/site/data/banka-mdc-kirilimi.xlsx
+++ b/site/data/banka-mdc-kirilimi.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U319"/>
+  <dimension ref="A1:U332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -17395,32 +17395,56 @@
       <c r="D258" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E258" s="8" t="n"/>
-      <c r="F258" s="8" t="n"/>
-      <c r="G258" s="8" t="n"/>
-      <c r="H258" s="8" t="n"/>
+      <c r="E258" s="8" t="n">
+        <v>3839</v>
+      </c>
+      <c r="F258" s="8" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G258" s="8" t="n">
+        <v>198</v>
+      </c>
+      <c r="H258" s="8" t="n">
+        <v>1065</v>
+      </c>
       <c r="I258" s="8" t="n">
         <v>82</v>
       </c>
       <c r="J258" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="K258" s="8" t="n"/>
-      <c r="L258" s="8" t="n"/>
-      <c r="M258" s="8" t="n"/>
-      <c r="N258" s="8" t="n"/>
+      <c r="K258" s="8" t="n">
+        <v>2176</v>
+      </c>
+      <c r="L258" s="8" t="n">
+        <v>547</v>
+      </c>
+      <c r="M258" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="N258" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="O258" s="8" t="n">
         <v>83</v>
       </c>
       <c r="P258" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="Q258" s="8" t="n"/>
-      <c r="R258" s="8" t="n"/>
-      <c r="S258" s="8" t="n"/>
-      <c r="T258" s="8" t="n"/>
+      <c r="Q258" s="8" t="n">
+        <v>6015</v>
+      </c>
+      <c r="R258" s="8" t="n">
+        <v>4024</v>
+      </c>
+      <c r="S258" s="8" t="n">
+        <v>270</v>
+      </c>
+      <c r="T258" s="8" t="n">
+        <v>1065</v>
+      </c>
       <c r="U258" s="9" t="n">
-        <v>102</v>
+        <v>11476</v>
       </c>
     </row>
     <row r="259">
@@ -17440,32 +17464,56 @@
       <c r="D259" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="E259" s="8" t="n"/>
-      <c r="F259" s="8" t="n"/>
-      <c r="G259" s="8" t="n"/>
-      <c r="H259" s="8" t="n"/>
+      <c r="E259" s="8" t="n">
+        <v>3839</v>
+      </c>
+      <c r="F259" s="8" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G259" s="8" t="n">
+        <v>198</v>
+      </c>
+      <c r="H259" s="8" t="n">
+        <v>1065</v>
+      </c>
       <c r="I259" s="8" t="n">
         <v>82</v>
       </c>
       <c r="J259" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="K259" s="8" t="n"/>
-      <c r="L259" s="8" t="n"/>
-      <c r="M259" s="8" t="n"/>
-      <c r="N259" s="8" t="n"/>
+      <c r="K259" s="8" t="n">
+        <v>2176</v>
+      </c>
+      <c r="L259" s="8" t="n">
+        <v>547</v>
+      </c>
+      <c r="M259" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="N259" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="O259" s="8" t="n">
         <v>83</v>
       </c>
       <c r="P259" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="Q259" s="8" t="n"/>
-      <c r="R259" s="8" t="n"/>
-      <c r="S259" s="8" t="n"/>
-      <c r="T259" s="8" t="n"/>
+      <c r="Q259" s="8" t="n">
+        <v>6015</v>
+      </c>
+      <c r="R259" s="8" t="n">
+        <v>4024</v>
+      </c>
+      <c r="S259" s="8" t="n">
+        <v>270</v>
+      </c>
+      <c r="T259" s="8" t="n">
+        <v>1065</v>
+      </c>
       <c r="U259" s="9" t="n">
-        <v>102</v>
+        <v>11476</v>
       </c>
     </row>
     <row r="260">
@@ -17476,41 +17524,65 @@
       </c>
       <c r="B260" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç1</t>
+          <t>2021 Ç3</t>
         </is>
       </c>
       <c r="C260" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D260" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="E260" s="8" t="n"/>
-      <c r="F260" s="8" t="n"/>
-      <c r="G260" s="8" t="n"/>
-      <c r="H260" s="8" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="E260" s="8" t="n">
+        <v>3839</v>
+      </c>
+      <c r="F260" s="8" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G260" s="8" t="n">
+        <v>198</v>
+      </c>
+      <c r="H260" s="8" t="n">
+        <v>1065</v>
+      </c>
       <c r="I260" s="8" t="n">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="J260" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="K260" s="8" t="n"/>
-      <c r="L260" s="8" t="n"/>
-      <c r="M260" s="8" t="n"/>
-      <c r="N260" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="K260" s="8" t="n">
+        <v>2176</v>
+      </c>
+      <c r="L260" s="8" t="n">
+        <v>547</v>
+      </c>
+      <c r="M260" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="N260" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="O260" s="8" t="n">
-        <v>352</v>
+        <v>83</v>
       </c>
       <c r="P260" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q260" s="8" t="n"/>
-      <c r="R260" s="8" t="n"/>
-      <c r="S260" s="8" t="n"/>
-      <c r="T260" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="Q260" s="8" t="n">
+        <v>6015</v>
+      </c>
+      <c r="R260" s="8" t="n">
+        <v>4024</v>
+      </c>
+      <c r="S260" s="8" t="n">
+        <v>270</v>
+      </c>
+      <c r="T260" s="8" t="n">
+        <v>1065</v>
+      </c>
       <c r="U260" s="9" t="n">
-        <v>394</v>
+        <v>11476</v>
       </c>
     </row>
     <row r="261">
@@ -17521,41 +17593,65 @@
       </c>
       <c r="B261" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç2</t>
+          <t>2021 Ç4</t>
         </is>
       </c>
       <c r="C261" s="8" t="n">
         <v>1</v>
       </c>
       <c r="D261" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="E261" s="8" t="n"/>
-      <c r="F261" s="8" t="n"/>
-      <c r="G261" s="8" t="n"/>
-      <c r="H261" s="8" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="E261" s="8" t="n">
+        <v>3839</v>
+      </c>
+      <c r="F261" s="8" t="n">
+        <v>3478</v>
+      </c>
+      <c r="G261" s="8" t="n">
+        <v>198</v>
+      </c>
+      <c r="H261" s="8" t="n">
+        <v>1065</v>
+      </c>
       <c r="I261" s="8" t="n">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="J261" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="K261" s="8" t="n"/>
-      <c r="L261" s="8" t="n"/>
-      <c r="M261" s="8" t="n"/>
-      <c r="N261" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="K261" s="8" t="n">
+        <v>2176</v>
+      </c>
+      <c r="L261" s="8" t="n">
+        <v>547</v>
+      </c>
+      <c r="M261" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="N261" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="O261" s="8" t="n">
-        <v>246</v>
+        <v>83</v>
       </c>
       <c r="P261" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q261" s="8" t="n"/>
-      <c r="R261" s="8" t="n"/>
-      <c r="S261" s="8" t="n"/>
-      <c r="T261" s="8" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="Q261" s="8" t="n">
+        <v>6015</v>
+      </c>
+      <c r="R261" s="8" t="n">
+        <v>4024</v>
+      </c>
+      <c r="S261" s="8" t="n">
+        <v>270</v>
+      </c>
+      <c r="T261" s="8" t="n">
+        <v>1065</v>
+      </c>
       <c r="U261" s="9" t="n">
-        <v>292</v>
+        <v>11476</v>
       </c>
     </row>
     <row r="262">
@@ -17566,41 +17662,65 @@
       </c>
       <c r="B262" s="7" t="inlineStr">
         <is>
-          <t>2022 Ç3</t>
+          <t>2022 Ç1</t>
         </is>
       </c>
       <c r="C262" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D262" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E262" s="8" t="n"/>
-      <c r="F262" s="8" t="n"/>
-      <c r="G262" s="8" t="n"/>
-      <c r="H262" s="8" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="E262" s="8" t="n">
+        <v>4385</v>
+      </c>
+      <c r="F262" s="8" t="n">
+        <v>3867</v>
+      </c>
+      <c r="G262" s="8" t="n">
+        <v>194</v>
+      </c>
+      <c r="H262" s="8" t="n">
+        <v>1072</v>
+      </c>
       <c r="I262" s="8" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="J262" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="K262" s="8" t="n"/>
-      <c r="L262" s="8" t="n"/>
-      <c r="M262" s="8" t="n"/>
-      <c r="N262" s="8" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="K262" s="8" t="n">
+        <v>1748</v>
+      </c>
+      <c r="L262" s="8" t="n">
+        <v>593</v>
+      </c>
+      <c r="M262" s="8" t="n">
+        <v>1911</v>
+      </c>
+      <c r="N262" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="O262" s="8" t="n">
-        <v>2</v>
+        <v>352</v>
       </c>
       <c r="P262" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q262" s="8" t="n"/>
-      <c r="R262" s="8" t="n"/>
-      <c r="S262" s="8" t="n"/>
-      <c r="T262" s="8" t="n"/>
+        <v>43</v>
+      </c>
+      <c r="Q262" s="8" t="n">
+        <v>6134</v>
+      </c>
+      <c r="R262" s="8" t="n">
+        <v>4460</v>
+      </c>
+      <c r="S262" s="8" t="n">
+        <v>2105</v>
+      </c>
+      <c r="T262" s="8" t="n">
+        <v>1072</v>
+      </c>
       <c r="U262" s="9" t="n">
-        <v>36</v>
+        <v>14165</v>
       </c>
     </row>
     <row r="263">
@@ -17611,41 +17731,65 @@
       </c>
       <c r="B263" s="7" t="inlineStr">
         <is>
-          <t>2023 Ç3</t>
+          <t>2022 Ç2</t>
         </is>
       </c>
       <c r="C263" s="8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D263" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="E263" s="8" t="n"/>
-      <c r="F263" s="8" t="n"/>
-      <c r="G263" s="8" t="n"/>
-      <c r="H263" s="8" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="E263" s="8" t="n">
+        <v>5611</v>
+      </c>
+      <c r="F263" s="8" t="n">
+        <v>4025</v>
+      </c>
+      <c r="G263" s="8" t="n">
+        <v>199</v>
+      </c>
+      <c r="H263" s="8" t="n">
+        <v>1205</v>
+      </c>
       <c r="I263" s="8" t="n">
-        <v>880</v>
+        <v>245</v>
       </c>
       <c r="J263" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="K263" s="8" t="n"/>
-      <c r="L263" s="8" t="n"/>
-      <c r="M263" s="8" t="n"/>
-      <c r="N263" s="8" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="K263" s="8" t="n">
+        <v>1328</v>
+      </c>
+      <c r="L263" s="8" t="n">
+        <v>675</v>
+      </c>
+      <c r="M263" s="8" t="n">
+        <v>2120</v>
+      </c>
+      <c r="N263" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="O263" s="8" t="n">
-        <v>880</v>
+        <v>246</v>
       </c>
       <c r="P263" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="Q263" s="8" t="n"/>
-      <c r="R263" s="8" t="n"/>
-      <c r="S263" s="8" t="n"/>
-      <c r="T263" s="8" t="n"/>
+        <v>46</v>
+      </c>
+      <c r="Q263" s="8" t="n">
+        <v>6939</v>
+      </c>
+      <c r="R263" s="8" t="n">
+        <v>4699</v>
+      </c>
+      <c r="S263" s="8" t="n">
+        <v>2318</v>
+      </c>
+      <c r="T263" s="8" t="n">
+        <v>1205</v>
+      </c>
       <c r="U263" s="9" t="n">
-        <v>945</v>
+        <v>15454</v>
       </c>
     </row>
     <row r="264">
@@ -17656,41 +17800,65 @@
       </c>
       <c r="B264" s="7" t="inlineStr">
         <is>
-          <t>2024 Ç1</t>
-        </is>
-      </c>
-      <c r="C264" s="8" t="n"/>
-      <c r="D264" s="8" t="n"/>
+          <t>2022 Ç3</t>
+        </is>
+      </c>
+      <c r="C264" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D264" s="8" t="n">
+        <v>7</v>
+      </c>
       <c r="E264" s="8" t="n">
-        <v>3059</v>
+        <v>5348</v>
       </c>
       <c r="F264" s="8" t="n">
-        <v>6006</v>
-      </c>
-      <c r="G264" s="8" t="n"/>
-      <c r="H264" s="8" t="n"/>
-      <c r="I264" s="8" t="n"/>
-      <c r="J264" s="8" t="n"/>
+        <v>4384</v>
+      </c>
+      <c r="G264" s="8" t="n">
+        <v>1654</v>
+      </c>
+      <c r="H264" s="8" t="n">
+        <v>855</v>
+      </c>
+      <c r="I264" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" s="8" t="n">
+        <v>21</v>
+      </c>
       <c r="K264" s="8" t="n">
-        <v>19</v>
+        <v>640</v>
       </c>
       <c r="L264" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M264" s="8" t="n">
+        <v>1654</v>
+      </c>
+      <c r="N264" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="M264" s="8" t="n"/>
-      <c r="N264" s="8" t="n"/>
-      <c r="O264" s="8" t="n"/>
-      <c r="P264" s="8" t="n"/>
+      <c r="P264" s="8" t="n">
+        <v>28</v>
+      </c>
       <c r="Q264" s="8" t="n">
-        <v>3078</v>
+        <v>5988</v>
       </c>
       <c r="R264" s="8" t="n">
-        <v>6008</v>
-      </c>
-      <c r="S264" s="8" t="n"/>
-      <c r="T264" s="8" t="n"/>
+        <v>4385</v>
+      </c>
+      <c r="S264" s="8" t="n">
+        <v>3308</v>
+      </c>
+      <c r="T264" s="8" t="n">
+        <v>855</v>
+      </c>
       <c r="U264" s="9" t="n">
-        <v>9087</v>
+        <v>14566</v>
       </c>
     </row>
     <row r="265">
@@ -17701,938 +17869,938 @@
       </c>
       <c r="B265" s="7" t="inlineStr">
         <is>
+          <t>2022 Ç4</t>
+        </is>
+      </c>
+      <c r="C265" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D265" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E265" s="8" t="n">
+        <v>5663</v>
+      </c>
+      <c r="F265" s="8" t="n">
+        <v>4802</v>
+      </c>
+      <c r="G265" s="8" t="n">
+        <v>3310</v>
+      </c>
+      <c r="H265" s="8" t="n">
+        <v>970</v>
+      </c>
+      <c r="I265" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="K265" s="8" t="n">
+        <v>482</v>
+      </c>
+      <c r="L265" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M265" s="8" t="n">
+        <v>3018</v>
+      </c>
+      <c r="N265" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O265" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P265" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q265" s="8" t="n">
+        <v>6145</v>
+      </c>
+      <c r="R265" s="8" t="n">
+        <v>4802</v>
+      </c>
+      <c r="S265" s="8" t="n">
+        <v>6328</v>
+      </c>
+      <c r="T265" s="8" t="n">
+        <v>970</v>
+      </c>
+      <c r="U265" s="9" t="n">
+        <v>18281</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="6" t="inlineStr">
+        <is>
+          <t>Odea</t>
+        </is>
+      </c>
+      <c r="B266" s="7" t="inlineStr">
+        <is>
+          <t>2023 Ç2</t>
+        </is>
+      </c>
+      <c r="C266" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D266" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E266" s="8" t="n">
+        <v>2951</v>
+      </c>
+      <c r="F266" s="8" t="n">
+        <v>7350</v>
+      </c>
+      <c r="G266" s="8" t="n">
+        <v>7238</v>
+      </c>
+      <c r="H266" s="8" t="n">
+        <v>1280</v>
+      </c>
+      <c r="I266" s="8" t="n">
+        <v>1321</v>
+      </c>
+      <c r="J266" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="K266" s="8" t="n">
+        <v>103</v>
+      </c>
+      <c r="L266" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M266" s="8" t="n">
+        <v>3877</v>
+      </c>
+      <c r="N266" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O266" s="8" t="n">
+        <v>1321</v>
+      </c>
+      <c r="P266" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q266" s="8" t="n">
+        <v>3054</v>
+      </c>
+      <c r="R266" s="8" t="n">
+        <v>7351</v>
+      </c>
+      <c r="S266" s="8" t="n">
+        <v>11115</v>
+      </c>
+      <c r="T266" s="8" t="n">
+        <v>1280</v>
+      </c>
+      <c r="U266" s="9" t="n">
+        <v>24191</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="6" t="inlineStr">
+        <is>
+          <t>Odea</t>
+        </is>
+      </c>
+      <c r="B267" s="7" t="inlineStr">
+        <is>
+          <t>2023 Ç3</t>
+        </is>
+      </c>
+      <c r="C267" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D267" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E267" s="8" t="n">
+        <v>2298</v>
+      </c>
+      <c r="F267" s="8" t="n">
+        <v>6763</v>
+      </c>
+      <c r="G267" s="8" t="n">
+        <v>6471</v>
+      </c>
+      <c r="H267" s="8" t="n">
+        <v>1245</v>
+      </c>
+      <c r="I267" s="8" t="n">
+        <v>880</v>
+      </c>
+      <c r="J267" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="K267" s="8" t="n">
+        <v>204</v>
+      </c>
+      <c r="L267" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M267" s="8" t="n">
+        <v>2954</v>
+      </c>
+      <c r="N267" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O267" s="8" t="n">
+        <v>880</v>
+      </c>
+      <c r="P267" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q267" s="8" t="n">
+        <v>2502</v>
+      </c>
+      <c r="R267" s="8" t="n">
+        <v>6763</v>
+      </c>
+      <c r="S267" s="8" t="n">
+        <v>9425</v>
+      </c>
+      <c r="T267" s="8" t="n">
+        <v>1245</v>
+      </c>
+      <c r="U267" s="9" t="n">
+        <v>20880</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="6" t="inlineStr">
+        <is>
+          <t>Odea</t>
+        </is>
+      </c>
+      <c r="B268" s="7" t="inlineStr">
+        <is>
+          <t>2023 Ç4</t>
+        </is>
+      </c>
+      <c r="C268" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D268" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E268" s="8" t="n">
+        <v>2951</v>
+      </c>
+      <c r="F268" s="8" t="n">
+        <v>7350</v>
+      </c>
+      <c r="G268" s="8" t="n">
+        <v>7238</v>
+      </c>
+      <c r="H268" s="8" t="n">
+        <v>1280</v>
+      </c>
+      <c r="I268" s="8" t="n">
+        <v>1321</v>
+      </c>
+      <c r="J268" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="K268" s="8" t="n">
+        <v>103</v>
+      </c>
+      <c r="L268" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M268" s="8" t="n">
+        <v>3877</v>
+      </c>
+      <c r="N268" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O268" s="8" t="n">
+        <v>1321</v>
+      </c>
+      <c r="P268" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q268" s="8" t="n">
+        <v>3054</v>
+      </c>
+      <c r="R268" s="8" t="n">
+        <v>7351</v>
+      </c>
+      <c r="S268" s="8" t="n">
+        <v>11115</v>
+      </c>
+      <c r="T268" s="8" t="n">
+        <v>1280</v>
+      </c>
+      <c r="U268" s="9" t="n">
+        <v>24191</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="6" t="inlineStr">
+        <is>
+          <t>Odea</t>
+        </is>
+      </c>
+      <c r="B269" s="7" t="inlineStr">
+        <is>
+          <t>2024 Ç1</t>
+        </is>
+      </c>
+      <c r="C269" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D269" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="E269" s="8" t="n">
+        <v>3059</v>
+      </c>
+      <c r="F269" s="8" t="n">
+        <v>6006</v>
+      </c>
+      <c r="G269" s="8" t="n">
+        <v>9717</v>
+      </c>
+      <c r="H269" s="8" t="n">
+        <v>999</v>
+      </c>
+      <c r="I269" s="8" t="n">
+        <v>2132</v>
+      </c>
+      <c r="J269" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="K269" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="L269" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M269" s="8" t="n">
+        <v>3951</v>
+      </c>
+      <c r="N269" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O269" s="8" t="n">
+        <v>2133</v>
+      </c>
+      <c r="P269" s="8" t="n">
+        <v>174</v>
+      </c>
+      <c r="Q269" s="8" t="n">
+        <v>3078</v>
+      </c>
+      <c r="R269" s="8" t="n">
+        <v>6008</v>
+      </c>
+      <c r="S269" s="8" t="n">
+        <v>13669</v>
+      </c>
+      <c r="T269" s="8" t="n">
+        <v>999</v>
+      </c>
+      <c r="U269" s="9" t="n">
+        <v>26062</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="6" t="inlineStr">
+        <is>
+          <t>Odea</t>
+        </is>
+      </c>
+      <c r="B270" s="7" t="inlineStr">
+        <is>
+          <t>2024 Ç2</t>
+        </is>
+      </c>
+      <c r="C270" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D270" s="8" t="n">
+        <v>281</v>
+      </c>
+      <c r="E270" s="8" t="n">
+        <v>3313</v>
+      </c>
+      <c r="F270" s="8" t="n">
+        <v>7198</v>
+      </c>
+      <c r="G270" s="8" t="n">
+        <v>8529</v>
+      </c>
+      <c r="H270" s="8" t="n">
+        <v>925</v>
+      </c>
+      <c r="I270" s="8" t="n">
+        <v>1664</v>
+      </c>
+      <c r="J270" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="K270" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="L270" s="8" t="n">
+        <v>656</v>
+      </c>
+      <c r="M270" s="8" t="n">
+        <v>4679</v>
+      </c>
+      <c r="N270" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O270" s="8" t="n">
+        <v>1664</v>
+      </c>
+      <c r="P270" s="8" t="n">
+        <v>336</v>
+      </c>
+      <c r="Q270" s="8" t="n">
+        <v>3329</v>
+      </c>
+      <c r="R270" s="8" t="n">
+        <v>7854</v>
+      </c>
+      <c r="S270" s="8" t="n">
+        <v>13208</v>
+      </c>
+      <c r="T270" s="8" t="n">
+        <v>925</v>
+      </c>
+      <c r="U270" s="9" t="n">
+        <v>27316</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="6" t="inlineStr">
+        <is>
+          <t>Odea</t>
+        </is>
+      </c>
+      <c r="B271" s="7" t="inlineStr">
+        <is>
+          <t>2024 Ç3</t>
+        </is>
+      </c>
+      <c r="C271" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D271" s="8" t="n">
+        <v>132</v>
+      </c>
+      <c r="E271" s="8" t="n">
+        <v>3098</v>
+      </c>
+      <c r="F271" s="8" t="n">
+        <v>7287</v>
+      </c>
+      <c r="G271" s="8" t="n">
+        <v>9142</v>
+      </c>
+      <c r="H271" s="8" t="n">
+        <v>994</v>
+      </c>
+      <c r="I271" s="8" t="n">
+        <v>1888</v>
+      </c>
+      <c r="J271" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="K271" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="L271" s="8" t="n">
+        <v>1031</v>
+      </c>
+      <c r="M271" s="8" t="n">
+        <v>5138</v>
+      </c>
+      <c r="N271" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O271" s="8" t="n">
+        <v>1888</v>
+      </c>
+      <c r="P271" s="8" t="n">
+        <v>193</v>
+      </c>
+      <c r="Q271" s="8" t="n">
+        <v>3117</v>
+      </c>
+      <c r="R271" s="8" t="n">
+        <v>8318</v>
+      </c>
+      <c r="S271" s="8" t="n">
+        <v>14281</v>
+      </c>
+      <c r="T271" s="8" t="n">
+        <v>994</v>
+      </c>
+      <c r="U271" s="9" t="n">
+        <v>28792</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="6" t="inlineStr">
+        <is>
+          <t>Odea</t>
+        </is>
+      </c>
+      <c r="B272" s="7" t="inlineStr">
+        <is>
+          <t>2024 Ç4</t>
+        </is>
+      </c>
+      <c r="C272" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D272" s="8" t="n">
+        <v>102</v>
+      </c>
+      <c r="E272" s="8" t="n">
+        <v>3059</v>
+      </c>
+      <c r="F272" s="8" t="n">
+        <v>6006</v>
+      </c>
+      <c r="G272" s="8" t="n">
+        <v>9717</v>
+      </c>
+      <c r="H272" s="8" t="n">
+        <v>999</v>
+      </c>
+      <c r="I272" s="8" t="n">
+        <v>2132</v>
+      </c>
+      <c r="J272" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="K272" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="L272" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M272" s="8" t="n">
+        <v>3951</v>
+      </c>
+      <c r="N272" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O272" s="8" t="n">
+        <v>2133</v>
+      </c>
+      <c r="P272" s="8" t="n">
+        <v>174</v>
+      </c>
+      <c r="Q272" s="8" t="n">
+        <v>3078</v>
+      </c>
+      <c r="R272" s="8" t="n">
+        <v>6008</v>
+      </c>
+      <c r="S272" s="8" t="n">
+        <v>13669</v>
+      </c>
+      <c r="T272" s="8" t="n">
+        <v>999</v>
+      </c>
+      <c r="U272" s="9" t="n">
+        <v>26062</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="6" t="inlineStr">
+        <is>
+          <t>Odea</t>
+        </is>
+      </c>
+      <c r="B273" s="7" t="inlineStr">
+        <is>
           <t>2025 Ç1</t>
         </is>
       </c>
-      <c r="C265" s="8" t="n"/>
-      <c r="D265" s="8" t="n"/>
-      <c r="E265" s="8" t="n">
+      <c r="C273" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D273" s="8" t="n">
+        <v>203</v>
+      </c>
+      <c r="E273" s="8" t="n">
         <v>2925</v>
       </c>
-      <c r="F265" s="8" t="n">
+      <c r="F273" s="8" t="n">
         <v>5543</v>
       </c>
-      <c r="G265" s="8" t="n"/>
-      <c r="H265" s="8" t="n"/>
-      <c r="I265" s="8" t="n"/>
-      <c r="J265" s="8" t="n"/>
-      <c r="K265" s="8" t="n">
+      <c r="G273" s="8" t="n">
+        <v>10318</v>
+      </c>
+      <c r="H273" s="8" t="n">
+        <v>1086</v>
+      </c>
+      <c r="I273" s="8" t="n">
+        <v>2751</v>
+      </c>
+      <c r="J273" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="K273" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="L265" s="8" t="n">
+      <c r="L273" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="M265" s="8" t="n"/>
-      <c r="N265" s="8" t="n"/>
-      <c r="O265" s="8" t="n"/>
-      <c r="P265" s="8" t="n"/>
-      <c r="Q265" s="8" t="n">
+      <c r="M273" s="8" t="n">
+        <v>3339</v>
+      </c>
+      <c r="N273" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O273" s="8" t="n">
+        <v>2751</v>
+      </c>
+      <c r="P273" s="8" t="n">
+        <v>292</v>
+      </c>
+      <c r="Q273" s="8" t="n">
         <v>2944</v>
       </c>
-      <c r="R265" s="8" t="n">
+      <c r="R273" s="8" t="n">
         <v>5545</v>
       </c>
-      <c r="S265" s="8" t="n"/>
-      <c r="T265" s="8" t="n"/>
-      <c r="U265" s="9" t="n">
-        <v>8490</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="10" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="B266" s="11" t="inlineStr">
-        <is>
-          <t>2021 Ç1</t>
-        </is>
-      </c>
-      <c r="C266" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D266" s="12" t="n">
+      <c r="S273" s="8" t="n">
+        <v>13657</v>
+      </c>
+      <c r="T273" s="8" t="n">
+        <v>1086</v>
+      </c>
+      <c r="U273" s="9" t="n">
+        <v>26275</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="6" t="inlineStr">
+        <is>
+          <t>Odea</t>
+        </is>
+      </c>
+      <c r="B274" s="7" t="inlineStr">
+        <is>
+          <t>2025 Ç2</t>
+        </is>
+      </c>
+      <c r="C274" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D274" s="8" t="n">
+        <v>260</v>
+      </c>
+      <c r="E274" s="8" t="n"/>
+      <c r="F274" s="8" t="n"/>
+      <c r="G274" s="8" t="n">
+        <v>10767</v>
+      </c>
+      <c r="H274" s="8" t="n">
+        <v>1162</v>
+      </c>
+      <c r="I274" s="8" t="n">
+        <v>3057</v>
+      </c>
+      <c r="J274" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="K274" s="8" t="n"/>
+      <c r="L274" s="8" t="n"/>
+      <c r="M274" s="8" t="n">
+        <v>766</v>
+      </c>
+      <c r="N274" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O274" s="8" t="n">
+        <v>3057</v>
+      </c>
+      <c r="P274" s="8" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q274" s="8" t="n"/>
+      <c r="R274" s="8" t="n"/>
+      <c r="S274" s="8" t="n">
+        <v>11533</v>
+      </c>
+      <c r="T274" s="8" t="n">
+        <v>1162</v>
+      </c>
+      <c r="U274" s="9" t="n">
+        <v>16102</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="6" t="inlineStr">
+        <is>
+          <t>Odea</t>
+        </is>
+      </c>
+      <c r="B275" s="7" t="inlineStr">
+        <is>
+          <t>2025 Ç3</t>
+        </is>
+      </c>
+      <c r="C275" s="8" t="n">
+        <v>164</v>
+      </c>
+      <c r="D275" s="8" t="n">
+        <v>254</v>
+      </c>
+      <c r="E275" s="8" t="n"/>
+      <c r="F275" s="8" t="n"/>
+      <c r="G275" s="8" t="n">
+        <v>14257</v>
+      </c>
+      <c r="H275" s="8" t="n">
+        <v>1235</v>
+      </c>
+      <c r="I275" s="8" t="n">
+        <v>3364</v>
+      </c>
+      <c r="J275" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="K275" s="8" t="n"/>
+      <c r="L275" s="8" t="n"/>
+      <c r="M275" s="8" t="n">
+        <v>575</v>
+      </c>
+      <c r="N275" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O275" s="8" t="n">
+        <v>3528</v>
+      </c>
+      <c r="P275" s="8" t="n">
+        <v>346</v>
+      </c>
+      <c r="Q275" s="8" t="n"/>
+      <c r="R275" s="8" t="n"/>
+      <c r="S275" s="8" t="n">
+        <v>14831</v>
+      </c>
+      <c r="T275" s="8" t="n">
+        <v>1235</v>
+      </c>
+      <c r="U275" s="9" t="n">
+        <v>19940</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="6" t="inlineStr">
+        <is>
+          <t>Odea</t>
+        </is>
+      </c>
+      <c r="B276" s="7" t="inlineStr">
+        <is>
+          <t>2025 Ç4</t>
+        </is>
+      </c>
+      <c r="C276" s="8" t="n">
+        <v>118</v>
+      </c>
+      <c r="D276" s="8" t="n">
+        <v>234</v>
+      </c>
+      <c r="E276" s="8" t="n">
+        <v>4922</v>
+      </c>
+      <c r="F276" s="8" t="n">
+        <v>10474</v>
+      </c>
+      <c r="G276" s="8" t="n">
+        <v>15167</v>
+      </c>
+      <c r="H276" s="8" t="n">
+        <v>1269</v>
+      </c>
+      <c r="I276" s="8" t="n">
+        <v>3763</v>
+      </c>
+      <c r="J276" s="8" t="n">
+        <v>104</v>
+      </c>
+      <c r="K276" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="L276" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E266" s="12" t="n">
-        <v>2166</v>
-      </c>
-      <c r="F266" s="12" t="n">
-        <v>1663</v>
-      </c>
-      <c r="G266" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H266" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I266" s="12" t="n">
-        <v>546</v>
-      </c>
-      <c r="J266" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K266" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="L266" s="12" t="n">
-        <v>2277</v>
-      </c>
-      <c r="M266" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="N266" s="12" t="n">
-        <v>622</v>
-      </c>
-      <c r="O266" s="12" t="n">
-        <v>546</v>
-      </c>
-      <c r="P266" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q266" s="12" t="n">
-        <v>4056</v>
-      </c>
-      <c r="R266" s="12" t="n">
-        <v>3940</v>
-      </c>
-      <c r="S266" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="T266" s="12" t="n">
-        <v>622</v>
-      </c>
-      <c r="U266" s="13" t="n">
-        <v>9236</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="10" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="B267" s="11" t="inlineStr">
-        <is>
-          <t>2021 Ç2</t>
-        </is>
-      </c>
-      <c r="C267" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D267" s="12" t="n">
+      <c r="M276" s="8" t="n">
+        <v>568</v>
+      </c>
+      <c r="N276" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O276" s="8" t="n">
+        <v>3882</v>
+      </c>
+      <c r="P276" s="8" t="n">
+        <v>338</v>
+      </c>
+      <c r="Q276" s="8" t="n">
+        <v>4952</v>
+      </c>
+      <c r="R276" s="8" t="n">
+        <v>10477</v>
+      </c>
+      <c r="S276" s="8" t="n">
+        <v>15735</v>
+      </c>
+      <c r="T276" s="8" t="n">
+        <v>1269</v>
+      </c>
+      <c r="U276" s="9" t="n">
+        <v>36653</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="6" t="inlineStr">
+        <is>
+          <t>Odea</t>
+        </is>
+      </c>
+      <c r="B277" s="7" t="inlineStr">
+        <is>
+          <t>2026 Ç1</t>
+        </is>
+      </c>
+      <c r="C277" s="8" t="n">
+        <v>577</v>
+      </c>
+      <c r="D277" s="8" t="n">
+        <v>874</v>
+      </c>
+      <c r="E277" s="8" t="n">
+        <v>8718</v>
+      </c>
+      <c r="F277" s="8" t="n">
+        <v>10883</v>
+      </c>
+      <c r="G277" s="8" t="n">
+        <v>15356</v>
+      </c>
+      <c r="H277" s="8" t="n">
+        <v>894</v>
+      </c>
+      <c r="I277" s="8" t="n">
+        <v>4563</v>
+      </c>
+      <c r="J277" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="K277" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="L277" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E267" s="12" t="n">
-        <v>2166</v>
-      </c>
-      <c r="F267" s="12" t="n">
-        <v>1663</v>
-      </c>
-      <c r="G267" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H267" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I267" s="12" t="n">
-        <v>546</v>
-      </c>
-      <c r="J267" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K267" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="L267" s="12" t="n">
-        <v>2277</v>
-      </c>
-      <c r="M267" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="N267" s="12" t="n">
-        <v>622</v>
-      </c>
-      <c r="O267" s="12" t="n">
-        <v>546</v>
-      </c>
-      <c r="P267" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q267" s="12" t="n">
-        <v>4056</v>
-      </c>
-      <c r="R267" s="12" t="n">
-        <v>3940</v>
-      </c>
-      <c r="S267" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="T267" s="12" t="n">
-        <v>622</v>
-      </c>
-      <c r="U267" s="13" t="n">
-        <v>9236</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="10" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="B268" s="11" t="inlineStr">
-        <is>
-          <t>2021 Ç3</t>
-        </is>
-      </c>
-      <c r="C268" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D268" s="12" t="n">
+      <c r="M277" s="8" t="n">
+        <v>708</v>
+      </c>
+      <c r="N277" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O277" s="8" t="n">
+        <v>5140</v>
+      </c>
+      <c r="P277" s="8" t="n">
+        <v>968</v>
+      </c>
+      <c r="Q277" s="8" t="n">
+        <v>8767</v>
+      </c>
+      <c r="R277" s="8" t="n">
+        <v>10886</v>
+      </c>
+      <c r="S277" s="8" t="n">
+        <v>16064</v>
+      </c>
+      <c r="T277" s="8" t="n">
+        <v>894</v>
+      </c>
+      <c r="U277" s="9" t="n">
+        <v>42719</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="6" t="inlineStr">
+        <is>
+          <t>Odea</t>
+        </is>
+      </c>
+      <c r="B278" s="7" t="inlineStr">
+        <is>
+          <t>2026 Ç2</t>
+        </is>
+      </c>
+      <c r="C278" s="8" t="n">
+        <v>1230</v>
+      </c>
+      <c r="D278" s="8" t="n">
+        <v>938</v>
+      </c>
+      <c r="E278" s="8" t="n">
+        <v>14910</v>
+      </c>
+      <c r="F278" s="8" t="n">
+        <v>6878</v>
+      </c>
+      <c r="G278" s="8" t="n">
+        <v>16312</v>
+      </c>
+      <c r="H278" s="8" t="n">
+        <v>925</v>
+      </c>
+      <c r="I278" s="8" t="n">
+        <v>4538</v>
+      </c>
+      <c r="J278" s="8" t="n">
+        <v>113</v>
+      </c>
+      <c r="K278" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="L278" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E268" s="12" t="n">
-        <v>2166</v>
-      </c>
-      <c r="F268" s="12" t="n">
-        <v>1663</v>
-      </c>
-      <c r="G268" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H268" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I268" s="12" t="n">
-        <v>546</v>
-      </c>
-      <c r="J268" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K268" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="L268" s="12" t="n">
-        <v>2277</v>
-      </c>
-      <c r="M268" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="N268" s="12" t="n">
-        <v>622</v>
-      </c>
-      <c r="O268" s="12" t="n">
-        <v>546</v>
-      </c>
-      <c r="P268" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q268" s="12" t="n">
-        <v>4056</v>
-      </c>
-      <c r="R268" s="12" t="n">
-        <v>3940</v>
-      </c>
-      <c r="S268" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="T268" s="12" t="n">
-        <v>622</v>
-      </c>
-      <c r="U268" s="13" t="n">
-        <v>9236</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="10" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="B269" s="11" t="inlineStr">
-        <is>
-          <t>2021 Ç4</t>
-        </is>
-      </c>
-      <c r="C269" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D269" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E269" s="12" t="n">
-        <v>2166</v>
-      </c>
-      <c r="F269" s="12" t="n">
-        <v>1663</v>
-      </c>
-      <c r="G269" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H269" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I269" s="12" t="n">
-        <v>546</v>
-      </c>
-      <c r="J269" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K269" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="L269" s="12" t="n">
-        <v>2277</v>
-      </c>
-      <c r="M269" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="N269" s="12" t="n">
-        <v>622</v>
-      </c>
-      <c r="O269" s="12" t="n">
-        <v>546</v>
-      </c>
-      <c r="P269" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q269" s="12" t="n">
-        <v>4056</v>
-      </c>
-      <c r="R269" s="12" t="n">
-        <v>3940</v>
-      </c>
-      <c r="S269" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="T269" s="12" t="n">
-        <v>622</v>
-      </c>
-      <c r="U269" s="13" t="n">
-        <v>9236</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="10" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="B270" s="11" t="inlineStr">
-        <is>
-          <t>2022 Ç1</t>
-        </is>
-      </c>
-      <c r="C270" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D270" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E270" s="12" t="n">
-        <v>2941</v>
-      </c>
-      <c r="F270" s="12" t="n">
-        <v>2316</v>
-      </c>
-      <c r="G270" s="12" t="n">
-        <v>590</v>
-      </c>
-      <c r="H270" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I270" s="12" t="n">
-        <v>805</v>
-      </c>
-      <c r="J270" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K270" s="12" t="n">
-        <v>1593</v>
-      </c>
-      <c r="L270" s="12" t="n">
-        <v>2075</v>
-      </c>
-      <c r="M270" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="N270" s="12" t="n">
-        <v>694</v>
-      </c>
-      <c r="O270" s="12" t="n">
-        <v>805</v>
-      </c>
-      <c r="P270" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q270" s="12" t="n">
-        <v>4534</v>
-      </c>
-      <c r="R270" s="12" t="n">
-        <v>4392</v>
-      </c>
-      <c r="S270" s="12" t="n">
-        <v>641</v>
-      </c>
-      <c r="T270" s="12" t="n">
-        <v>694</v>
-      </c>
-      <c r="U270" s="13" t="n">
-        <v>11080</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="10" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="B271" s="11" t="inlineStr">
-        <is>
-          <t>2022 Ç2</t>
-        </is>
-      </c>
-      <c r="C271" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D271" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E271" s="12" t="n">
-        <v>2881</v>
-      </c>
-      <c r="F271" s="12" t="n">
-        <v>2483</v>
-      </c>
-      <c r="G271" s="12" t="n">
-        <v>686</v>
-      </c>
-      <c r="H271" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I271" s="12" t="n">
-        <v>1614</v>
-      </c>
-      <c r="J271" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K271" s="12" t="n">
-        <v>2504</v>
-      </c>
-      <c r="L271" s="12" t="n">
-        <v>1298</v>
-      </c>
-      <c r="M271" s="12" t="n">
-        <v>640</v>
-      </c>
-      <c r="N271" s="12" t="n">
-        <v>900</v>
-      </c>
-      <c r="O271" s="12" t="n">
-        <v>1614</v>
-      </c>
-      <c r="P271" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q271" s="12" t="n">
-        <v>5385</v>
-      </c>
-      <c r="R271" s="12" t="n">
-        <v>3780</v>
-      </c>
-      <c r="S271" s="12" t="n">
-        <v>1326</v>
-      </c>
-      <c r="T271" s="12" t="n">
-        <v>900</v>
-      </c>
-      <c r="U271" s="13" t="n">
-        <v>13030</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="10" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="B272" s="11" t="inlineStr">
-        <is>
-          <t>2022 Ç3</t>
-        </is>
-      </c>
-      <c r="C272" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D272" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E272" s="12" t="n">
-        <v>3321</v>
-      </c>
-      <c r="F272" s="12" t="n">
-        <v>3009</v>
-      </c>
-      <c r="G272" s="12" t="n">
-        <v>953</v>
-      </c>
-      <c r="H272" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="I272" s="12" t="n">
-        <v>1669</v>
-      </c>
-      <c r="J272" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="K272" s="12" t="n">
-        <v>2248</v>
-      </c>
-      <c r="L272" s="12" t="n">
-        <v>1732</v>
-      </c>
-      <c r="M272" s="12" t="n">
-        <v>610</v>
-      </c>
-      <c r="N272" s="12" t="n">
-        <v>1168</v>
-      </c>
-      <c r="O272" s="12" t="n">
-        <v>1669</v>
-      </c>
-      <c r="P272" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q272" s="12" t="n">
-        <v>5570</v>
-      </c>
-      <c r="R272" s="12" t="n">
-        <v>4741</v>
-      </c>
-      <c r="S272" s="12" t="n">
-        <v>1563</v>
-      </c>
-      <c r="T272" s="12" t="n">
-        <v>1185</v>
-      </c>
-      <c r="U272" s="13" t="n">
-        <v>14755</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="10" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="B273" s="11" t="inlineStr">
-        <is>
-          <t>2022 Ç4</t>
-        </is>
-      </c>
-      <c r="C273" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D273" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E273" s="12" t="n">
-        <v>3574</v>
-      </c>
-      <c r="F273" s="12" t="n">
-        <v>3328</v>
-      </c>
-      <c r="G273" s="12" t="n">
-        <v>1007</v>
-      </c>
-      <c r="H273" s="12" t="n">
-        <v>270</v>
-      </c>
-      <c r="I273" s="12" t="n">
-        <v>2316</v>
-      </c>
-      <c r="J273" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K273" s="12" t="n">
-        <v>2141</v>
-      </c>
-      <c r="L273" s="12" t="n">
-        <v>2336</v>
-      </c>
-      <c r="M273" s="12" t="n">
-        <v>603</v>
-      </c>
-      <c r="N273" s="12" t="n">
-        <v>1357</v>
-      </c>
-      <c r="O273" s="12" t="n">
-        <v>2316</v>
-      </c>
-      <c r="P273" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q273" s="12" t="n">
-        <v>5716</v>
-      </c>
-      <c r="R273" s="12" t="n">
-        <v>5664</v>
-      </c>
-      <c r="S273" s="12" t="n">
-        <v>1609</v>
-      </c>
-      <c r="T273" s="12" t="n">
-        <v>1627</v>
-      </c>
-      <c r="U273" s="13" t="n">
-        <v>16961</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="10" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="B274" s="11" t="inlineStr">
-        <is>
-          <t>2023 Ç1</t>
-        </is>
-      </c>
-      <c r="C274" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D274" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E274" s="12" t="n">
-        <v>2531</v>
-      </c>
-      <c r="F274" s="12" t="n">
-        <v>3102</v>
-      </c>
-      <c r="G274" s="12" t="n">
-        <v>1080</v>
-      </c>
-      <c r="H274" s="12" t="n">
-        <v>1257</v>
-      </c>
-      <c r="I274" s="12" t="n">
-        <v>2393</v>
-      </c>
-      <c r="J274" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="K274" s="12" t="n">
-        <v>1994</v>
-      </c>
-      <c r="L274" s="12" t="n">
-        <v>2404</v>
-      </c>
-      <c r="M274" s="12" t="n">
-        <v>594</v>
-      </c>
-      <c r="N274" s="12" t="n">
-        <v>1465</v>
-      </c>
-      <c r="O274" s="12" t="n">
-        <v>2393</v>
-      </c>
-      <c r="P274" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q274" s="12" t="n">
-        <v>4525</v>
-      </c>
-      <c r="R274" s="12" t="n">
-        <v>5506</v>
-      </c>
-      <c r="S274" s="12" t="n">
-        <v>1674</v>
-      </c>
-      <c r="T274" s="12" t="n">
-        <v>2722</v>
-      </c>
-      <c r="U274" s="13" t="n">
-        <v>16850</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="10" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="B275" s="11" t="inlineStr">
-        <is>
-          <t>2023 Ç2</t>
-        </is>
-      </c>
-      <c r="C275" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D275" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E275" s="12" t="n">
-        <v>2164</v>
-      </c>
-      <c r="F275" s="12" t="n">
-        <v>4521</v>
-      </c>
-      <c r="G275" s="12" t="n">
-        <v>1305</v>
-      </c>
-      <c r="H275" s="12" t="n">
-        <v>2307</v>
-      </c>
-      <c r="I275" s="12" t="n">
-        <v>2481</v>
-      </c>
-      <c r="J275" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="K275" s="12" t="n">
-        <v>1672</v>
-      </c>
-      <c r="L275" s="12" t="n">
-        <v>3253</v>
-      </c>
-      <c r="M275" s="12" t="n">
-        <v>586</v>
-      </c>
-      <c r="N275" s="12" t="n">
-        <v>1480</v>
-      </c>
-      <c r="O275" s="12" t="n">
-        <v>2481</v>
-      </c>
-      <c r="P275" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q275" s="12" t="n">
-        <v>3836</v>
-      </c>
-      <c r="R275" s="12" t="n">
-        <v>7774</v>
-      </c>
-      <c r="S275" s="12" t="n">
-        <v>1891</v>
-      </c>
-      <c r="T275" s="12" t="n">
-        <v>3787</v>
-      </c>
-      <c r="U275" s="13" t="n">
-        <v>19814</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="10" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="B276" s="11" t="inlineStr">
-        <is>
-          <t>2023 Ç3</t>
-        </is>
-      </c>
-      <c r="C276" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D276" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E276" s="12" t="n">
-        <v>2329</v>
-      </c>
-      <c r="F276" s="12" t="n">
-        <v>4615</v>
-      </c>
-      <c r="G276" s="12" t="n">
-        <v>1753</v>
-      </c>
-      <c r="H276" s="12" t="n">
-        <v>2398</v>
-      </c>
-      <c r="I276" s="12" t="n">
-        <v>2897</v>
-      </c>
-      <c r="J276" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="K276" s="12" t="n">
-        <v>1544</v>
-      </c>
-      <c r="L276" s="12" t="n">
-        <v>3118</v>
-      </c>
-      <c r="M276" s="12" t="n">
-        <v>583</v>
-      </c>
-      <c r="N276" s="12" t="n">
-        <v>577</v>
-      </c>
-      <c r="O276" s="12" t="n">
-        <v>2897</v>
-      </c>
-      <c r="P276" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q276" s="12" t="n">
-        <v>3873</v>
-      </c>
-      <c r="R276" s="12" t="n">
-        <v>7734</v>
-      </c>
-      <c r="S276" s="12" t="n">
-        <v>2336</v>
-      </c>
-      <c r="T276" s="12" t="n">
-        <v>2974</v>
-      </c>
-      <c r="U276" s="13" t="n">
-        <v>19861</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="10" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="B277" s="11" t="inlineStr">
-        <is>
-          <t>2023 Ç4</t>
-        </is>
-      </c>
-      <c r="C277" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D277" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="E277" s="12" t="n">
-        <v>3672</v>
-      </c>
-      <c r="F277" s="12" t="n">
-        <v>5386</v>
-      </c>
-      <c r="G277" s="12" t="n">
-        <v>2642</v>
-      </c>
-      <c r="H277" s="12" t="n">
-        <v>2633</v>
-      </c>
-      <c r="I277" s="12" t="n">
-        <v>3988</v>
-      </c>
-      <c r="J277" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="K277" s="12" t="n">
-        <v>1819</v>
-      </c>
-      <c r="L277" s="12" t="n">
-        <v>3499</v>
-      </c>
-      <c r="M277" s="12" t="n">
-        <v>581</v>
-      </c>
-      <c r="N277" s="12" t="n">
-        <v>295</v>
-      </c>
-      <c r="O277" s="12" t="n">
-        <v>3988</v>
-      </c>
-      <c r="P277" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q277" s="12" t="n">
-        <v>5491</v>
-      </c>
-      <c r="R277" s="12" t="n">
-        <v>8885</v>
-      </c>
-      <c r="S277" s="12" t="n">
-        <v>3223</v>
-      </c>
-      <c r="T277" s="12" t="n">
-        <v>2928</v>
-      </c>
-      <c r="U277" s="13" t="n">
-        <v>24550</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="10" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-      <c r="B278" s="11" t="inlineStr">
-        <is>
-          <t>2024 Ç1</t>
-        </is>
-      </c>
-      <c r="C278" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="D278" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="E278" s="12" t="n">
-        <v>5597</v>
-      </c>
-      <c r="F278" s="12" t="n">
-        <v>6274</v>
-      </c>
-      <c r="G278" s="12" t="n">
-        <v>3134</v>
-      </c>
-      <c r="H278" s="12" t="n">
-        <v>2832</v>
-      </c>
-      <c r="I278" s="12" t="n">
-        <v>4117</v>
-      </c>
-      <c r="J278" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="K278" s="12" t="n">
-        <v>1846</v>
-      </c>
-      <c r="L278" s="12" t="n">
-        <v>4464</v>
-      </c>
-      <c r="M278" s="12" t="n">
-        <v>580</v>
-      </c>
-      <c r="N278" s="12" t="n">
-        <v>329</v>
-      </c>
-      <c r="O278" s="12" t="n">
-        <v>4134</v>
-      </c>
-      <c r="P278" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q278" s="12" t="n">
-        <v>7444</v>
-      </c>
-      <c r="R278" s="12" t="n">
-        <v>10738</v>
-      </c>
-      <c r="S278" s="12" t="n">
-        <v>3713</v>
-      </c>
-      <c r="T278" s="12" t="n">
-        <v>3161</v>
-      </c>
-      <c r="U278" s="13" t="n">
-        <v>29228</v>
+      <c r="M278" s="8" t="n">
+        <v>233</v>
+      </c>
+      <c r="N278" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" s="8" t="n">
+        <v>5768</v>
+      </c>
+      <c r="P278" s="8" t="n">
+        <v>1051</v>
+      </c>
+      <c r="Q278" s="8" t="n">
+        <v>14948</v>
+      </c>
+      <c r="R278" s="8" t="n">
+        <v>6881</v>
+      </c>
+      <c r="S278" s="8" t="n">
+        <v>16545</v>
+      </c>
+      <c r="T278" s="8" t="n">
+        <v>925</v>
+      </c>
+      <c r="U278" s="9" t="n">
+        <v>46118</v>
       </c>
     </row>
     <row r="279">
@@ -18643,65 +18811,65 @@
       </c>
       <c r="B279" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç2</t>
+          <t>2021 Ç1</t>
         </is>
       </c>
       <c r="C279" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D279" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E279" s="12" t="n">
-        <v>5898</v>
+        <v>2166</v>
       </c>
       <c r="F279" s="12" t="n">
-        <v>6215</v>
+        <v>1663</v>
       </c>
       <c r="G279" s="12" t="n">
-        <v>3555</v>
+        <v>0</v>
       </c>
       <c r="H279" s="12" t="n">
-        <v>2940</v>
+        <v>0</v>
       </c>
       <c r="I279" s="12" t="n">
-        <v>3805</v>
+        <v>546</v>
       </c>
       <c r="J279" s="12" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="K279" s="12" t="n">
-        <v>1596</v>
+        <v>1890</v>
       </c>
       <c r="L279" s="12" t="n">
-        <v>1977</v>
+        <v>2277</v>
       </c>
       <c r="M279" s="12" t="n">
-        <v>578</v>
+        <v>65</v>
       </c>
       <c r="N279" s="12" t="n">
-        <v>340</v>
+        <v>622</v>
       </c>
       <c r="O279" s="12" t="n">
-        <v>3840</v>
+        <v>546</v>
       </c>
       <c r="P279" s="12" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="Q279" s="12" t="n">
-        <v>7494</v>
+        <v>4056</v>
       </c>
       <c r="R279" s="12" t="n">
-        <v>8192</v>
+        <v>3940</v>
       </c>
       <c r="S279" s="12" t="n">
-        <v>4132</v>
+        <v>65</v>
       </c>
       <c r="T279" s="12" t="n">
-        <v>3280</v>
+        <v>622</v>
       </c>
       <c r="U279" s="13" t="n">
-        <v>26976</v>
+        <v>9236</v>
       </c>
     </row>
     <row r="280">
@@ -18712,65 +18880,65 @@
       </c>
       <c r="B280" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç3</t>
+          <t>2021 Ç2</t>
         </is>
       </c>
       <c r="C280" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D280" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E280" s="12" t="n">
-        <v>6672</v>
+        <v>2166</v>
       </c>
       <c r="F280" s="12" t="n">
-        <v>6599</v>
+        <v>1663</v>
       </c>
       <c r="G280" s="12" t="n">
-        <v>3769</v>
+        <v>0</v>
       </c>
       <c r="H280" s="12" t="n">
-        <v>2997</v>
+        <v>0</v>
       </c>
       <c r="I280" s="12" t="n">
-        <v>4514</v>
+        <v>546</v>
       </c>
       <c r="J280" s="12" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="K280" s="12" t="n">
-        <v>1439</v>
+        <v>1890</v>
       </c>
       <c r="L280" s="12" t="n">
-        <v>1231</v>
+        <v>2277</v>
       </c>
       <c r="M280" s="12" t="n">
-        <v>576</v>
+        <v>65</v>
       </c>
       <c r="N280" s="12" t="n">
-        <v>359</v>
+        <v>622</v>
       </c>
       <c r="O280" s="12" t="n">
-        <v>4534</v>
+        <v>546</v>
       </c>
       <c r="P280" s="12" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="Q280" s="12" t="n">
-        <v>8110</v>
+        <v>4056</v>
       </c>
       <c r="R280" s="12" t="n">
-        <v>7830</v>
+        <v>3940</v>
       </c>
       <c r="S280" s="12" t="n">
-        <v>4345</v>
+        <v>65</v>
       </c>
       <c r="T280" s="12" t="n">
-        <v>3356</v>
+        <v>622</v>
       </c>
       <c r="U280" s="13" t="n">
-        <v>28216</v>
+        <v>9236</v>
       </c>
     </row>
     <row r="281">
@@ -18781,65 +18949,65 @@
       </c>
       <c r="B281" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç4</t>
+          <t>2021 Ç3</t>
         </is>
       </c>
       <c r="C281" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D281" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E281" s="12" t="n">
+        <v>2166</v>
+      </c>
+      <c r="F281" s="12" t="n">
+        <v>1663</v>
+      </c>
+      <c r="G281" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H281" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I281" s="12" t="n">
+        <v>546</v>
+      </c>
+      <c r="J281" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K281" s="12" t="n">
+        <v>1890</v>
+      </c>
+      <c r="L281" s="12" t="n">
+        <v>2277</v>
+      </c>
+      <c r="M281" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="N281" s="12" t="n">
+        <v>622</v>
+      </c>
+      <c r="O281" s="12" t="n">
+        <v>546</v>
+      </c>
+      <c r="P281" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="E281" s="12" t="n">
-        <v>8060</v>
-      </c>
-      <c r="F281" s="12" t="n">
-        <v>6427</v>
-      </c>
-      <c r="G281" s="12" t="n">
-        <v>3918</v>
-      </c>
-      <c r="H281" s="12" t="n">
-        <v>3164</v>
-      </c>
-      <c r="I281" s="12" t="n">
-        <v>5692</v>
-      </c>
-      <c r="J281" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="K281" s="12" t="n">
-        <v>1348</v>
-      </c>
-      <c r="L281" s="12" t="n">
-        <v>1661</v>
-      </c>
-      <c r="M281" s="12" t="n">
-        <v>575</v>
-      </c>
-      <c r="N281" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O281" s="12" t="n">
-        <v>5724</v>
-      </c>
-      <c r="P281" s="12" t="n">
-        <v>38</v>
-      </c>
       <c r="Q281" s="12" t="n">
-        <v>9409</v>
+        <v>4056</v>
       </c>
       <c r="R281" s="12" t="n">
-        <v>8088</v>
+        <v>3940</v>
       </c>
       <c r="S281" s="12" t="n">
-        <v>4493</v>
+        <v>65</v>
       </c>
       <c r="T281" s="12" t="n">
-        <v>3164</v>
+        <v>622</v>
       </c>
       <c r="U281" s="13" t="n">
-        <v>30915</v>
+        <v>9236</v>
       </c>
     </row>
     <row r="282">
@@ -18850,65 +19018,65 @@
       </c>
       <c r="B282" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç1</t>
+          <t>2021 Ç4</t>
         </is>
       </c>
       <c r="C282" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D282" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E282" s="12" t="n">
+        <v>2166</v>
+      </c>
+      <c r="F282" s="12" t="n">
+        <v>1663</v>
+      </c>
+      <c r="G282" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H282" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I282" s="12" t="n">
+        <v>546</v>
+      </c>
+      <c r="J282" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K282" s="12" t="n">
+        <v>1890</v>
+      </c>
+      <c r="L282" s="12" t="n">
+        <v>2277</v>
+      </c>
+      <c r="M282" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="N282" s="12" t="n">
+        <v>622</v>
+      </c>
+      <c r="O282" s="12" t="n">
+        <v>546</v>
+      </c>
+      <c r="P282" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="E282" s="12" t="n">
-        <v>9734</v>
-      </c>
-      <c r="F282" s="12" t="n">
-        <v>6509</v>
-      </c>
-      <c r="G282" s="12" t="n">
-        <v>4158</v>
-      </c>
-      <c r="H282" s="12" t="n">
-        <v>3322</v>
-      </c>
-      <c r="I282" s="12" t="n">
-        <v>4809</v>
-      </c>
-      <c r="J282" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="K282" s="12" t="n">
-        <v>1334</v>
-      </c>
-      <c r="L282" s="12" t="n">
-        <v>2172</v>
-      </c>
-      <c r="M282" s="12" t="n">
-        <v>574</v>
-      </c>
-      <c r="N282" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O282" s="12" t="n">
-        <v>4834</v>
-      </c>
-      <c r="P282" s="12" t="n">
-        <v>41</v>
-      </c>
       <c r="Q282" s="12" t="n">
-        <v>11068</v>
+        <v>4056</v>
       </c>
       <c r="R282" s="12" t="n">
-        <v>8681</v>
+        <v>3940</v>
       </c>
       <c r="S282" s="12" t="n">
-        <v>4732</v>
+        <v>65</v>
       </c>
       <c r="T282" s="12" t="n">
-        <v>3322</v>
+        <v>622</v>
       </c>
       <c r="U282" s="13" t="n">
-        <v>32678</v>
+        <v>9236</v>
       </c>
     </row>
     <row r="283">
@@ -18919,65 +19087,65 @@
       </c>
       <c r="B283" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç2</t>
+          <t>2022 Ç1</t>
         </is>
       </c>
       <c r="C283" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D283" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E283" s="12" t="n">
-        <v>11294</v>
+        <v>2941</v>
       </c>
       <c r="F283" s="12" t="n">
-        <v>7122</v>
+        <v>2316</v>
       </c>
       <c r="G283" s="12" t="n">
-        <v>2001</v>
+        <v>590</v>
       </c>
       <c r="H283" s="12" t="n">
-        <v>2474</v>
+        <v>0</v>
       </c>
       <c r="I283" s="12" t="n">
-        <v>5259</v>
+        <v>805</v>
       </c>
       <c r="J283" s="12" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="K283" s="12" t="n">
-        <v>972</v>
+        <v>1593</v>
       </c>
       <c r="L283" s="12" t="n">
-        <v>2157</v>
+        <v>2075</v>
       </c>
       <c r="M283" s="12" t="n">
-        <v>574</v>
+        <v>51</v>
       </c>
       <c r="N283" s="12" t="n">
-        <v>0</v>
+        <v>694</v>
       </c>
       <c r="O283" s="12" t="n">
-        <v>5259</v>
+        <v>805</v>
       </c>
       <c r="P283" s="12" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="Q283" s="12" t="n">
-        <v>12266</v>
+        <v>4534</v>
       </c>
       <c r="R283" s="12" t="n">
-        <v>9280</v>
+        <v>4392</v>
       </c>
       <c r="S283" s="12" t="n">
-        <v>2575</v>
+        <v>641</v>
       </c>
       <c r="T283" s="12" t="n">
-        <v>2474</v>
+        <v>694</v>
       </c>
       <c r="U283" s="13" t="n">
-        <v>31898</v>
+        <v>11080</v>
       </c>
     </row>
     <row r="284">
@@ -18988,65 +19156,65 @@
       </c>
       <c r="B284" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç3</t>
+          <t>2022 Ç2</t>
         </is>
       </c>
       <c r="C284" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D284" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E284" s="12" t="n">
-        <v>13376</v>
+        <v>2881</v>
       </c>
       <c r="F284" s="12" t="n">
-        <v>7919</v>
+        <v>2483</v>
       </c>
       <c r="G284" s="12" t="n">
-        <v>3269</v>
+        <v>686</v>
       </c>
       <c r="H284" s="12" t="n">
-        <v>2539</v>
+        <v>0</v>
       </c>
       <c r="I284" s="12" t="n">
-        <v>5683</v>
+        <v>1614</v>
       </c>
       <c r="J284" s="12" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="K284" s="12" t="n">
-        <v>450</v>
+        <v>2504</v>
       </c>
       <c r="L284" s="12" t="n">
-        <v>2126</v>
+        <v>1298</v>
       </c>
       <c r="M284" s="12" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="N284" s="12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="O284" s="12" t="n">
-        <v>5683</v>
+        <v>1614</v>
       </c>
       <c r="P284" s="12" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="Q284" s="12" t="n">
-        <v>13827</v>
+        <v>5385</v>
       </c>
       <c r="R284" s="12" t="n">
-        <v>10045</v>
+        <v>3780</v>
       </c>
       <c r="S284" s="12" t="n">
-        <v>3269</v>
+        <v>1326</v>
       </c>
       <c r="T284" s="12" t="n">
-        <v>2539</v>
+        <v>900</v>
       </c>
       <c r="U284" s="13" t="n">
-        <v>35410</v>
+        <v>13030</v>
       </c>
     </row>
     <row r="285">
@@ -19057,65 +19225,65 @@
       </c>
       <c r="B285" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç4</t>
+          <t>2022 Ç3</t>
         </is>
       </c>
       <c r="C285" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D285" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E285" s="12" t="n">
-        <v>16627</v>
+        <v>3321</v>
       </c>
       <c r="F285" s="12" t="n">
-        <v>8691</v>
+        <v>3009</v>
       </c>
       <c r="G285" s="12" t="n">
-        <v>3263</v>
+        <v>953</v>
       </c>
       <c r="H285" s="12" t="n">
-        <v>2673</v>
+        <v>17</v>
       </c>
       <c r="I285" s="12" t="n">
-        <v>6366</v>
+        <v>1669</v>
       </c>
       <c r="J285" s="12" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="K285" s="12" t="n">
-        <v>350</v>
+        <v>2248</v>
       </c>
       <c r="L285" s="12" t="n">
-        <v>3764</v>
+        <v>1732</v>
       </c>
       <c r="M285" s="12" t="n">
-        <v>0</v>
+        <v>610</v>
       </c>
       <c r="N285" s="12" t="n">
-        <v>0</v>
+        <v>1168</v>
       </c>
       <c r="O285" s="12" t="n">
-        <v>6366</v>
+        <v>1669</v>
       </c>
       <c r="P285" s="12" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="Q285" s="12" t="n">
-        <v>16978</v>
+        <v>5570</v>
       </c>
       <c r="R285" s="12" t="n">
-        <v>12455</v>
+        <v>4741</v>
       </c>
       <c r="S285" s="12" t="n">
-        <v>3263</v>
+        <v>1563</v>
       </c>
       <c r="T285" s="12" t="n">
-        <v>2673</v>
+        <v>1185</v>
       </c>
       <c r="U285" s="13" t="n">
-        <v>41795</v>
+        <v>14755</v>
       </c>
     </row>
     <row r="286">
@@ -19126,65 +19294,65 @@
       </c>
       <c r="B286" s="11" t="inlineStr">
         <is>
-          <t>2026 Ç1</t>
+          <t>2022 Ç4</t>
         </is>
       </c>
       <c r="C286" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D286" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E286" s="12" t="n">
-        <v>13091</v>
+        <v>3574</v>
       </c>
       <c r="F286" s="12" t="n">
-        <v>8627</v>
+        <v>3328</v>
       </c>
       <c r="G286" s="12" t="n">
-        <v>3729</v>
+        <v>1007</v>
       </c>
       <c r="H286" s="12" t="n">
-        <v>2248</v>
+        <v>270</v>
       </c>
       <c r="I286" s="12" t="n">
-        <v>6794</v>
+        <v>2316</v>
       </c>
       <c r="J286" s="12" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="K286" s="12" t="n">
-        <v>350</v>
+        <v>2141</v>
       </c>
       <c r="L286" s="12" t="n">
-        <v>2825</v>
+        <v>2336</v>
       </c>
       <c r="M286" s="12" t="n">
-        <v>0</v>
+        <v>603</v>
       </c>
       <c r="N286" s="12" t="n">
-        <v>446</v>
+        <v>1357</v>
       </c>
       <c r="O286" s="12" t="n">
-        <v>6794</v>
+        <v>2316</v>
       </c>
       <c r="P286" s="12" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="Q286" s="12" t="n">
-        <v>13441</v>
+        <v>5716</v>
       </c>
       <c r="R286" s="12" t="n">
-        <v>11452</v>
+        <v>5664</v>
       </c>
       <c r="S286" s="12" t="n">
-        <v>3729</v>
+        <v>1609</v>
       </c>
       <c r="T286" s="12" t="n">
-        <v>2694</v>
+        <v>1627</v>
       </c>
       <c r="U286" s="13" t="n">
-        <v>38163</v>
+        <v>16961</v>
       </c>
     </row>
     <row r="287">
@@ -19195,910 +19363,1096 @@
       </c>
       <c r="B287" s="11" t="inlineStr">
         <is>
-          <t>2026 Ç2</t>
+          <t>2023 Ç1</t>
         </is>
       </c>
       <c r="C287" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D287" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E287" s="12" t="n">
-        <v>15117</v>
+        <v>2531</v>
       </c>
       <c r="F287" s="12" t="n">
-        <v>9079</v>
+        <v>3102</v>
       </c>
       <c r="G287" s="12" t="n">
-        <v>4446</v>
+        <v>1080</v>
       </c>
       <c r="H287" s="12" t="n">
-        <v>2406</v>
-      </c>
-      <c r="I287" s="12" t="n"/>
+        <v>1257</v>
+      </c>
+      <c r="I287" s="12" t="n">
+        <v>2393</v>
+      </c>
       <c r="J287" s="12" t="n">
-        <v>-13</v>
+        <v>26</v>
       </c>
       <c r="K287" s="12" t="n">
-        <v>22</v>
+        <v>1994</v>
       </c>
       <c r="L287" s="12" t="n">
-        <v>2879</v>
+        <v>2404</v>
       </c>
       <c r="M287" s="12" t="n">
-        <v>0</v>
+        <v>594</v>
       </c>
       <c r="N287" s="12" t="n">
-        <v>468</v>
-      </c>
-      <c r="O287" s="12" t="n"/>
+        <v>1465</v>
+      </c>
+      <c r="O287" s="12" t="n">
+        <v>2393</v>
+      </c>
       <c r="P287" s="12" t="n">
-        <v>-2</v>
+        <v>31</v>
       </c>
       <c r="Q287" s="12" t="n">
-        <v>15139</v>
+        <v>4525</v>
       </c>
       <c r="R287" s="12" t="n">
-        <v>11958</v>
+        <v>5506</v>
       </c>
       <c r="S287" s="12" t="n">
-        <v>4446</v>
+        <v>1674</v>
       </c>
       <c r="T287" s="12" t="n">
-        <v>2874</v>
+        <v>2722</v>
       </c>
       <c r="U287" s="13" t="n">
-        <v>41788</v>
+        <v>16850</v>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="6" t="inlineStr">
-        <is>
-          <t>HSBC</t>
-        </is>
-      </c>
-      <c r="B288" s="7" t="inlineStr">
-        <is>
-          <t>2022 Ç3</t>
-        </is>
-      </c>
-      <c r="C288" s="8" t="n">
-        <v>312</v>
-      </c>
-      <c r="D288" s="8" t="n">
-        <v>222</v>
-      </c>
-      <c r="E288" s="8" t="n">
-        <v>3528</v>
-      </c>
-      <c r="F288" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G288" s="8" t="n">
-        <v>2432</v>
-      </c>
-      <c r="H288" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I288" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J288" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K288" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L288" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M288" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N288" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O288" s="8" t="n">
-        <v>316</v>
-      </c>
-      <c r="P288" s="8" t="n">
-        <v>222</v>
-      </c>
-      <c r="Q288" s="8" t="n">
-        <v>3528</v>
-      </c>
-      <c r="R288" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S288" s="8" t="n">
-        <v>2432</v>
-      </c>
-      <c r="T288" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U288" s="9" t="n">
-        <v>6498</v>
+      <c r="A288" s="10" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="B288" s="11" t="inlineStr">
+        <is>
+          <t>2023 Ç2</t>
+        </is>
+      </c>
+      <c r="C288" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D288" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E288" s="12" t="n">
+        <v>2164</v>
+      </c>
+      <c r="F288" s="12" t="n">
+        <v>4521</v>
+      </c>
+      <c r="G288" s="12" t="n">
+        <v>1305</v>
+      </c>
+      <c r="H288" s="12" t="n">
+        <v>2307</v>
+      </c>
+      <c r="I288" s="12" t="n">
+        <v>2481</v>
+      </c>
+      <c r="J288" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K288" s="12" t="n">
+        <v>1672</v>
+      </c>
+      <c r="L288" s="12" t="n">
+        <v>3253</v>
+      </c>
+      <c r="M288" s="12" t="n">
+        <v>586</v>
+      </c>
+      <c r="N288" s="12" t="n">
+        <v>1480</v>
+      </c>
+      <c r="O288" s="12" t="n">
+        <v>2481</v>
+      </c>
+      <c r="P288" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q288" s="12" t="n">
+        <v>3836</v>
+      </c>
+      <c r="R288" s="12" t="n">
+        <v>7774</v>
+      </c>
+      <c r="S288" s="12" t="n">
+        <v>1891</v>
+      </c>
+      <c r="T288" s="12" t="n">
+        <v>3787</v>
+      </c>
+      <c r="U288" s="13" t="n">
+        <v>19814</v>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="6" t="inlineStr">
-        <is>
-          <t>HSBC</t>
-        </is>
-      </c>
-      <c r="B289" s="7" t="inlineStr">
+      <c r="A289" s="10" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
+      <c r="B289" s="11" t="inlineStr">
         <is>
           <t>2023 Ç3</t>
         </is>
       </c>
-      <c r="C289" s="8" t="n">
-        <v>568</v>
-      </c>
-      <c r="D289" s="8" t="n">
-        <v>272</v>
-      </c>
-      <c r="E289" s="8" t="n">
-        <v>5967</v>
-      </c>
-      <c r="F289" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G289" s="8" t="n">
-        <v>3500</v>
-      </c>
-      <c r="H289" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I289" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="J289" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K289" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L289" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M289" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N289" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O289" s="8" t="n">
-        <v>572</v>
-      </c>
-      <c r="P289" s="8" t="n">
-        <v>272</v>
-      </c>
-      <c r="Q289" s="8" t="n">
-        <v>5967</v>
-      </c>
-      <c r="R289" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S289" s="8" t="n">
-        <v>3500</v>
-      </c>
-      <c r="T289" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U289" s="9" t="n">
-        <v>10311</v>
+      <c r="C289" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D289" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E289" s="12" t="n">
+        <v>2329</v>
+      </c>
+      <c r="F289" s="12" t="n">
+        <v>4615</v>
+      </c>
+      <c r="G289" s="12" t="n">
+        <v>1753</v>
+      </c>
+      <c r="H289" s="12" t="n">
+        <v>2398</v>
+      </c>
+      <c r="I289" s="12" t="n">
+        <v>2897</v>
+      </c>
+      <c r="J289" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="K289" s="12" t="n">
+        <v>1544</v>
+      </c>
+      <c r="L289" s="12" t="n">
+        <v>3118</v>
+      </c>
+      <c r="M289" s="12" t="n">
+        <v>583</v>
+      </c>
+      <c r="N289" s="12" t="n">
+        <v>577</v>
+      </c>
+      <c r="O289" s="12" t="n">
+        <v>2897</v>
+      </c>
+      <c r="P289" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q289" s="12" t="n">
+        <v>3873</v>
+      </c>
+      <c r="R289" s="12" t="n">
+        <v>7734</v>
+      </c>
+      <c r="S289" s="12" t="n">
+        <v>2336</v>
+      </c>
+      <c r="T289" s="12" t="n">
+        <v>2974</v>
+      </c>
+      <c r="U289" s="13" t="n">
+        <v>19861</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="10" t="inlineStr">
         <is>
-          <t>ABank</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="B290" s="11" t="inlineStr">
         <is>
-          <t>2021 Ç1</t>
+          <t>2023 Ç4</t>
         </is>
       </c>
       <c r="C290" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D290" s="12" t="n">
-        <v>315</v>
-      </c>
-      <c r="E290" s="12" t="n"/>
-      <c r="F290" s="12" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="E290" s="12" t="n">
+        <v>3672</v>
+      </c>
+      <c r="F290" s="12" t="n">
+        <v>5386</v>
+      </c>
       <c r="G290" s="12" t="n">
-        <v>76</v>
+        <v>2642</v>
       </c>
       <c r="H290" s="12" t="n">
-        <v>5807</v>
+        <v>2633</v>
       </c>
       <c r="I290" s="12" t="n">
-        <v>0</v>
+        <v>3988</v>
       </c>
       <c r="J290" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K290" s="12" t="n"/>
-      <c r="L290" s="12" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="K290" s="12" t="n">
+        <v>1819</v>
+      </c>
+      <c r="L290" s="12" t="n">
+        <v>3499</v>
+      </c>
       <c r="M290" s="12" t="n">
-        <v>0</v>
+        <v>581</v>
       </c>
       <c r="N290" s="12" t="n">
-        <v>95</v>
+        <v>295</v>
       </c>
       <c r="O290" s="12" t="n">
-        <v>29</v>
+        <v>3988</v>
       </c>
       <c r="P290" s="12" t="n">
-        <v>315</v>
-      </c>
-      <c r="Q290" s="12" t="n"/>
-      <c r="R290" s="12" t="n"/>
+        <v>35</v>
+      </c>
+      <c r="Q290" s="12" t="n">
+        <v>5491</v>
+      </c>
+      <c r="R290" s="12" t="n">
+        <v>8885</v>
+      </c>
       <c r="S290" s="12" t="n">
-        <v>76</v>
+        <v>3223</v>
       </c>
       <c r="T290" s="12" t="n">
-        <v>5903</v>
+        <v>2928</v>
       </c>
       <c r="U290" s="13" t="n">
-        <v>5993</v>
+        <v>24550</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="10" t="inlineStr">
         <is>
-          <t>ABank</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="B291" s="11" t="inlineStr">
         <is>
-          <t>2021 Ç2</t>
+          <t>2024 Ç1</t>
         </is>
       </c>
       <c r="C291" s="12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D291" s="12" t="n">
-        <v>315</v>
-      </c>
-      <c r="E291" s="12" t="n"/>
-      <c r="F291" s="12" t="n"/>
+        <v>13</v>
+      </c>
+      <c r="E291" s="12" t="n">
+        <v>5597</v>
+      </c>
+      <c r="F291" s="12" t="n">
+        <v>6274</v>
+      </c>
       <c r="G291" s="12" t="n">
-        <v>76</v>
+        <v>3134</v>
       </c>
       <c r="H291" s="12" t="n">
-        <v>5807</v>
+        <v>2832</v>
       </c>
       <c r="I291" s="12" t="n">
-        <v>0</v>
+        <v>4117</v>
       </c>
       <c r="J291" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K291" s="12" t="n"/>
-      <c r="L291" s="12" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="K291" s="12" t="n">
+        <v>1846</v>
+      </c>
+      <c r="L291" s="12" t="n">
+        <v>4464</v>
+      </c>
       <c r="M291" s="12" t="n">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="N291" s="12" t="n">
-        <v>95</v>
+        <v>329</v>
       </c>
       <c r="O291" s="12" t="n">
-        <v>20</v>
+        <v>4134</v>
       </c>
       <c r="P291" s="12" t="n">
-        <v>315</v>
-      </c>
-      <c r="Q291" s="12" t="n"/>
-      <c r="R291" s="12" t="n"/>
+        <v>38</v>
+      </c>
+      <c r="Q291" s="12" t="n">
+        <v>7444</v>
+      </c>
+      <c r="R291" s="12" t="n">
+        <v>10738</v>
+      </c>
       <c r="S291" s="12" t="n">
-        <v>76</v>
+        <v>3713</v>
       </c>
       <c r="T291" s="12" t="n">
-        <v>5903</v>
+        <v>3161</v>
       </c>
       <c r="U291" s="13" t="n">
-        <v>5993</v>
+        <v>29228</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="10" t="inlineStr">
         <is>
-          <t>ABank</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="B292" s="11" t="inlineStr">
         <is>
-          <t>2021 Ç3</t>
+          <t>2024 Ç2</t>
         </is>
       </c>
       <c r="C292" s="12" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D292" s="12" t="n">
-        <v>315</v>
-      </c>
-      <c r="E292" s="12" t="n"/>
-      <c r="F292" s="12" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="E292" s="12" t="n">
+        <v>5898</v>
+      </c>
+      <c r="F292" s="12" t="n">
+        <v>6215</v>
+      </c>
       <c r="G292" s="12" t="n">
-        <v>76</v>
+        <v>3555</v>
       </c>
       <c r="H292" s="12" t="n">
-        <v>5807</v>
+        <v>2940</v>
       </c>
       <c r="I292" s="12" t="n">
-        <v>0</v>
+        <v>3805</v>
       </c>
       <c r="J292" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K292" s="12" t="n"/>
-      <c r="L292" s="12" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="K292" s="12" t="n">
+        <v>1596</v>
+      </c>
+      <c r="L292" s="12" t="n">
+        <v>1977</v>
+      </c>
       <c r="M292" s="12" t="n">
-        <v>0</v>
+        <v>578</v>
       </c>
       <c r="N292" s="12" t="n">
-        <v>95</v>
+        <v>340</v>
       </c>
       <c r="O292" s="12" t="n">
-        <v>22</v>
+        <v>3840</v>
       </c>
       <c r="P292" s="12" t="n">
-        <v>315</v>
-      </c>
-      <c r="Q292" s="12" t="n"/>
-      <c r="R292" s="12" t="n"/>
+        <v>38</v>
+      </c>
+      <c r="Q292" s="12" t="n">
+        <v>7494</v>
+      </c>
+      <c r="R292" s="12" t="n">
+        <v>8192</v>
+      </c>
       <c r="S292" s="12" t="n">
-        <v>76</v>
+        <v>4132</v>
       </c>
       <c r="T292" s="12" t="n">
-        <v>5903</v>
+        <v>3280</v>
       </c>
       <c r="U292" s="13" t="n">
-        <v>5993</v>
+        <v>26976</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="10" t="inlineStr">
         <is>
-          <t>ABank</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="B293" s="11" t="inlineStr">
         <is>
-          <t>2021 Ç4</t>
+          <t>2024 Ç3</t>
         </is>
       </c>
       <c r="C293" s="12" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D293" s="12" t="n">
-        <v>315</v>
+        <v>12</v>
       </c>
       <c r="E293" s="12" t="n">
-        <v>1134</v>
+        <v>6672</v>
       </c>
       <c r="F293" s="12" t="n">
-        <v>1517</v>
+        <v>6599</v>
       </c>
       <c r="G293" s="12" t="n">
-        <v>76</v>
+        <v>3769</v>
       </c>
       <c r="H293" s="12" t="n">
-        <v>5807</v>
+        <v>2997</v>
       </c>
       <c r="I293" s="12" t="n">
-        <v>0</v>
+        <v>4514</v>
       </c>
       <c r="J293" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K293" s="12" t="n">
-        <v>51</v>
+        <v>1439</v>
       </c>
       <c r="L293" s="12" t="n">
-        <v>0</v>
+        <v>1231</v>
       </c>
       <c r="M293" s="12" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="N293" s="12" t="n">
-        <v>95</v>
+        <v>359</v>
       </c>
       <c r="O293" s="12" t="n">
-        <v>23</v>
+        <v>4534</v>
       </c>
       <c r="P293" s="12" t="n">
-        <v>315</v>
+        <v>41</v>
       </c>
       <c r="Q293" s="12" t="n">
-        <v>1185</v>
+        <v>8110</v>
       </c>
       <c r="R293" s="12" t="n">
-        <v>1517</v>
+        <v>7830</v>
       </c>
       <c r="S293" s="12" t="n">
-        <v>76</v>
+        <v>4345</v>
       </c>
       <c r="T293" s="12" t="n">
-        <v>5903</v>
+        <v>3356</v>
       </c>
       <c r="U293" s="13" t="n">
-        <v>8695</v>
+        <v>28216</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="10" t="inlineStr">
         <is>
-          <t>ABank</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="B294" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç1</t>
-        </is>
-      </c>
-      <c r="C294" s="12" t="n"/>
+          <t>2024 Ç4</t>
+        </is>
+      </c>
+      <c r="C294" s="12" t="n">
+        <v>33</v>
+      </c>
       <c r="D294" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E294" s="12" t="n"/>
-      <c r="F294" s="12" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="E294" s="12" t="n">
+        <v>8060</v>
+      </c>
+      <c r="F294" s="12" t="n">
+        <v>6427</v>
+      </c>
       <c r="G294" s="12" t="n">
-        <v>74</v>
+        <v>3918</v>
       </c>
       <c r="H294" s="12" t="n">
-        <v>6130</v>
-      </c>
-      <c r="I294" s="12" t="n"/>
+        <v>3164</v>
+      </c>
+      <c r="I294" s="12" t="n">
+        <v>5692</v>
+      </c>
       <c r="J294" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K294" s="12" t="n"/>
-      <c r="L294" s="12" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="K294" s="12" t="n">
+        <v>1348</v>
+      </c>
+      <c r="L294" s="12" t="n">
+        <v>1661</v>
+      </c>
       <c r="M294" s="12" t="n">
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="N294" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="O294" s="12" t="n"/>
+      <c r="O294" s="12" t="n">
+        <v>5724</v>
+      </c>
       <c r="P294" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q294" s="12" t="n"/>
-      <c r="R294" s="12" t="n"/>
+        <v>38</v>
+      </c>
+      <c r="Q294" s="12" t="n">
+        <v>9409</v>
+      </c>
+      <c r="R294" s="12" t="n">
+        <v>8088</v>
+      </c>
       <c r="S294" s="12" t="n">
-        <v>74</v>
+        <v>4493</v>
       </c>
       <c r="T294" s="12" t="n">
-        <v>6130</v>
+        <v>3164</v>
       </c>
       <c r="U294" s="13" t="n">
-        <v>6228</v>
+        <v>30915</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="10" t="inlineStr">
         <is>
-          <t>ABank</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="B295" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç2</t>
-        </is>
-      </c>
-      <c r="C295" s="12" t="n"/>
-      <c r="D295" s="12" t="n"/>
-      <c r="E295" s="12" t="n"/>
-      <c r="F295" s="12" t="n"/>
+          <t>2025 Ç1</t>
+        </is>
+      </c>
+      <c r="C295" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D295" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E295" s="12" t="n">
+        <v>9734</v>
+      </c>
+      <c r="F295" s="12" t="n">
+        <v>6509</v>
+      </c>
       <c r="G295" s="12" t="n">
-        <v>182</v>
+        <v>4158</v>
       </c>
       <c r="H295" s="12" t="n">
-        <v>7056</v>
-      </c>
-      <c r="I295" s="12" t="n"/>
-      <c r="J295" s="12" t="n"/>
-      <c r="K295" s="12" t="n"/>
-      <c r="L295" s="12" t="n"/>
+        <v>3322</v>
+      </c>
+      <c r="I295" s="12" t="n">
+        <v>4809</v>
+      </c>
+      <c r="J295" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K295" s="12" t="n">
+        <v>1334</v>
+      </c>
+      <c r="L295" s="12" t="n">
+        <v>2172</v>
+      </c>
       <c r="M295" s="12" t="n">
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="N295" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="O295" s="12" t="n"/>
-      <c r="P295" s="12" t="n"/>
-      <c r="Q295" s="12" t="n"/>
-      <c r="R295" s="12" t="n"/>
+      <c r="O295" s="12" t="n">
+        <v>4834</v>
+      </c>
+      <c r="P295" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q295" s="12" t="n">
+        <v>11068</v>
+      </c>
+      <c r="R295" s="12" t="n">
+        <v>8681</v>
+      </c>
       <c r="S295" s="12" t="n">
-        <v>182</v>
+        <v>4732</v>
       </c>
       <c r="T295" s="12" t="n">
-        <v>7056</v>
+        <v>3322</v>
       </c>
       <c r="U295" s="13" t="n">
-        <v>7658</v>
+        <v>32678</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="10" t="inlineStr">
         <is>
-          <t>ABank</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="B296" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç3</t>
-        </is>
-      </c>
-      <c r="C296" s="12" t="n"/>
-      <c r="D296" s="12" t="n"/>
-      <c r="E296" s="12" t="n"/>
-      <c r="F296" s="12" t="n"/>
+          <t>2025 Ç2</t>
+        </is>
+      </c>
+      <c r="C296" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D296" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E296" s="12" t="n">
+        <v>11294</v>
+      </c>
+      <c r="F296" s="12" t="n">
+        <v>7122</v>
+      </c>
       <c r="G296" s="12" t="n">
-        <v>796</v>
+        <v>2001</v>
       </c>
       <c r="H296" s="12" t="n">
-        <v>5128</v>
-      </c>
-      <c r="I296" s="12" t="n"/>
-      <c r="J296" s="12" t="n"/>
-      <c r="K296" s="12" t="n"/>
-      <c r="L296" s="12" t="n"/>
+        <v>2474</v>
+      </c>
+      <c r="I296" s="12" t="n">
+        <v>5259</v>
+      </c>
+      <c r="J296" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="K296" s="12" t="n">
+        <v>972</v>
+      </c>
+      <c r="L296" s="12" t="n">
+        <v>2157</v>
+      </c>
       <c r="M296" s="12" t="n">
-        <v>0</v>
+        <v>574</v>
       </c>
       <c r="N296" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="O296" s="12" t="n"/>
-      <c r="P296" s="12" t="n"/>
-      <c r="Q296" s="12" t="n"/>
-      <c r="R296" s="12" t="n"/>
+      <c r="O296" s="12" t="n">
+        <v>5259</v>
+      </c>
+      <c r="P296" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q296" s="12" t="n">
+        <v>12266</v>
+      </c>
+      <c r="R296" s="12" t="n">
+        <v>9280</v>
+      </c>
       <c r="S296" s="12" t="n">
-        <v>796</v>
+        <v>2575</v>
       </c>
       <c r="T296" s="12" t="n">
-        <v>5128</v>
+        <v>2474</v>
       </c>
       <c r="U296" s="13" t="n">
-        <v>6446</v>
+        <v>31898</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="10" t="inlineStr">
         <is>
-          <t>ABank</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="B297" s="11" t="inlineStr">
         <is>
-          <t>2022 Ç4</t>
-        </is>
-      </c>
-      <c r="C297" s="12" t="n"/>
-      <c r="D297" s="12" t="n"/>
+          <t>2025 Ç3</t>
+        </is>
+      </c>
+      <c r="C297" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D297" s="12" t="n">
+        <v>10</v>
+      </c>
       <c r="E297" s="12" t="n">
-        <v>2048</v>
+        <v>13376</v>
       </c>
       <c r="F297" s="12" t="n">
-        <v>2049</v>
+        <v>7919</v>
       </c>
       <c r="G297" s="12" t="n">
-        <v>1502</v>
+        <v>3269</v>
       </c>
       <c r="H297" s="12" t="n">
-        <v>5146</v>
-      </c>
-      <c r="I297" s="12" t="n"/>
-      <c r="J297" s="12" t="n"/>
+        <v>2539</v>
+      </c>
+      <c r="I297" s="12" t="n">
+        <v>5683</v>
+      </c>
+      <c r="J297" s="12" t="n">
+        <v>38</v>
+      </c>
       <c r="K297" s="12" t="n">
-        <v>38</v>
+        <v>450</v>
       </c>
       <c r="L297" s="12" t="n">
-        <v>0</v>
+        <v>2126</v>
       </c>
       <c r="M297" s="12" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="N297" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="O297" s="12" t="n"/>
-      <c r="P297" s="12" t="n"/>
+      <c r="O297" s="12" t="n">
+        <v>5683</v>
+      </c>
+      <c r="P297" s="12" t="n">
+        <v>48</v>
+      </c>
       <c r="Q297" s="12" t="n">
-        <v>2086</v>
+        <v>13827</v>
       </c>
       <c r="R297" s="12" t="n">
-        <v>2049</v>
+        <v>10045</v>
       </c>
       <c r="S297" s="12" t="n">
-        <v>1862</v>
+        <v>3269</v>
       </c>
       <c r="T297" s="12" t="n">
-        <v>5146</v>
+        <v>2539</v>
       </c>
       <c r="U297" s="13" t="n">
-        <v>11766</v>
+        <v>35410</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="10" t="inlineStr">
         <is>
-          <t>ABank</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="B298" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç1</t>
-        </is>
-      </c>
-      <c r="C298" s="12" t="n"/>
+          <t>2025 Ç4</t>
+        </is>
+      </c>
+      <c r="C298" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="D298" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="E298" s="12" t="n"/>
-      <c r="F298" s="12" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="E298" s="12" t="n">
+        <v>16627</v>
+      </c>
+      <c r="F298" s="12" t="n">
+        <v>8691</v>
+      </c>
       <c r="G298" s="12" t="n">
-        <v>1542</v>
+        <v>3263</v>
       </c>
       <c r="H298" s="12" t="n">
-        <v>5294</v>
-      </c>
-      <c r="I298" s="12" t="n"/>
+        <v>2673</v>
+      </c>
+      <c r="I298" s="12" t="n">
+        <v>6366</v>
+      </c>
       <c r="J298" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K298" s="12" t="n"/>
-      <c r="L298" s="12" t="n"/>
+        <v>50</v>
+      </c>
+      <c r="K298" s="12" t="n">
+        <v>350</v>
+      </c>
+      <c r="L298" s="12" t="n">
+        <v>3764</v>
+      </c>
       <c r="M298" s="12" t="n">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="N298" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="O298" s="12" t="n"/>
+      <c r="O298" s="12" t="n">
+        <v>6366</v>
+      </c>
       <c r="P298" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q298" s="12" t="n"/>
-      <c r="R298" s="12" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="Q298" s="12" t="n">
+        <v>16978</v>
+      </c>
+      <c r="R298" s="12" t="n">
+        <v>12455</v>
+      </c>
       <c r="S298" s="12" t="n">
-        <v>1893</v>
+        <v>3263</v>
       </c>
       <c r="T298" s="12" t="n">
-        <v>5294</v>
+        <v>2673</v>
       </c>
       <c r="U298" s="13" t="n">
-        <v>7219</v>
+        <v>41795</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="10" t="inlineStr">
         <is>
-          <t>ABank</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="B299" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç2</t>
-        </is>
-      </c>
-      <c r="C299" s="12" t="n"/>
+          <t>2026 Ç1</t>
+        </is>
+      </c>
+      <c r="C299" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="D299" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E299" s="12" t="n"/>
-      <c r="F299" s="12" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="E299" s="12" t="n">
+        <v>13091</v>
+      </c>
+      <c r="F299" s="12" t="n">
+        <v>8627</v>
+      </c>
       <c r="G299" s="12" t="n">
-        <v>1300</v>
+        <v>3729</v>
       </c>
       <c r="H299" s="12" t="n">
-        <v>7093</v>
-      </c>
-      <c r="I299" s="12" t="n"/>
+        <v>2248</v>
+      </c>
+      <c r="I299" s="12" t="n">
+        <v>6794</v>
+      </c>
       <c r="J299" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K299" s="12" t="n"/>
-      <c r="L299" s="12" t="n"/>
+        <v>41</v>
+      </c>
+      <c r="K299" s="12" t="n">
+        <v>350</v>
+      </c>
+      <c r="L299" s="12" t="n">
+        <v>2825</v>
+      </c>
       <c r="M299" s="12" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="N299" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O299" s="12" t="n"/>
+        <v>446</v>
+      </c>
+      <c r="O299" s="12" t="n">
+        <v>6794</v>
+      </c>
       <c r="P299" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q299" s="12" t="n"/>
-      <c r="R299" s="12" t="n"/>
+        <v>52</v>
+      </c>
+      <c r="Q299" s="12" t="n">
+        <v>13441</v>
+      </c>
+      <c r="R299" s="12" t="n">
+        <v>11452</v>
+      </c>
       <c r="S299" s="12" t="n">
-        <v>1530</v>
+        <v>3729</v>
       </c>
       <c r="T299" s="12" t="n">
-        <v>7093</v>
+        <v>2694</v>
       </c>
       <c r="U299" s="13" t="n">
-        <v>8668</v>
+        <v>38163</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="10" t="inlineStr">
         <is>
-          <t>ABank</t>
+          <t>Aktif</t>
         </is>
       </c>
       <c r="B300" s="11" t="inlineStr">
         <is>
-          <t>2023 Ç3</t>
-        </is>
-      </c>
-      <c r="C300" s="12" t="n"/>
+          <t>2026 Ç2</t>
+        </is>
+      </c>
+      <c r="C300" s="12" t="n">
+        <v>0</v>
+      </c>
       <c r="D300" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E300" s="12" t="n"/>
-      <c r="F300" s="12" t="n"/>
+        <v>11</v>
+      </c>
+      <c r="E300" s="12" t="n">
+        <v>15117</v>
+      </c>
+      <c r="F300" s="12" t="n">
+        <v>9079</v>
+      </c>
       <c r="G300" s="12" t="n">
-        <v>1393</v>
+        <v>4446</v>
       </c>
       <c r="H300" s="12" t="n">
-        <v>7554</v>
+        <v>2406</v>
       </c>
       <c r="I300" s="12" t="n"/>
       <c r="J300" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K300" s="12" t="n"/>
-      <c r="L300" s="12" t="n"/>
+        <v>-13</v>
+      </c>
+      <c r="K300" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="L300" s="12" t="n">
+        <v>2879</v>
+      </c>
       <c r="M300" s="12" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="N300" s="12" t="n">
-        <v>0</v>
+        <v>468</v>
       </c>
       <c r="O300" s="12" t="n"/>
       <c r="P300" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q300" s="12" t="n"/>
-      <c r="R300" s="12" t="n"/>
+        <v>-2</v>
+      </c>
+      <c r="Q300" s="12" t="n">
+        <v>15139</v>
+      </c>
+      <c r="R300" s="12" t="n">
+        <v>11958</v>
+      </c>
       <c r="S300" s="12" t="n">
-        <v>1495</v>
+        <v>4446</v>
       </c>
       <c r="T300" s="12" t="n">
-        <v>7554</v>
+        <v>2874</v>
       </c>
       <c r="U300" s="13" t="n">
-        <v>9068</v>
+        <v>41788</v>
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="10" t="inlineStr">
-        <is>
-          <t>ABank</t>
-        </is>
-      </c>
-      <c r="B301" s="11" t="inlineStr">
-        <is>
-          <t>2023 Ç4</t>
-        </is>
-      </c>
-      <c r="C301" s="12" t="n"/>
-      <c r="D301" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="E301" s="12" t="n">
-        <v>3284</v>
-      </c>
-      <c r="F301" s="12" t="n">
-        <v>3523</v>
-      </c>
-      <c r="G301" s="12" t="n">
-        <v>1448</v>
-      </c>
-      <c r="H301" s="12" t="n">
-        <v>8073</v>
-      </c>
-      <c r="I301" s="12" t="n"/>
-      <c r="J301" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K301" s="12" t="n">
-        <v>167</v>
-      </c>
-      <c r="L301" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M301" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="N301" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O301" s="12" t="n"/>
-      <c r="P301" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q301" s="12" t="n">
-        <v>3451</v>
-      </c>
-      <c r="R301" s="12" t="n">
-        <v>3523</v>
-      </c>
-      <c r="S301" s="12" t="n">
-        <v>1529</v>
-      </c>
-      <c r="T301" s="12" t="n">
-        <v>8073</v>
-      </c>
-      <c r="U301" s="13" t="n">
-        <v>16605</v>
+      <c r="A301" s="6" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="B301" s="7" t="inlineStr">
+        <is>
+          <t>2022 Ç3</t>
+        </is>
+      </c>
+      <c r="C301" s="8" t="n">
+        <v>312</v>
+      </c>
+      <c r="D301" s="8" t="n">
+        <v>222</v>
+      </c>
+      <c r="E301" s="8" t="n">
+        <v>3528</v>
+      </c>
+      <c r="F301" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G301" s="8" t="n">
+        <v>2432</v>
+      </c>
+      <c r="H301" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I301" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J301" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L301" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M301" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N301" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O301" s="8" t="n">
+        <v>316</v>
+      </c>
+      <c r="P301" s="8" t="n">
+        <v>222</v>
+      </c>
+      <c r="Q301" s="8" t="n">
+        <v>3528</v>
+      </c>
+      <c r="R301" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S301" s="8" t="n">
+        <v>2432</v>
+      </c>
+      <c r="T301" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U301" s="9" t="n">
+        <v>6498</v>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="10" t="inlineStr">
-        <is>
-          <t>ABank</t>
-        </is>
-      </c>
-      <c r="B302" s="11" t="inlineStr">
-        <is>
-          <t>2024 Ç1</t>
-        </is>
-      </c>
-      <c r="C302" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="D302" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="E302" s="12" t="n"/>
-      <c r="F302" s="12" t="n"/>
-      <c r="G302" s="12" t="n">
-        <v>1533</v>
-      </c>
-      <c r="H302" s="12" t="n">
-        <v>8086</v>
-      </c>
-      <c r="I302" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J302" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K302" s="12" t="n"/>
-      <c r="L302" s="12" t="n"/>
-      <c r="M302" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="N302" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O302" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="P302" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q302" s="12" t="n"/>
-      <c r="R302" s="12" t="n"/>
-      <c r="S302" s="12" t="n">
-        <v>1566</v>
-      </c>
-      <c r="T302" s="12" t="n">
-        <v>8086</v>
-      </c>
-      <c r="U302" s="13" t="n">
-        <v>9718</v>
+      <c r="A302" s="6" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="B302" s="7" t="inlineStr">
+        <is>
+          <t>2023 Ç3</t>
+        </is>
+      </c>
+      <c r="C302" s="8" t="n">
+        <v>568</v>
+      </c>
+      <c r="D302" s="8" t="n">
+        <v>272</v>
+      </c>
+      <c r="E302" s="8" t="n">
+        <v>5967</v>
+      </c>
+      <c r="F302" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" s="8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H302" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I302" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J302" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L302" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M302" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N302" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O302" s="8" t="n">
+        <v>572</v>
+      </c>
+      <c r="P302" s="8" t="n">
+        <v>272</v>
+      </c>
+      <c r="Q302" s="8" t="n">
+        <v>5967</v>
+      </c>
+      <c r="R302" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S302" s="8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="T302" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U302" s="9" t="n">
+        <v>10311</v>
       </c>
     </row>
     <row r="303">
@@ -20109,22 +20463,22 @@
       </c>
       <c r="B303" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç2</t>
+          <t>2021 Ç1</t>
         </is>
       </c>
       <c r="C303" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D303" s="12" t="n">
-        <v>33</v>
+        <v>315</v>
       </c>
       <c r="E303" s="12" t="n"/>
       <c r="F303" s="12" t="n"/>
       <c r="G303" s="12" t="n">
-        <v>1612</v>
+        <v>76</v>
       </c>
       <c r="H303" s="12" t="n">
-        <v>8155</v>
+        <v>5807</v>
       </c>
       <c r="I303" s="12" t="n">
         <v>0</v>
@@ -20135,27 +20489,27 @@
       <c r="K303" s="12" t="n"/>
       <c r="L303" s="12" t="n"/>
       <c r="M303" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="N303" s="12" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O303" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="P303" s="12" t="n">
-        <v>33</v>
+        <v>315</v>
       </c>
       <c r="Q303" s="12" t="n"/>
       <c r="R303" s="12" t="n"/>
       <c r="S303" s="12" t="n">
-        <v>1650</v>
+        <v>76</v>
       </c>
       <c r="T303" s="12" t="n">
-        <v>8155</v>
+        <v>5903</v>
       </c>
       <c r="U303" s="13" t="n">
-        <v>9839</v>
+        <v>5993</v>
       </c>
     </row>
     <row r="304">
@@ -20166,22 +20520,22 @@
       </c>
       <c r="B304" s="11" t="inlineStr">
         <is>
-          <t>2024 Ç3</t>
+          <t>2021 Ç2</t>
         </is>
       </c>
       <c r="C304" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D304" s="12" t="n">
-        <v>29</v>
+        <v>315</v>
       </c>
       <c r="E304" s="12" t="n"/>
       <c r="F304" s="12" t="n"/>
       <c r="G304" s="12" t="n">
-        <v>1675</v>
+        <v>76</v>
       </c>
       <c r="H304" s="12" t="n">
-        <v>8536</v>
+        <v>5807</v>
       </c>
       <c r="I304" s="12" t="n">
         <v>0</v>
@@ -20192,27 +20546,27 @@
       <c r="K304" s="12" t="n"/>
       <c r="L304" s="12" t="n"/>
       <c r="M304" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="N304" s="12" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O304" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P304" s="12" t="n">
-        <v>29</v>
+        <v>315</v>
       </c>
       <c r="Q304" s="12" t="n"/>
       <c r="R304" s="12" t="n"/>
       <c r="S304" s="12" t="n">
-        <v>1737</v>
+        <v>76</v>
       </c>
       <c r="T304" s="12" t="n">
-        <v>8536</v>
+        <v>5903</v>
       </c>
       <c r="U304" s="13" t="n">
-        <v>10302</v>
+        <v>5993</v>
       </c>
     </row>
     <row r="305">
@@ -20223,26 +20577,22 @@
       </c>
       <c r="B305" s="11" t="inlineStr">
         <is>
-          <t>2025 Ç1</t>
+          <t>2021 Ç3</t>
         </is>
       </c>
       <c r="C305" s="12" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="D305" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E305" s="12" t="n">
-        <v>3011</v>
-      </c>
-      <c r="F305" s="12" t="n">
-        <v>4383</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="E305" s="12" t="n"/>
+      <c r="F305" s="12" t="n"/>
       <c r="G305" s="12" t="n">
-        <v>1816</v>
+        <v>76</v>
       </c>
       <c r="H305" s="12" t="n">
-        <v>8103</v>
+        <v>5807</v>
       </c>
       <c r="I305" s="12" t="n">
         <v>0</v>
@@ -20250,38 +20600,30 @@
       <c r="J305" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K305" s="12" t="n">
-        <v>615</v>
-      </c>
-      <c r="L305" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="K305" s="12" t="n"/>
+      <c r="L305" s="12" t="n"/>
       <c r="M305" s="12" t="n">
-        <v>1326</v>
+        <v>0</v>
       </c>
       <c r="N305" s="12" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O305" s="12" t="n">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="P305" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q305" s="12" t="n">
-        <v>3626</v>
-      </c>
-      <c r="R305" s="12" t="n">
-        <v>4383</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="Q305" s="12" t="n"/>
+      <c r="R305" s="12" t="n"/>
       <c r="S305" s="12" t="n">
-        <v>3142</v>
+        <v>76</v>
       </c>
       <c r="T305" s="12" t="n">
-        <v>8103</v>
+        <v>5903</v>
       </c>
       <c r="U305" s="13" t="n">
-        <v>19308</v>
+        <v>5993</v>
       </c>
     </row>
     <row r="306">
@@ -20292,828 +20634,1551 @@
       </c>
       <c r="B306" s="11" t="inlineStr">
         <is>
+          <t>2021 Ç4</t>
+        </is>
+      </c>
+      <c r="C306" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="D306" s="12" t="n">
+        <v>315</v>
+      </c>
+      <c r="E306" s="12" t="n">
+        <v>1134</v>
+      </c>
+      <c r="F306" s="12" t="n">
+        <v>1517</v>
+      </c>
+      <c r="G306" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="H306" s="12" t="n">
+        <v>5807</v>
+      </c>
+      <c r="I306" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J306" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K306" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="L306" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M306" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N306" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="O306" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="P306" s="12" t="n">
+        <v>315</v>
+      </c>
+      <c r="Q306" s="12" t="n">
+        <v>1185</v>
+      </c>
+      <c r="R306" s="12" t="n">
+        <v>1517</v>
+      </c>
+      <c r="S306" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="T306" s="12" t="n">
+        <v>5903</v>
+      </c>
+      <c r="U306" s="13" t="n">
+        <v>8695</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="10" t="inlineStr">
+        <is>
+          <t>ABank</t>
+        </is>
+      </c>
+      <c r="B307" s="11" t="inlineStr">
+        <is>
+          <t>2022 Ç1</t>
+        </is>
+      </c>
+      <c r="C307" s="12" t="n"/>
+      <c r="D307" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E307" s="12" t="n"/>
+      <c r="F307" s="12" t="n"/>
+      <c r="G307" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="H307" s="12" t="n">
+        <v>6130</v>
+      </c>
+      <c r="I307" s="12" t="n"/>
+      <c r="J307" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K307" s="12" t="n"/>
+      <c r="L307" s="12" t="n"/>
+      <c r="M307" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N307" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O307" s="12" t="n"/>
+      <c r="P307" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q307" s="12" t="n"/>
+      <c r="R307" s="12" t="n"/>
+      <c r="S307" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="T307" s="12" t="n">
+        <v>6130</v>
+      </c>
+      <c r="U307" s="13" t="n">
+        <v>6228</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="10" t="inlineStr">
+        <is>
+          <t>ABank</t>
+        </is>
+      </c>
+      <c r="B308" s="11" t="inlineStr">
+        <is>
+          <t>2022 Ç2</t>
+        </is>
+      </c>
+      <c r="C308" s="12" t="n"/>
+      <c r="D308" s="12" t="n"/>
+      <c r="E308" s="12" t="n"/>
+      <c r="F308" s="12" t="n"/>
+      <c r="G308" s="12" t="n">
+        <v>182</v>
+      </c>
+      <c r="H308" s="12" t="n">
+        <v>7056</v>
+      </c>
+      <c r="I308" s="12" t="n"/>
+      <c r="J308" s="12" t="n"/>
+      <c r="K308" s="12" t="n"/>
+      <c r="L308" s="12" t="n"/>
+      <c r="M308" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N308" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O308" s="12" t="n"/>
+      <c r="P308" s="12" t="n"/>
+      <c r="Q308" s="12" t="n"/>
+      <c r="R308" s="12" t="n"/>
+      <c r="S308" s="12" t="n">
+        <v>182</v>
+      </c>
+      <c r="T308" s="12" t="n">
+        <v>7056</v>
+      </c>
+      <c r="U308" s="13" t="n">
+        <v>7658</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="10" t="inlineStr">
+        <is>
+          <t>ABank</t>
+        </is>
+      </c>
+      <c r="B309" s="11" t="inlineStr">
+        <is>
+          <t>2022 Ç3</t>
+        </is>
+      </c>
+      <c r="C309" s="12" t="n"/>
+      <c r="D309" s="12" t="n"/>
+      <c r="E309" s="12" t="n"/>
+      <c r="F309" s="12" t="n"/>
+      <c r="G309" s="12" t="n">
+        <v>796</v>
+      </c>
+      <c r="H309" s="12" t="n">
+        <v>5128</v>
+      </c>
+      <c r="I309" s="12" t="n"/>
+      <c r="J309" s="12" t="n"/>
+      <c r="K309" s="12" t="n"/>
+      <c r="L309" s="12" t="n"/>
+      <c r="M309" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N309" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O309" s="12" t="n"/>
+      <c r="P309" s="12" t="n"/>
+      <c r="Q309" s="12" t="n"/>
+      <c r="R309" s="12" t="n"/>
+      <c r="S309" s="12" t="n">
+        <v>796</v>
+      </c>
+      <c r="T309" s="12" t="n">
+        <v>5128</v>
+      </c>
+      <c r="U309" s="13" t="n">
+        <v>6446</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="10" t="inlineStr">
+        <is>
+          <t>ABank</t>
+        </is>
+      </c>
+      <c r="B310" s="11" t="inlineStr">
+        <is>
+          <t>2022 Ç4</t>
+        </is>
+      </c>
+      <c r="C310" s="12" t="n"/>
+      <c r="D310" s="12" t="n"/>
+      <c r="E310" s="12" t="n">
+        <v>2048</v>
+      </c>
+      <c r="F310" s="12" t="n">
+        <v>2049</v>
+      </c>
+      <c r="G310" s="12" t="n">
+        <v>1502</v>
+      </c>
+      <c r="H310" s="12" t="n">
+        <v>5146</v>
+      </c>
+      <c r="I310" s="12" t="n"/>
+      <c r="J310" s="12" t="n"/>
+      <c r="K310" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="L310" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M310" s="12" t="n">
+        <v>360</v>
+      </c>
+      <c r="N310" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O310" s="12" t="n"/>
+      <c r="P310" s="12" t="n"/>
+      <c r="Q310" s="12" t="n">
+        <v>2086</v>
+      </c>
+      <c r="R310" s="12" t="n">
+        <v>2049</v>
+      </c>
+      <c r="S310" s="12" t="n">
+        <v>1862</v>
+      </c>
+      <c r="T310" s="12" t="n">
+        <v>5146</v>
+      </c>
+      <c r="U310" s="13" t="n">
+        <v>11766</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="10" t="inlineStr">
+        <is>
+          <t>ABank</t>
+        </is>
+      </c>
+      <c r="B311" s="11" t="inlineStr">
+        <is>
+          <t>2023 Ç1</t>
+        </is>
+      </c>
+      <c r="C311" s="12" t="n"/>
+      <c r="D311" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E311" s="12" t="n"/>
+      <c r="F311" s="12" t="n"/>
+      <c r="G311" s="12" t="n">
+        <v>1542</v>
+      </c>
+      <c r="H311" s="12" t="n">
+        <v>5294</v>
+      </c>
+      <c r="I311" s="12" t="n"/>
+      <c r="J311" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" s="12" t="n"/>
+      <c r="L311" s="12" t="n"/>
+      <c r="M311" s="12" t="n">
+        <v>351</v>
+      </c>
+      <c r="N311" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O311" s="12" t="n"/>
+      <c r="P311" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q311" s="12" t="n"/>
+      <c r="R311" s="12" t="n"/>
+      <c r="S311" s="12" t="n">
+        <v>1893</v>
+      </c>
+      <c r="T311" s="12" t="n">
+        <v>5294</v>
+      </c>
+      <c r="U311" s="13" t="n">
+        <v>7219</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="10" t="inlineStr">
+        <is>
+          <t>ABank</t>
+        </is>
+      </c>
+      <c r="B312" s="11" t="inlineStr">
+        <is>
+          <t>2023 Ç2</t>
+        </is>
+      </c>
+      <c r="C312" s="12" t="n"/>
+      <c r="D312" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E312" s="12" t="n"/>
+      <c r="F312" s="12" t="n"/>
+      <c r="G312" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="H312" s="12" t="n">
+        <v>7093</v>
+      </c>
+      <c r="I312" s="12" t="n"/>
+      <c r="J312" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K312" s="12" t="n"/>
+      <c r="L312" s="12" t="n"/>
+      <c r="M312" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="N312" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O312" s="12" t="n"/>
+      <c r="P312" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q312" s="12" t="n"/>
+      <c r="R312" s="12" t="n"/>
+      <c r="S312" s="12" t="n">
+        <v>1530</v>
+      </c>
+      <c r="T312" s="12" t="n">
+        <v>7093</v>
+      </c>
+      <c r="U312" s="13" t="n">
+        <v>8668</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="10" t="inlineStr">
+        <is>
+          <t>ABank</t>
+        </is>
+      </c>
+      <c r="B313" s="11" t="inlineStr">
+        <is>
+          <t>2023 Ç3</t>
+        </is>
+      </c>
+      <c r="C313" s="12" t="n"/>
+      <c r="D313" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E313" s="12" t="n"/>
+      <c r="F313" s="12" t="n"/>
+      <c r="G313" s="12" t="n">
+        <v>1393</v>
+      </c>
+      <c r="H313" s="12" t="n">
+        <v>7554</v>
+      </c>
+      <c r="I313" s="12" t="n"/>
+      <c r="J313" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K313" s="12" t="n"/>
+      <c r="L313" s="12" t="n"/>
+      <c r="M313" s="12" t="n">
+        <v>102</v>
+      </c>
+      <c r="N313" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O313" s="12" t="n"/>
+      <c r="P313" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q313" s="12" t="n"/>
+      <c r="R313" s="12" t="n"/>
+      <c r="S313" s="12" t="n">
+        <v>1495</v>
+      </c>
+      <c r="T313" s="12" t="n">
+        <v>7554</v>
+      </c>
+      <c r="U313" s="13" t="n">
+        <v>9068</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="10" t="inlineStr">
+        <is>
+          <t>ABank</t>
+        </is>
+      </c>
+      <c r="B314" s="11" t="inlineStr">
+        <is>
+          <t>2023 Ç4</t>
+        </is>
+      </c>
+      <c r="C314" s="12" t="n"/>
+      <c r="D314" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E314" s="12" t="n">
+        <v>3284</v>
+      </c>
+      <c r="F314" s="12" t="n">
+        <v>3523</v>
+      </c>
+      <c r="G314" s="12" t="n">
+        <v>1448</v>
+      </c>
+      <c r="H314" s="12" t="n">
+        <v>8073</v>
+      </c>
+      <c r="I314" s="12" t="n"/>
+      <c r="J314" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K314" s="12" t="n">
+        <v>167</v>
+      </c>
+      <c r="L314" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M314" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="N314" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O314" s="12" t="n"/>
+      <c r="P314" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q314" s="12" t="n">
+        <v>3451</v>
+      </c>
+      <c r="R314" s="12" t="n">
+        <v>3523</v>
+      </c>
+      <c r="S314" s="12" t="n">
+        <v>1529</v>
+      </c>
+      <c r="T314" s="12" t="n">
+        <v>8073</v>
+      </c>
+      <c r="U314" s="13" t="n">
+        <v>16605</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="10" t="inlineStr">
+        <is>
+          <t>ABank</t>
+        </is>
+      </c>
+      <c r="B315" s="11" t="inlineStr">
+        <is>
+          <t>2024 Ç1</t>
+        </is>
+      </c>
+      <c r="C315" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="D315" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="E315" s="12" t="n"/>
+      <c r="F315" s="12" t="n"/>
+      <c r="G315" s="12" t="n">
+        <v>1533</v>
+      </c>
+      <c r="H315" s="12" t="n">
+        <v>8086</v>
+      </c>
+      <c r="I315" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J315" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K315" s="12" t="n"/>
+      <c r="L315" s="12" t="n"/>
+      <c r="M315" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="N315" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O315" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="P315" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q315" s="12" t="n"/>
+      <c r="R315" s="12" t="n"/>
+      <c r="S315" s="12" t="n">
+        <v>1566</v>
+      </c>
+      <c r="T315" s="12" t="n">
+        <v>8086</v>
+      </c>
+      <c r="U315" s="13" t="n">
+        <v>9718</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="10" t="inlineStr">
+        <is>
+          <t>ABank</t>
+        </is>
+      </c>
+      <c r="B316" s="11" t="inlineStr">
+        <is>
+          <t>2024 Ç2</t>
+        </is>
+      </c>
+      <c r="C316" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D316" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="E316" s="12" t="n"/>
+      <c r="F316" s="12" t="n"/>
+      <c r="G316" s="12" t="n">
+        <v>1612</v>
+      </c>
+      <c r="H316" s="12" t="n">
+        <v>8155</v>
+      </c>
+      <c r="I316" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J316" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K316" s="12" t="n"/>
+      <c r="L316" s="12" t="n"/>
+      <c r="M316" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="N316" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O316" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P316" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q316" s="12" t="n"/>
+      <c r="R316" s="12" t="n"/>
+      <c r="S316" s="12" t="n">
+        <v>1650</v>
+      </c>
+      <c r="T316" s="12" t="n">
+        <v>8155</v>
+      </c>
+      <c r="U316" s="13" t="n">
+        <v>9839</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="10" t="inlineStr">
+        <is>
+          <t>ABank</t>
+        </is>
+      </c>
+      <c r="B317" s="11" t="inlineStr">
+        <is>
+          <t>2024 Ç3</t>
+        </is>
+      </c>
+      <c r="C317" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D317" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="E317" s="12" t="n"/>
+      <c r="F317" s="12" t="n"/>
+      <c r="G317" s="12" t="n">
+        <v>1675</v>
+      </c>
+      <c r="H317" s="12" t="n">
+        <v>8536</v>
+      </c>
+      <c r="I317" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J317" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K317" s="12" t="n"/>
+      <c r="L317" s="12" t="n"/>
+      <c r="M317" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="N317" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O317" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P317" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q317" s="12" t="n"/>
+      <c r="R317" s="12" t="n"/>
+      <c r="S317" s="12" t="n">
+        <v>1737</v>
+      </c>
+      <c r="T317" s="12" t="n">
+        <v>8536</v>
+      </c>
+      <c r="U317" s="13" t="n">
+        <v>10302</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="10" t="inlineStr">
+        <is>
+          <t>ABank</t>
+        </is>
+      </c>
+      <c r="B318" s="11" t="inlineStr">
+        <is>
+          <t>2025 Ç1</t>
+        </is>
+      </c>
+      <c r="C318" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="D318" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E318" s="12" t="n">
+        <v>3011</v>
+      </c>
+      <c r="F318" s="12" t="n">
+        <v>4383</v>
+      </c>
+      <c r="G318" s="12" t="n">
+        <v>1816</v>
+      </c>
+      <c r="H318" s="12" t="n">
+        <v>8103</v>
+      </c>
+      <c r="I318" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K318" s="12" t="n">
+        <v>615</v>
+      </c>
+      <c r="L318" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M318" s="12" t="n">
+        <v>1326</v>
+      </c>
+      <c r="N318" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O318" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="P318" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q318" s="12" t="n">
+        <v>3626</v>
+      </c>
+      <c r="R318" s="12" t="n">
+        <v>4383</v>
+      </c>
+      <c r="S318" s="12" t="n">
+        <v>3142</v>
+      </c>
+      <c r="T318" s="12" t="n">
+        <v>8103</v>
+      </c>
+      <c r="U318" s="13" t="n">
+        <v>19308</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="10" t="inlineStr">
+        <is>
+          <t>ABank</t>
+        </is>
+      </c>
+      <c r="B319" s="11" t="inlineStr">
+        <is>
           <t>2025 Ç2</t>
         </is>
       </c>
-      <c r="C306" s="12" t="n">
+      <c r="C319" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="D306" s="12" t="n">
+      <c r="D319" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="E306" s="12" t="n">
+      <c r="E319" s="12" t="n">
         <v>2624</v>
       </c>
-      <c r="F306" s="12" t="n">
+      <c r="F319" s="12" t="n">
         <v>4641</v>
       </c>
-      <c r="G306" s="12" t="n">
+      <c r="G319" s="12" t="n">
         <v>1821</v>
       </c>
-      <c r="H306" s="12" t="n">
+      <c r="H319" s="12" t="n">
         <v>8441</v>
       </c>
-      <c r="I306" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J306" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K306" s="12" t="n">
+      <c r="I319" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J319" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K319" s="12" t="n">
         <v>152</v>
       </c>
-      <c r="L306" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M306" s="12" t="n">
+      <c r="L319" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M319" s="12" t="n">
         <v>1630</v>
       </c>
-      <c r="N306" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O306" s="12" t="n">
+      <c r="N319" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O319" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="P306" s="12" t="n">
+      <c r="P319" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="Q306" s="12" t="n">
+      <c r="Q319" s="12" t="n">
         <v>2776</v>
       </c>
-      <c r="R306" s="12" t="n">
+      <c r="R319" s="12" t="n">
         <v>4641</v>
       </c>
-      <c r="S306" s="12" t="n">
+      <c r="S319" s="12" t="n">
         <v>3450</v>
       </c>
-      <c r="T306" s="12" t="n">
+      <c r="T319" s="12" t="n">
         <v>8441</v>
       </c>
-      <c r="U306" s="13" t="n">
+      <c r="U319" s="13" t="n">
         <v>19365</v>
       </c>
     </row>
-    <row r="307">
-      <c r="A307" s="6" t="inlineStr">
+    <row r="320">
+      <c r="A320" s="6" t="inlineStr">
         <is>
           <t>Şeker</t>
         </is>
       </c>
-      <c r="B307" s="7" t="inlineStr">
+      <c r="B320" s="7" t="inlineStr">
         <is>
           <t>2021 Ç1</t>
         </is>
       </c>
-      <c r="C307" s="8" t="n">
+      <c r="C320" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D307" s="8" t="n">
+      <c r="D320" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="E307" s="8" t="n">
+      <c r="E320" s="8" t="n">
         <v>517</v>
       </c>
-      <c r="F307" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G307" s="8" t="n">
+      <c r="F320" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G320" s="8" t="n">
         <v>2583</v>
       </c>
-      <c r="H307" s="8" t="n">
+      <c r="H320" s="8" t="n">
         <v>1266</v>
       </c>
-      <c r="I307" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J307" s="8" t="n">
+      <c r="I320" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J320" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="K307" s="8" t="n">
+      <c r="K320" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="L307" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M307" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N307" s="8" t="n">
+      <c r="L320" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M320" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N320" s="8" t="n">
         <v>1503</v>
       </c>
-      <c r="O307" s="8" t="n">
+      <c r="O320" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="P307" s="8" t="n">
+      <c r="P320" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="Q307" s="8" t="n">
+      <c r="Q320" s="8" t="n">
         <v>524</v>
       </c>
-      <c r="R307" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S307" s="8" t="n">
+      <c r="R320" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S320" s="8" t="n">
         <v>2583</v>
       </c>
-      <c r="T307" s="8" t="n">
+      <c r="T320" s="8" t="n">
         <v>2768</v>
       </c>
-      <c r="U307" s="9" t="n">
+      <c r="U320" s="9" t="n">
         <v>5947</v>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" s="6" t="inlineStr">
+    <row r="321">
+      <c r="A321" s="6" t="inlineStr">
         <is>
           <t>Şeker</t>
         </is>
       </c>
-      <c r="B308" s="7" t="inlineStr">
+      <c r="B321" s="7" t="inlineStr">
         <is>
           <t>2021 Ç2</t>
         </is>
       </c>
-      <c r="C308" s="8" t="n">
+      <c r="C321" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D308" s="8" t="n">
+      <c r="D321" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="E308" s="8" t="n">
+      <c r="E321" s="8" t="n">
         <v>517</v>
       </c>
-      <c r="F308" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G308" s="8" t="n">
+      <c r="F321" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G321" s="8" t="n">
         <v>2583</v>
       </c>
-      <c r="H308" s="8" t="n">
+      <c r="H321" s="8" t="n">
         <v>1266</v>
       </c>
-      <c r="I308" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J308" s="8" t="n">
+      <c r="I321" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J321" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="K308" s="8" t="n">
+      <c r="K321" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="L308" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M308" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N308" s="8" t="n">
+      <c r="L321" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M321" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N321" s="8" t="n">
         <v>1503</v>
       </c>
-      <c r="O308" s="8" t="n">
+      <c r="O321" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="P308" s="8" t="n">
+      <c r="P321" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="Q308" s="8" t="n">
+      <c r="Q321" s="8" t="n">
         <v>524</v>
       </c>
-      <c r="R308" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S308" s="8" t="n">
+      <c r="R321" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S321" s="8" t="n">
         <v>2583</v>
       </c>
-      <c r="T308" s="8" t="n">
+      <c r="T321" s="8" t="n">
         <v>2768</v>
       </c>
-      <c r="U308" s="9" t="n">
+      <c r="U321" s="9" t="n">
         <v>5947</v>
       </c>
     </row>
-    <row r="309">
-      <c r="A309" s="6" t="inlineStr">
+    <row r="322">
+      <c r="A322" s="6" t="inlineStr">
         <is>
           <t>Şeker</t>
         </is>
       </c>
-      <c r="B309" s="7" t="inlineStr">
+      <c r="B322" s="7" t="inlineStr">
         <is>
           <t>2021 Ç3</t>
         </is>
       </c>
-      <c r="C309" s="8" t="n">
+      <c r="C322" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D309" s="8" t="n">
+      <c r="D322" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="E309" s="8" t="n">
+      <c r="E322" s="8" t="n">
         <v>517</v>
       </c>
-      <c r="F309" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G309" s="8" t="n">
+      <c r="F322" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G322" s="8" t="n">
         <v>2583</v>
       </c>
-      <c r="H309" s="8" t="n">
+      <c r="H322" s="8" t="n">
         <v>1266</v>
       </c>
-      <c r="I309" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J309" s="8" t="n">
+      <c r="I322" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J322" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="K309" s="8" t="n">
+      <c r="K322" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="L309" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M309" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N309" s="8" t="n">
+      <c r="L322" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M322" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N322" s="8" t="n">
         <v>1503</v>
       </c>
-      <c r="O309" s="8" t="n">
+      <c r="O322" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="P309" s="8" t="n">
+      <c r="P322" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="Q309" s="8" t="n">
+      <c r="Q322" s="8" t="n">
         <v>524</v>
       </c>
-      <c r="R309" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S309" s="8" t="n">
+      <c r="R322" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S322" s="8" t="n">
         <v>2583</v>
       </c>
-      <c r="T309" s="8" t="n">
+      <c r="T322" s="8" t="n">
         <v>2768</v>
       </c>
-      <c r="U309" s="9" t="n">
+      <c r="U322" s="9" t="n">
         <v>5947</v>
       </c>
     </row>
-    <row r="310">
-      <c r="A310" s="6" t="inlineStr">
+    <row r="323">
+      <c r="A323" s="6" t="inlineStr">
         <is>
           <t>Şeker</t>
         </is>
       </c>
-      <c r="B310" s="7" t="inlineStr">
+      <c r="B323" s="7" t="inlineStr">
         <is>
           <t>2021 Ç4</t>
         </is>
       </c>
-      <c r="C310" s="8" t="n">
+      <c r="C323" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D310" s="8" t="n">
+      <c r="D323" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="E310" s="8" t="n">
+      <c r="E323" s="8" t="n">
         <v>517</v>
       </c>
-      <c r="F310" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G310" s="8" t="n">
+      <c r="F323" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G323" s="8" t="n">
         <v>2583</v>
       </c>
-      <c r="H310" s="8" t="n">
+      <c r="H323" s="8" t="n">
         <v>1266</v>
       </c>
-      <c r="I310" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J310" s="8" t="n">
+      <c r="I323" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J323" s="8" t="n">
         <v>62</v>
       </c>
-      <c r="K310" s="8" t="n">
+      <c r="K323" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="L310" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M310" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N310" s="8" t="n">
+      <c r="L323" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M323" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N323" s="8" t="n">
         <v>1503</v>
       </c>
-      <c r="O310" s="8" t="n">
+      <c r="O323" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="P310" s="8" t="n">
+      <c r="P323" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="Q310" s="8" t="n">
+      <c r="Q323" s="8" t="n">
         <v>524</v>
       </c>
-      <c r="R310" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S310" s="8" t="n">
+      <c r="R323" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S323" s="8" t="n">
         <v>2583</v>
       </c>
-      <c r="T310" s="8" t="n">
+      <c r="T323" s="8" t="n">
         <v>2768</v>
       </c>
-      <c r="U310" s="9" t="n">
+      <c r="U323" s="9" t="n">
         <v>5947</v>
       </c>
     </row>
-    <row r="311">
-      <c r="A311" s="6" t="inlineStr">
+    <row r="324">
+      <c r="A324" s="6" t="inlineStr">
         <is>
           <t>Şeker</t>
         </is>
       </c>
-      <c r="B311" s="7" t="inlineStr">
+      <c r="B324" s="7" t="inlineStr">
         <is>
           <t>2022 Ç1</t>
         </is>
       </c>
-      <c r="C311" s="8" t="n">
+      <c r="C324" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D311" s="8" t="n">
+      <c r="D324" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="E311" s="8" t="n">
+      <c r="E324" s="8" t="n">
         <v>320</v>
       </c>
-      <c r="F311" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G311" s="8" t="n">
+      <c r="F324" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G324" s="8" t="n">
         <v>2708</v>
       </c>
-      <c r="H311" s="8" t="n">
+      <c r="H324" s="8" t="n">
         <v>1892</v>
       </c>
-      <c r="I311" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J311" s="8" t="n">
+      <c r="I324" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J324" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="K311" s="8" t="n">
+      <c r="K324" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="L311" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M311" s="8" t="n">
+      <c r="L324" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M324" s="8" t="n">
         <v>223</v>
       </c>
-      <c r="N311" s="8" t="n">
+      <c r="N324" s="8" t="n">
         <v>1365</v>
       </c>
-      <c r="O311" s="8" t="n">
+      <c r="O324" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="P311" s="8" t="n">
+      <c r="P324" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="Q311" s="8" t="n">
+      <c r="Q324" s="8" t="n">
         <v>328</v>
       </c>
-      <c r="R311" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S311" s="8" t="n">
+      <c r="R324" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S324" s="8" t="n">
         <v>2931</v>
       </c>
-      <c r="T311" s="8" t="n">
+      <c r="T324" s="8" t="n">
         <v>3257</v>
       </c>
-      <c r="U311" s="9" t="n">
+      <c r="U324" s="9" t="n">
         <v>6598</v>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" s="6" t="inlineStr">
+    <row r="325">
+      <c r="A325" s="6" t="inlineStr">
         <is>
           <t>Şeker</t>
         </is>
       </c>
-      <c r="B312" s="7" t="inlineStr">
+      <c r="B325" s="7" t="inlineStr">
         <is>
           <t>2022 Ç2</t>
         </is>
       </c>
-      <c r="C312" s="8" t="n">
+      <c r="C325" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="D312" s="8" t="n">
+      <c r="D325" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="E312" s="8" t="n">
+      <c r="E325" s="8" t="n">
         <v>335</v>
       </c>
-      <c r="F312" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G312" s="8" t="n">
+      <c r="F325" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G325" s="8" t="n">
         <v>3127</v>
       </c>
-      <c r="H312" s="8" t="n">
+      <c r="H325" s="8" t="n">
         <v>2266</v>
       </c>
-      <c r="I312" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J312" s="8" t="n">
+      <c r="I325" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J325" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="K312" s="8" t="n">
+      <c r="K325" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="L312" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M312" s="8" t="n">
+      <c r="L325" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M325" s="8" t="n">
         <v>241</v>
       </c>
-      <c r="N312" s="8" t="n">
+      <c r="N325" s="8" t="n">
         <v>614</v>
       </c>
-      <c r="O312" s="8" t="n">
+      <c r="O325" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="P312" s="8" t="n">
+      <c r="P325" s="8" t="n">
         <v>89</v>
       </c>
-      <c r="Q312" s="8" t="n">
+      <c r="Q325" s="8" t="n">
         <v>342</v>
       </c>
-      <c r="R312" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S312" s="8" t="n">
+      <c r="R325" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S325" s="8" t="n">
         <v>3368</v>
       </c>
-      <c r="T312" s="8" t="n">
+      <c r="T325" s="8" t="n">
         <v>2880</v>
       </c>
-      <c r="U312" s="9" t="n">
+      <c r="U325" s="9" t="n">
         <v>6681</v>
       </c>
     </row>
-    <row r="313">
-      <c r="A313" s="6" t="inlineStr">
+    <row r="326">
+      <c r="A326" s="6" t="inlineStr">
         <is>
           <t>Şeker</t>
         </is>
       </c>
-      <c r="B313" s="7" t="inlineStr">
+      <c r="B326" s="7" t="inlineStr">
         <is>
           <t>2022 Ç3</t>
         </is>
       </c>
-      <c r="C313" s="8" t="n">
+      <c r="C326" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D313" s="8" t="n">
+      <c r="D326" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="E313" s="8" t="n">
+      <c r="E326" s="8" t="n">
         <v>103</v>
       </c>
-      <c r="F313" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G313" s="8" t="n">
+      <c r="F326" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G326" s="8" t="n">
         <v>4463</v>
       </c>
-      <c r="H313" s="8" t="n">
+      <c r="H326" s="8" t="n">
         <v>2488</v>
       </c>
-      <c r="I313" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J313" s="8" t="n">
+      <c r="I326" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" s="8" t="n">
         <v>70</v>
       </c>
-      <c r="K313" s="8" t="n">
+      <c r="K326" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="L313" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M313" s="8" t="n">
+      <c r="L326" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M326" s="8" t="n">
         <v>750</v>
       </c>
-      <c r="N313" s="8" t="n">
+      <c r="N326" s="8" t="n">
         <v>686</v>
       </c>
-      <c r="O313" s="8" t="n">
+      <c r="O326" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="P313" s="8" t="n">
+      <c r="P326" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="Q313" s="8" t="n">
+      <c r="Q326" s="8" t="n">
         <v>116</v>
       </c>
-      <c r="R313" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S313" s="8" t="n">
+      <c r="R326" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S326" s="8" t="n">
         <v>5213</v>
       </c>
-      <c r="T313" s="8" t="n">
+      <c r="T326" s="8" t="n">
         <v>3175</v>
       </c>
-      <c r="U313" s="9" t="n">
+      <c r="U326" s="9" t="n">
         <v>8605</v>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" s="6" t="inlineStr">
+    <row r="327">
+      <c r="A327" s="6" t="inlineStr">
         <is>
           <t>Şeker</t>
         </is>
       </c>
-      <c r="B314" s="7" t="inlineStr">
+      <c r="B327" s="7" t="inlineStr">
         <is>
           <t>2022 Ç4</t>
         </is>
       </c>
-      <c r="C314" s="8" t="n">
+      <c r="C327" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="D314" s="8" t="n">
+      <c r="D327" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="E314" s="8" t="n">
+      <c r="E327" s="8" t="n">
         <v>107</v>
       </c>
-      <c r="F314" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G314" s="8" t="n">
+      <c r="F327" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G327" s="8" t="n">
         <v>5735</v>
       </c>
-      <c r="H314" s="8" t="n">
+      <c r="H327" s="8" t="n">
         <v>2545</v>
       </c>
-      <c r="I314" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J314" s="8" t="n">
+      <c r="I327" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J327" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="K314" s="8" t="n">
+      <c r="K327" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="L314" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M314" s="8" t="n">
+      <c r="L327" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M327" s="8" t="n">
         <v>2617</v>
       </c>
-      <c r="N314" s="8" t="n">
+      <c r="N327" s="8" t="n">
         <v>688</v>
       </c>
-      <c r="O314" s="8" t="n">
+      <c r="O327" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="P314" s="8" t="n">
+      <c r="P327" s="8" t="n">
         <v>110</v>
       </c>
-      <c r="Q314" s="8" t="n">
+      <c r="Q327" s="8" t="n">
         <v>120</v>
       </c>
-      <c r="R314" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S314" s="8" t="n">
+      <c r="R327" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S327" s="8" t="n">
         <v>8352</v>
       </c>
-      <c r="T314" s="8" t="n">
+      <c r="T327" s="8" t="n">
         <v>3233</v>
       </c>
-      <c r="U314" s="9" t="n">
+      <c r="U327" s="9" t="n">
         <v>11826</v>
       </c>
     </row>
-    <row r="315">
-      <c r="A315" s="6" t="inlineStr">
+    <row r="328">
+      <c r="A328" s="6" t="inlineStr">
         <is>
           <t>Şeker</t>
         </is>
       </c>
-      <c r="B315" s="7" t="inlineStr">
+      <c r="B328" s="7" t="inlineStr">
         <is>
           <t>2023 Ç2</t>
         </is>
       </c>
-      <c r="C315" s="8" t="n">
+      <c r="C328" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D315" s="8" t="n">
+      <c r="D328" s="8" t="n">
         <v>95</v>
       </c>
-      <c r="E315" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F315" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G315" s="8" t="n">
+      <c r="E328" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F328" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G328" s="8" t="n">
         <v>6203</v>
       </c>
-      <c r="H315" s="8" t="n">
+      <c r="H328" s="8" t="n">
         <v>3518</v>
       </c>
-      <c r="I315" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J315" s="8" t="n">
+      <c r="I328" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J328" s="8" t="n">
         <v>131</v>
       </c>
-      <c r="K315" s="8" t="n">
+      <c r="K328" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="L315" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M315" s="8" t="n">
+      <c r="L328" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M328" s="8" t="n">
         <v>519</v>
       </c>
-      <c r="N315" s="8" t="n">
+      <c r="N328" s="8" t="n">
         <v>684</v>
       </c>
-      <c r="O315" s="8" t="n">
+      <c r="O328" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="P315" s="8" t="n">
+      <c r="P328" s="8" t="n">
         <v>227</v>
       </c>
-      <c r="Q315" s="8" t="n">
+      <c r="Q328" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="R315" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S315" s="8" t="n">
+      <c r="R328" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S328" s="8" t="n">
         <v>6722</v>
       </c>
-      <c r="T315" s="8" t="n">
+      <c r="T328" s="8" t="n">
         <v>4202</v>
       </c>
-      <c r="U315" s="9" t="n">
+      <c r="U328" s="9" t="n">
         <v>11170</v>
       </c>
     </row>
-    <row r="316">
-      <c r="A316" s="6" t="inlineStr">
+    <row r="329">
+      <c r="A329" s="6" t="inlineStr">
         <is>
           <t>Şeker</t>
         </is>
       </c>
-      <c r="B316" s="7" t="inlineStr">
+      <c r="B329" s="7" t="inlineStr">
         <is>
           <t>2023 Ç3</t>
         </is>
       </c>
-      <c r="C316" s="8" t="n">
+      <c r="C329" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D316" s="8" t="n">
+      <c r="D329" s="8" t="n">
         <v>96</v>
       </c>
-      <c r="E316" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F316" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G316" s="8" t="n">
+      <c r="E329" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F329" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G329" s="8" t="n">
         <v>6716</v>
       </c>
-      <c r="H316" s="8" t="n">
+      <c r="H329" s="8" t="n">
         <v>3684</v>
       </c>
-      <c r="I316" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J316" s="8" t="n">
+      <c r="I329" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J329" s="8" t="n">
         <v>135</v>
       </c>
-      <c r="K316" s="8" t="n">
+      <c r="K329" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="L316" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M316" s="8" t="n">
+      <c r="L329" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M329" s="8" t="n">
         <v>512</v>
       </c>
-      <c r="N316" s="8" t="n">
+      <c r="N329" s="8" t="n">
         <v>735</v>
       </c>
-      <c r="O316" s="8" t="n">
+      <c r="O329" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="P316" s="8" t="n">
+      <c r="P329" s="8" t="n">
         <v>231</v>
       </c>
-      <c r="Q316" s="8" t="n">
+      <c r="Q329" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="R316" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S316" s="8" t="n">
+      <c r="R329" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S329" s="8" t="n">
         <v>7228</v>
       </c>
-      <c r="T316" s="8" t="n">
+      <c r="T329" s="8" t="n">
         <v>4419</v>
       </c>
-      <c r="U316" s="9" t="n">
+      <c r="U329" s="9" t="n">
         <v>11898</v>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" s="6" t="inlineStr">
+    <row r="330">
+      <c r="A330" s="6" t="inlineStr">
         <is>
           <t>Şeker</t>
         </is>
       </c>
-      <c r="B317" s="7" t="inlineStr">
+      <c r="B330" s="7" t="inlineStr">
         <is>
           <t>2024 Ç2</t>
         </is>
       </c>
-      <c r="C317" s="8" t="n">
+      <c r="C330" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="D317" s="8" t="n">
+      <c r="D330" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="E317" s="8" t="n">
+      <c r="E330" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="F317" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G317" s="8" t="n">
+      <c r="F330" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G330" s="8" t="n">
         <v>8057</v>
       </c>
-      <c r="H317" s="8" t="n">
+      <c r="H330" s="8" t="n">
         <v>4557</v>
       </c>
-      <c r="I317" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J317" s="8" t="n">
+      <c r="I330" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J330" s="8" t="n">
         <v>184</v>
       </c>
-      <c r="K317" s="8" t="n">
+      <c r="K330" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="L317" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M317" s="8" t="n">
+      <c r="L330" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M330" s="8" t="n">
         <v>231</v>
       </c>
-      <c r="N317" s="8" t="n">
+      <c r="N330" s="8" t="n">
         <v>525</v>
       </c>
-      <c r="O317" s="8" t="n">
+      <c r="O330" s="8" t="n">
         <v>52</v>
       </c>
-      <c r="P317" s="8" t="n">
+      <c r="P330" s="8" t="n">
         <v>263</v>
       </c>
-      <c r="Q317" s="8" t="n">
+      <c r="Q330" s="8" t="n">
         <v>46</v>
       </c>
-      <c r="R317" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S317" s="8" t="n">
+      <c r="R330" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S330" s="8" t="n">
         <v>8288</v>
       </c>
-      <c r="T317" s="8" t="n">
+      <c r="T330" s="8" t="n">
         <v>5082</v>
       </c>
-      <c r="U317" s="9" t="n">
+      <c r="U330" s="9" t="n">
         <v>13732</v>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" s="2" t="inlineStr">
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
         <is>
           <t>Kaynak: bankaların solo BDDK formatlı bilançoları. ASA = GUD farkı kâr/zarara yansıtılan (1.2), SH = GUD farkı diğer kapsamlı gelire yansıtılan (1.3), VKET = itfa edilmiş maliyetle ölçülen diğer finansal varlıklar (2.4); DİBS = devlet borçlanma senetleri alt satırı, DİĞER = kalan. Yalnız PDF'i yüklenmiş banka-dönemler yer alır.</t>
         </is>
